--- a/balance/siam-legends-balance.xlsx
+++ b/balance/siam-legends-balance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kenio\Downloads\siam-legends-online (2)\siam-legends-online\balance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F6CFE75-7857-4E65-8AD0-513E1E8B4F7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4D56A65-6C81-4F9B-8778-C8DB7F9A73D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -117,7 +117,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="203">
   <si>
     <t>Siam Legends Online — ตารางสมดุลเกม (มอน / เลเวล / EXP)</t>
   </si>
@@ -723,6 +723,9 @@
   </si>
   <si>
     <t>บอสสุดท้าย</t>
+  </si>
+  <si>
+    <t>ปูแดง</t>
   </si>
 </sst>
 </file>
@@ -9844,7 +9847,7 @@
         <v>68</v>
       </c>
       <c r="G101" s="26">
-        <f t="shared" ref="G101:G132" si="21">MAX(1,D101-F101)</f>
+        <f t="shared" ref="G101:G104" si="21">MAX(1,D101-F101)</f>
         <v>1297.4000000000001</v>
       </c>
       <c r="H101" s="25">
@@ -9864,11 +9867,11 @@
         <v>686.62742622201927</v>
       </c>
       <c r="L101" s="25">
-        <f t="shared" ref="L101:L132" si="22">K101*60/J101</f>
+        <f t="shared" ref="L101:L104" si="22">K101*60/J101</f>
         <v>6058.4772901942879</v>
       </c>
       <c r="M101" s="25">
-        <f t="shared" ref="M101:M132" si="23">MAX(1,ROUND(B101/L101,0))</f>
+        <f t="shared" ref="M101:M104" si="23">MAX(1,ROUND(B101/L101,0))</f>
         <v>2260</v>
       </c>
       <c r="N101" s="25">
@@ -9884,7 +9887,7 @@
         <v>6058</v>
       </c>
       <c r="Q101" s="27">
-        <f t="shared" ref="Q101:Q132" si="24">P101*J101/60</f>
+        <f t="shared" ref="Q101:Q104" si="24">P101*J101/60</f>
         <v>686.57333333333338</v>
       </c>
       <c r="R101" s="26">
@@ -10120,7 +10123,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:O42"/>
+  <dimension ref="A1:O43"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -12243,6 +12246,53 @@
         <v>201</v>
       </c>
     </row>
+    <row r="43" spans="1:15">
+      <c r="A43" s="30" t="s">
+        <v>202</v>
+      </c>
+      <c r="B43" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="C43" s="31">
+        <v>3</v>
+      </c>
+      <c r="D43" s="31" t="s">
+        <v>119</v>
+      </c>
+      <c r="E43" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="F43" s="29">
+        <v>1.3</v>
+      </c>
+      <c r="G43" s="29">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="H43" s="25">
+        <f>ROUND(INDEX(เลเวล!$H$5:$H$104,C43)*F43*IF(D43="บอส",ตั้งค่า!$C$29,1),0)</f>
+        <v>81</v>
+      </c>
+      <c r="I43" s="25">
+        <f>ROUND(INDEX(เลเวล!$F$5:$F$104,C43)*IF(D43="บอส",ตั้งค่า!$C$32,1),0)</f>
+        <v>1</v>
+      </c>
+      <c r="J43" s="25">
+        <f>ROUND(INDEX(เลเวล!$I$5:$I$104,C43)*IF(D43="บอส",ตั้งค่า!$C$31,1),0)</f>
+        <v>10</v>
+      </c>
+      <c r="K43" s="25">
+        <f>ROUND(INDEX(เลเวล!$M$5:$M$104,C43)*G43*IF(D43="บอส",ตั้งค่า!$C$30,1),0)</f>
+        <v>43</v>
+      </c>
+      <c r="L43" s="25">
+        <f>ROUND(INDEX(เลเวล!$N$5:$N$104,C43)*IF(D43="บอส",ตั้งค่า!$C$33,1),0)</f>
+        <v>15</v>
+      </c>
+      <c r="M43" s="25">
+        <f>ROUND(INDEX(เลเวล!$O$5:$O$104,C43)*IF(D43="บอส",ตั้งค่า!$C$33,1),0)</f>
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/balance/siam-legends-balance.xlsx
+++ b/balance/siam-legends-balance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kenio\Downloads\siam-legends-online (2)\siam-legends-online\balance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4D56A65-6C81-4F9B-8778-C8DB7F9A73D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{374DD698-A2AD-4EEE-B88D-F7C5F97BBC14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -503,9 +503,6 @@
     <t>ช้าแต่ถึก</t>
   </si>
   <si>
-    <t>กบเขียว</t>
-  </si>
-  <si>
     <t>กระโดดไกล</t>
   </si>
   <si>
@@ -726,6 +723,9 @@
   </si>
   <si>
     <t>ปูแดง</t>
+  </si>
+  <si>
+    <t>กบบัว</t>
   </si>
 </sst>
 </file>
@@ -10414,7 +10414,7 @@
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="3" t="s">
-        <v>128</v>
+        <v>202</v>
       </c>
       <c r="B9" s="28" t="s">
         <v>118</v>
@@ -10463,12 +10463,12 @@
         <v>4</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B10" s="28" t="s">
         <v>118</v>
@@ -10480,7 +10480,7 @@
         <v>119</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F10" s="29">
         <v>1.2</v>
@@ -10517,12 +10517,12 @@
         <v>5</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B11" s="28" t="s">
         <v>118</v>
@@ -10534,7 +10534,7 @@
         <v>119</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F11" s="29">
         <v>1</v>
@@ -10571,12 +10571,12 @@
         <v>5</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="30" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B12" s="31" t="s">
         <v>118</v>
@@ -10585,10 +10585,10 @@
         <v>10</v>
       </c>
       <c r="D12" s="31" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F12" s="29">
         <v>1</v>
@@ -10625,15 +10625,15 @@
         <v>161</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B13" s="28" t="s">
         <v>138</v>
-      </c>
-      <c r="B13" s="28" t="s">
-        <v>139</v>
       </c>
       <c r="C13" s="28">
         <v>11</v>
@@ -10679,15 +10679,15 @@
         <v>4</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C14" s="28">
         <v>13</v>
@@ -10696,7 +10696,7 @@
         <v>119</v>
       </c>
       <c r="E14" s="28" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F14" s="29">
         <v>1</v>
@@ -10733,15 +10733,15 @@
         <v>5</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C15" s="28">
         <v>14</v>
@@ -10787,15 +10787,15 @@
         <v>5</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B16" s="28" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C16" s="28">
         <v>16</v>
@@ -10804,7 +10804,7 @@
         <v>119</v>
       </c>
       <c r="E16" s="28" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F16" s="29">
         <v>0.9</v>
@@ -10841,15 +10841,15 @@
         <v>4</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B17" s="28" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C17" s="28">
         <v>18</v>
@@ -10858,7 +10858,7 @@
         <v>119</v>
       </c>
       <c r="E17" s="28" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F17" s="29">
         <v>1.4</v>
@@ -10895,24 +10895,24 @@
         <v>6</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="30" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B18" s="31" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C18" s="31">
         <v>20</v>
       </c>
       <c r="D18" s="31" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E18" s="31" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F18" s="29">
         <v>1</v>
@@ -10949,15 +10949,15 @@
         <v>160</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B19" s="28" t="s">
         <v>151</v>
-      </c>
-      <c r="B19" s="28" t="s">
-        <v>152</v>
       </c>
       <c r="C19" s="28">
         <v>22</v>
@@ -10966,7 +10966,7 @@
         <v>119</v>
       </c>
       <c r="E19" s="28" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F19" s="29">
         <v>1.2</v>
@@ -11003,15 +11003,15 @@
         <v>5</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B20" s="28" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C20" s="28">
         <v>24</v>
@@ -11020,7 +11020,7 @@
         <v>119</v>
       </c>
       <c r="E20" s="28" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F20" s="29">
         <v>0.8</v>
@@ -11057,15 +11057,15 @@
         <v>4</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="21" spans="1:15">
       <c r="A21" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B21" s="28" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C21" s="28">
         <v>26</v>
@@ -11074,7 +11074,7 @@
         <v>119</v>
       </c>
       <c r="E21" s="28" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F21" s="29">
         <v>0.9</v>
@@ -11111,15 +11111,15 @@
         <v>4</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="22" spans="1:15">
       <c r="A22" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B22" s="28" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C22" s="28">
         <v>29</v>
@@ -11128,7 +11128,7 @@
         <v>119</v>
       </c>
       <c r="E22" s="28" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F22" s="29">
         <v>1.1000000000000001</v>
@@ -11165,15 +11165,15 @@
         <v>5</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="23" spans="1:15">
       <c r="A23" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B23" s="28" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C23" s="28">
         <v>32</v>
@@ -11182,7 +11182,7 @@
         <v>119</v>
       </c>
       <c r="E23" s="28" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F23" s="29">
         <v>1.6</v>
@@ -11219,24 +11219,24 @@
         <v>7</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="30" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B24" s="31" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C24" s="31">
         <v>35</v>
       </c>
       <c r="D24" s="31" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E24" s="31" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F24" s="29">
         <v>1</v>
@@ -11273,15 +11273,15 @@
         <v>161</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B25" s="28" t="s">
         <v>164</v>
-      </c>
-      <c r="B25" s="28" t="s">
-        <v>165</v>
       </c>
       <c r="C25" s="28">
         <v>38</v>
@@ -11290,7 +11290,7 @@
         <v>119</v>
       </c>
       <c r="E25" s="28" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F25" s="29">
         <v>1</v>
@@ -11327,15 +11327,15 @@
         <v>5</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B26" s="28" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C26" s="28">
         <v>41</v>
@@ -11344,7 +11344,7 @@
         <v>119</v>
       </c>
       <c r="E26" s="28" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F26" s="29">
         <v>0.8</v>
@@ -11381,15 +11381,15 @@
         <v>4</v>
       </c>
       <c r="O26" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B27" s="28" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C27" s="28">
         <v>43</v>
@@ -11398,7 +11398,7 @@
         <v>119</v>
       </c>
       <c r="E27" s="28" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F27" s="29">
         <v>1</v>
@@ -11435,15 +11435,15 @@
         <v>4</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B28" s="28" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C28" s="28">
         <v>46</v>
@@ -11452,7 +11452,7 @@
         <v>119</v>
       </c>
       <c r="E28" s="28" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F28" s="29">
         <v>1.2</v>
@@ -11489,15 +11489,15 @@
         <v>5</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B29" s="28" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C29" s="28">
         <v>50</v>
@@ -11506,7 +11506,7 @@
         <v>119</v>
       </c>
       <c r="E29" s="28" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F29" s="29">
         <v>1.5</v>
@@ -11543,24 +11543,24 @@
         <v>7</v>
       </c>
       <c r="O29" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="30" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B30" s="31" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C30" s="31">
         <v>55</v>
       </c>
       <c r="D30" s="31" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E30" s="31" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F30" s="29">
         <v>1</v>
@@ -11597,15 +11597,15 @@
         <v>160</v>
       </c>
       <c r="O30" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="1:15">
       <c r="A31" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B31" s="28" t="s">
         <v>177</v>
-      </c>
-      <c r="B31" s="28" t="s">
-        <v>178</v>
       </c>
       <c r="C31" s="28">
         <v>58</v>
@@ -11614,7 +11614,7 @@
         <v>119</v>
       </c>
       <c r="E31" s="28" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F31" s="29">
         <v>1.3</v>
@@ -11651,15 +11651,15 @@
         <v>6</v>
       </c>
       <c r="O31" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="32" spans="1:15">
       <c r="A32" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B32" s="28" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C32" s="28">
         <v>61</v>
@@ -11668,7 +11668,7 @@
         <v>119</v>
       </c>
       <c r="E32" s="28" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F32" s="29">
         <v>1.2</v>
@@ -11705,15 +11705,15 @@
         <v>5</v>
       </c>
       <c r="O32" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="33" spans="1:15">
       <c r="A33" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B33" s="28" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C33" s="28">
         <v>64</v>
@@ -11722,7 +11722,7 @@
         <v>119</v>
       </c>
       <c r="E33" s="28" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F33" s="29">
         <v>0.9</v>
@@ -11759,15 +11759,15 @@
         <v>4</v>
       </c>
       <c r="O33" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="34" spans="1:15">
       <c r="A34" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B34" s="28" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C34" s="28">
         <v>67</v>
@@ -11776,7 +11776,7 @@
         <v>119</v>
       </c>
       <c r="E34" s="28" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F34" s="29">
         <v>1.5</v>
@@ -11813,15 +11813,15 @@
         <v>6</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="35" spans="1:15">
       <c r="A35" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B35" s="28" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C35" s="28">
         <v>71</v>
@@ -11830,7 +11830,7 @@
         <v>119</v>
       </c>
       <c r="E35" s="28" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F35" s="29">
         <v>1.2</v>
@@ -11867,24 +11867,24 @@
         <v>5</v>
       </c>
       <c r="O35" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="36" spans="1:15">
       <c r="A36" s="30" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B36" s="31" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C36" s="31">
         <v>75</v>
       </c>
       <c r="D36" s="31" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E36" s="31" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F36" s="29">
         <v>1</v>
@@ -11921,15 +11921,15 @@
         <v>161</v>
       </c>
       <c r="O36" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="37" spans="1:15">
       <c r="A37" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B37" s="28" t="s">
         <v>190</v>
-      </c>
-      <c r="B37" s="28" t="s">
-        <v>191</v>
       </c>
       <c r="C37" s="28">
         <v>80</v>
@@ -11938,7 +11938,7 @@
         <v>119</v>
       </c>
       <c r="E37" s="28" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F37" s="29">
         <v>1.2</v>
@@ -11975,15 +11975,15 @@
         <v>5</v>
       </c>
       <c r="O37" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="38" spans="1:15">
       <c r="A38" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B38" s="28" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C38" s="28">
         <v>84</v>
@@ -11992,7 +11992,7 @@
         <v>119</v>
       </c>
       <c r="E38" s="28" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F38" s="29">
         <v>1.1000000000000001</v>
@@ -12029,15 +12029,15 @@
         <v>5</v>
       </c>
       <c r="O38" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="39" spans="1:15">
       <c r="A39" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B39" s="28" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C39" s="28">
         <v>88</v>
@@ -12046,7 +12046,7 @@
         <v>119</v>
       </c>
       <c r="E39" s="28" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F39" s="29">
         <v>0.9</v>
@@ -12083,15 +12083,15 @@
         <v>4</v>
       </c>
       <c r="O39" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="40" spans="1:15">
       <c r="A40" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B40" s="28" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C40" s="28">
         <v>92</v>
@@ -12100,7 +12100,7 @@
         <v>119</v>
       </c>
       <c r="E40" s="28" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F40" s="29">
         <v>1</v>
@@ -12137,15 +12137,15 @@
         <v>4</v>
       </c>
       <c r="O40" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="41" spans="1:15">
       <c r="A41" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B41" s="28" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C41" s="28">
         <v>96</v>
@@ -12154,7 +12154,7 @@
         <v>119</v>
       </c>
       <c r="E41" s="28" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F41" s="29">
         <v>1.3</v>
@@ -12194,19 +12194,19 @@
     </row>
     <row r="42" spans="1:15">
       <c r="A42" s="30" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B42" s="31" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C42" s="31">
         <v>100</v>
       </c>
       <c r="D42" s="31" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E42" s="31" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F42" s="29">
         <v>1</v>
@@ -12243,12 +12243,12 @@
         <v>160</v>
       </c>
       <c r="O42" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="43" spans="1:15">
       <c r="A43" s="30" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B43" s="31" t="s">
         <v>118</v>

--- a/balance/siam-legends-balance.xlsx
+++ b/balance/siam-legends-balance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kenio\Downloads\siam-legends-online (2)\siam-legends-online\balance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{374DD698-A2AD-4EEE-B88D-F7C5F97BBC14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5987B0D-99F5-40F8-ADCF-115C9207F7B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -117,7 +117,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="206">
   <si>
     <t>Siam Legends Online — ตารางสมดุลเกม (มอน / เลเวล / EXP)</t>
   </si>
@@ -726,6 +726,15 @@
   </si>
   <si>
     <t>กบบัว</t>
+  </si>
+  <si>
+    <t>ตั๊กแตนเคียว</t>
+  </si>
+  <si>
+    <t>บ้านปากอ่าว</t>
+  </si>
+  <si>
+    <t>หมึกหมวกเหล็ก</t>
   </si>
 </sst>
 </file>
@@ -10123,7 +10132,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:O43"/>
+  <dimension ref="A1:O45"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -12293,6 +12302,100 @@
         <v>22</v>
       </c>
     </row>
+    <row r="44" spans="1:15">
+      <c r="A44" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="B44" s="31" t="s">
+        <v>204</v>
+      </c>
+      <c r="C44" s="31">
+        <v>10</v>
+      </c>
+      <c r="D44" s="31" t="s">
+        <v>119</v>
+      </c>
+      <c r="E44" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="F44" s="29">
+        <v>1</v>
+      </c>
+      <c r="G44" s="29">
+        <v>1</v>
+      </c>
+      <c r="H44" s="25">
+        <f>ROUND(INDEX(เลเวล!$H$5:$H$104,C44)*F44*IF(D44="บอส",ตั้งค่า!$C$29,1),0)</f>
+        <v>136</v>
+      </c>
+      <c r="I44" s="25">
+        <f>ROUND(INDEX(เลเวล!$F$5:$F$104,C44)*IF(D44="บอส",ตั้งค่า!$C$32,1),0)</f>
+        <v>2</v>
+      </c>
+      <c r="J44" s="25">
+        <f>ROUND(INDEX(เลเวล!$I$5:$I$104,C44)*IF(D44="บอส",ตั้งค่า!$C$31,1),0)</f>
+        <v>18</v>
+      </c>
+      <c r="K44" s="25">
+        <f>ROUND(INDEX(เลเวล!$M$5:$M$104,C44)*G44*IF(D44="บอส",ตั้งค่า!$C$30,1),0)</f>
+        <v>215</v>
+      </c>
+      <c r="L44" s="25">
+        <f>ROUND(INDEX(เลเวล!$N$5:$N$104,C44)*IF(D44="บอส",ตั้งค่า!$C$33,1),0)</f>
+        <v>86</v>
+      </c>
+      <c r="M44" s="25">
+        <f>ROUND(INDEX(เลเวล!$O$5:$O$104,C44)*IF(D44="บอส",ตั้งค่า!$C$33,1),0)</f>
+        <v>129</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15">
+      <c r="A45" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="B45" s="31" t="s">
+        <v>204</v>
+      </c>
+      <c r="C45" s="31">
+        <v>12</v>
+      </c>
+      <c r="D45" s="31" t="s">
+        <v>119</v>
+      </c>
+      <c r="E45" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="F45" s="29">
+        <v>1</v>
+      </c>
+      <c r="G45" s="29">
+        <v>1</v>
+      </c>
+      <c r="H45" s="25">
+        <f>ROUND(INDEX(เลเวล!$H$5:$H$104,C45)*F45*IF(D45="บอส",ตั้งค่า!$C$29,1),0)</f>
+        <v>161</v>
+      </c>
+      <c r="I45" s="25">
+        <f>ROUND(INDEX(เลเวล!$F$5:$F$104,C45)*IF(D45="บอส",ตั้งค่า!$C$32,1),0)</f>
+        <v>2</v>
+      </c>
+      <c r="J45" s="25">
+        <f>ROUND(INDEX(เลเวล!$I$5:$I$104,C45)*IF(D45="บอส",ตั้งค่า!$C$31,1),0)</f>
+        <v>21</v>
+      </c>
+      <c r="K45" s="25">
+        <f>ROUND(INDEX(เลเวล!$M$5:$M$104,C45)*G45*IF(D45="บอส",ตั้งค่า!$C$30,1),0)</f>
+        <v>265</v>
+      </c>
+      <c r="L45" s="25">
+        <f>ROUND(INDEX(เลเวล!$N$5:$N$104,C45)*IF(D45="บอส",ตั้งค่า!$C$33,1),0)</f>
+        <v>106</v>
+      </c>
+      <c r="M45" s="25">
+        <f>ROUND(INDEX(เลเวล!$O$5:$O$104,C45)*IF(D45="บอส",ตั้งค่า!$C$33,1),0)</f>
+        <v>159</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/balance/siam-legends-balance.xlsx
+++ b/balance/siam-legends-balance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kenio\Downloads\siam-legends-online (2)\siam-legends-online\balance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0082F0A4-8C3F-4CBC-B300-1EDA867C562E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD699E35-CA26-4FDE-BF91-B30CD59E3938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,6 +18,7 @@
     <sheet name="เลเวล" sheetId="3" r:id="rId3"/>
     <sheet name="มอน" sheetId="4" r:id="rId4"/>
     <sheet name="สายเลี้ยงตัว" sheetId="5" r:id="rId5"/>
+    <sheet name="อุปกรณ์" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -61,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="270">
   <si>
     <t>Siam Legends Online — ตารางสมดุลเกม (มอน / เลเวล / EXP)</t>
   </si>
@@ -737,6 +738,141 @@
   <si>
     <t>แต้มสะสมถึงค่านี้</t>
   </si>
+  <si>
+    <t>อุปกรณ์ — ช่องใส่ 10 ช่องแบบ Ragnarok · แก้เฉพาะช่องสีน้ำเงิน แล้ว Save ใน Excel และรัน python tools/export_balance.py</t>
+  </si>
+  <si>
+    <t>ATK อาวุธ = ATK สายตี (ชีตสายเลี้ยงตัว) ที่เลเวลของ × ตั้งค่า!C14 × เลเวลของ · DEF/MDEF % = ค่ารวม × สัดส่วนช่อง × เลเวลของ ÷ เลเวลสูงสุด</t>
+  </si>
+  <si>
+    <t>ค่ารวมทุกชิ้นที่เลเวลสูงสุด</t>
+  </si>
+  <si>
+    <t>DEF % รวม</t>
+  </si>
+  <si>
+    <t>เท่ากับเพดาน DEF % ของมอน (docs/stat-system.md)</t>
+  </si>
+  <si>
+    <t>MDEF % รวม</t>
+  </si>
+  <si>
+    <t>เท่ากับเพดาน MDEF % ของมอน</t>
+  </si>
+  <si>
+    <t>ช่อง</t>
+  </si>
+  <si>
+    <t>key</t>
+  </si>
+  <si>
+    <t>สัดส่วน DEF</t>
+  </si>
+  <si>
+    <t>สัดส่วน MDEF</t>
+  </si>
+  <si>
+    <t>หัวบน</t>
+  </si>
+  <si>
+    <t>head_top</t>
+  </si>
+  <si>
+    <t>หัวกลาง</t>
+  </si>
+  <si>
+    <t>head_mid</t>
+  </si>
+  <si>
+    <t>หัวล่าง</t>
+  </si>
+  <si>
+    <t>head_low</t>
+  </si>
+  <si>
+    <t>ชุด</t>
+  </si>
+  <si>
+    <t>armor</t>
+  </si>
+  <si>
+    <t>อาวุธ</t>
+  </si>
+  <si>
+    <t>weapon</t>
+  </si>
+  <si>
+    <t>โล่</t>
+  </si>
+  <si>
+    <t>shield</t>
+  </si>
+  <si>
+    <t>ผ้าคลุม</t>
+  </si>
+  <si>
+    <t>garment</t>
+  </si>
+  <si>
+    <t>รองเท้า</t>
+  </si>
+  <si>
+    <t>shoes</t>
+  </si>
+  <si>
+    <t>เครื่องประดับ</t>
+  </si>
+  <si>
+    <t>accessory</t>
+  </si>
+  <si>
+    <t>รวม (ควรเป็น 1 · เครื่องประดับนับ 2 ชิ้น)</t>
+  </si>
+  <si>
+    <t>รายการอุปกรณ์ (id ต้องตรงกับ shared/items.ts) · ช่อง = ชื่อในตารางช่องด้านบน</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>มอนที่ดรอป</t>
+  </si>
+  <si>
+    <t>เลเวลของ</t>
+  </si>
+  <si>
+    <t>INT</t>
+  </si>
+  <si>
+    <t>LUK</t>
+  </si>
+  <si>
+    <t>straw_hat</t>
+  </si>
+  <si>
+    <t>หมวกฟาง</t>
+  </si>
+  <si>
+    <t>sickle</t>
+  </si>
+  <si>
+    <t>เคียว</t>
+  </si>
+  <si>
+    <t>iron_helmet</t>
+  </si>
+  <si>
+    <t>หมวกเหล็ก</t>
+  </si>
+  <si>
+    <t>sai_sin</t>
+  </si>
+  <si>
+    <t>สายสิญจน์</t>
+  </si>
+  <si>
+    <t>(ไม่ได้ดรอปจากมอน)</t>
+  </si>
 </sst>
 </file>
 
@@ -748,7 +884,7 @@
     <numFmt numFmtId="189" formatCode="0.0%"/>
     <numFmt numFmtId="190" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -824,8 +960,19 @@
       <color rgb="FF1F4FBF"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F4FBF"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -861,6 +1008,11 @@
         <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -889,7 +1041,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -926,6 +1078,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
@@ -1739,7 +1893,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-6CBD-4753-85E5-CD5164B846E8}"/>
+              <c16:uniqueId val="{00000000-1337-4857-B962-02348B824EFD}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -26716,4 +26870,402 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:N26"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="34" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="34" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>228</v>
+      </c>
+      <c r="B5" s="35">
+        <v>40</v>
+      </c>
+      <c r="C5" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>230</v>
+      </c>
+      <c r="B6" s="35">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="34" t="s">
+        <v>232</v>
+      </c>
+      <c r="B8" s="34" t="s">
+        <v>233</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>234</v>
+      </c>
+      <c r="D8" s="34" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>236</v>
+      </c>
+      <c r="B9" t="s">
+        <v>237</v>
+      </c>
+      <c r="C9" s="35">
+        <v>0.15</v>
+      </c>
+      <c r="D9" s="35">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>238</v>
+      </c>
+      <c r="B10" t="s">
+        <v>239</v>
+      </c>
+      <c r="C10" s="35">
+        <v>0.05</v>
+      </c>
+      <c r="D10" s="35">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>240</v>
+      </c>
+      <c r="B11" t="s">
+        <v>241</v>
+      </c>
+      <c r="C11" s="35">
+        <v>0.05</v>
+      </c>
+      <c r="D11" s="35">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>242</v>
+      </c>
+      <c r="B12" t="s">
+        <v>243</v>
+      </c>
+      <c r="C12" s="35">
+        <v>0.35</v>
+      </c>
+      <c r="D12" s="35">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>244</v>
+      </c>
+      <c r="B13" t="s">
+        <v>245</v>
+      </c>
+      <c r="C13" s="35">
+        <v>0</v>
+      </c>
+      <c r="D13" s="35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>246</v>
+      </c>
+      <c r="B14" t="s">
+        <v>247</v>
+      </c>
+      <c r="C14" s="35">
+        <v>0.2</v>
+      </c>
+      <c r="D14" s="35">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>248</v>
+      </c>
+      <c r="B15" t="s">
+        <v>249</v>
+      </c>
+      <c r="C15" s="35">
+        <v>0.1</v>
+      </c>
+      <c r="D15" s="35">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>250</v>
+      </c>
+      <c r="B16" t="s">
+        <v>251</v>
+      </c>
+      <c r="C16" s="35">
+        <v>0.1</v>
+      </c>
+      <c r="D16" s="35">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" t="s">
+        <v>252</v>
+      </c>
+      <c r="B17" t="s">
+        <v>253</v>
+      </c>
+      <c r="C17" s="35">
+        <v>0</v>
+      </c>
+      <c r="D17" s="35">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" t="s">
+        <v>254</v>
+      </c>
+      <c r="C18">
+        <f>SUM(C9:C17)+C17</f>
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <f>SUM(D9:D17)+D17</f>
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="34" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="34" t="s">
+        <v>256</v>
+      </c>
+      <c r="B22" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="C22" s="34" t="s">
+        <v>232</v>
+      </c>
+      <c r="D22" s="34" t="s">
+        <v>257</v>
+      </c>
+      <c r="E22" s="34" t="s">
+        <v>258</v>
+      </c>
+      <c r="F22" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="G22" s="34" t="s">
+        <v>122</v>
+      </c>
+      <c r="H22" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="I22" s="34" t="s">
+        <v>220</v>
+      </c>
+      <c r="J22" s="34" t="s">
+        <v>118</v>
+      </c>
+      <c r="K22" s="34" t="s">
+        <v>223</v>
+      </c>
+      <c r="L22" s="34" t="s">
+        <v>259</v>
+      </c>
+      <c r="M22" s="34" t="s">
+        <v>119</v>
+      </c>
+      <c r="N22" s="34" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" t="s">
+        <v>261</v>
+      </c>
+      <c r="B23" t="s">
+        <v>262</v>
+      </c>
+      <c r="C23" s="35" t="s">
+        <v>236</v>
+      </c>
+      <c r="D23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E23">
+        <f>INDEX(มอน!$C:$C,MATCH(D23,มอน!$A:$A,0))</f>
+        <v>8</v>
+      </c>
+      <c r="F23">
+        <f>IF(C23="อาวุธ",ROUND(INDEX(สายเลี้ยงตัว!$E$5:$E$104,E23)*ตั้งค่า!$C$14*E23,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <f>IF(VLOOKUP(C23,$A$9:$D$17,3,0)=0,0,MAX(1,ROUND($B$5*VLOOKUP(C23,$A$9:$D$17,3,0)*E23/ตั้งค่า!$C$6,0)))</f>
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <f>IF(VLOOKUP(C23,$A$9:$D$17,4,0)=0,0,MAX(1,ROUND($B$6*VLOOKUP(C23,$A$9:$D$17,4,0)*E23/ตั้งค่า!$C$6,0)))</f>
+        <v>1</v>
+      </c>
+      <c r="I23" s="35"/>
+      <c r="J23" s="35"/>
+      <c r="K23" s="35"/>
+      <c r="L23" s="35"/>
+      <c r="M23" s="35"/>
+      <c r="N23" s="35"/>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" t="s">
+        <v>263</v>
+      </c>
+      <c r="B24" t="s">
+        <v>264</v>
+      </c>
+      <c r="C24" s="35" t="s">
+        <v>244</v>
+      </c>
+      <c r="D24" t="s">
+        <v>211</v>
+      </c>
+      <c r="E24">
+        <f>INDEX(มอน!$C:$C,MATCH(D24,มอน!$A:$A,0))</f>
+        <v>10</v>
+      </c>
+      <c r="F24">
+        <f>IF(C24="อาวุธ",ROUND(INDEX(สายเลี้ยงตัว!$E$5:$E$104,E24)*ตั้งค่า!$C$14*E24,0),0)</f>
+        <v>3</v>
+      </c>
+      <c r="G24">
+        <f>IF(VLOOKUP(C24,$A$9:$D$17,3,0)=0,0,MAX(1,ROUND($B$5*VLOOKUP(C24,$A$9:$D$17,3,0)*E24/ตั้งค่า!$C$6,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <f>IF(VLOOKUP(C24,$A$9:$D$17,4,0)=0,0,MAX(1,ROUND($B$6*VLOOKUP(C24,$A$9:$D$17,4,0)*E24/ตั้งค่า!$C$6,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="I24" s="35"/>
+      <c r="J24" s="35"/>
+      <c r="K24" s="35"/>
+      <c r="L24" s="35"/>
+      <c r="M24" s="35"/>
+      <c r="N24" s="35"/>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" t="s">
+        <v>265</v>
+      </c>
+      <c r="B25" t="s">
+        <v>266</v>
+      </c>
+      <c r="C25" s="35" t="s">
+        <v>236</v>
+      </c>
+      <c r="D25" t="s">
+        <v>213</v>
+      </c>
+      <c r="E25">
+        <f>INDEX(มอน!$C:$C,MATCH(D25,มอน!$A:$A,0))</f>
+        <v>12</v>
+      </c>
+      <c r="F25">
+        <f>IF(C25="อาวุธ",ROUND(INDEX(สายเลี้ยงตัว!$E$5:$E$104,E25)*ตั้งค่า!$C$14*E25,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <f>IF(VLOOKUP(C25,$A$9:$D$17,3,0)=0,0,MAX(1,ROUND($B$5*VLOOKUP(C25,$A$9:$D$17,3,0)*E25/ตั้งค่า!$C$6,0)))</f>
+        <v>1</v>
+      </c>
+      <c r="H25">
+        <f>IF(VLOOKUP(C25,$A$9:$D$17,4,0)=0,0,MAX(1,ROUND($B$6*VLOOKUP(C25,$A$9:$D$17,4,0)*E25/ตั้งค่า!$C$6,0)))</f>
+        <v>1</v>
+      </c>
+      <c r="I25" s="35"/>
+      <c r="J25" s="35"/>
+      <c r="K25" s="35"/>
+      <c r="L25" s="35"/>
+      <c r="M25" s="35"/>
+      <c r="N25" s="35"/>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" t="s">
+        <v>267</v>
+      </c>
+      <c r="B26" t="s">
+        <v>268</v>
+      </c>
+      <c r="C26" s="35" t="s">
+        <v>252</v>
+      </c>
+      <c r="D26" t="s">
+        <v>269</v>
+      </c>
+      <c r="E26" s="35">
+        <v>1</v>
+      </c>
+      <c r="F26">
+        <f>IF(C26="อาวุธ",ROUND(INDEX(สายเลี้ยงตัว!$E$5:$E$104,E26)*ตั้งค่า!$C$14*E26,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <f>IF(VLOOKUP(C26,$A$9:$D$17,3,0)=0,0,MAX(1,ROUND($B$5*VLOOKUP(C26,$A$9:$D$17,3,0)*E26/ตั้งค่า!$C$6,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <f>IF(VLOOKUP(C26,$A$9:$D$17,4,0)=0,0,MAX(1,ROUND($B$6*VLOOKUP(C26,$A$9:$D$17,4,0)*E26/ตั้งค่า!$C$6,0)))</f>
+        <v>1</v>
+      </c>
+      <c r="I26" s="35"/>
+      <c r="J26" s="35"/>
+      <c r="K26" s="35"/>
+      <c r="L26" s="35"/>
+      <c r="M26" s="35"/>
+      <c r="N26" s="35"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/balance/siam-legends-balance.xlsx
+++ b/balance/siam-legends-balance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kenio\Downloads\siam-legends-online (2)\siam-legends-online\balance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD699E35-CA26-4FDE-BF91-B30CD59E3938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42D6F4DE-367B-4747-97BF-9481E4944414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1893,7 +1893,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-1337-4857-B962-02348B824EFD}"/>
+              <c16:uniqueId val="{00000000-6676-4525-BF4E-3358D49622A5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -10417,8 +10417,8 @@
         <v>1</v>
       </c>
       <c r="H5" s="25">
-        <f>ROUND(INDEX(เลเวล!$H$5:$H$104,C5)*F5*IF(D5="บอส",ตั้งค่า!$C$29,1),0)</f>
-        <v>44</v>
+        <f>ROUND(ตั้งค่า!$C$20*(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C5,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C5,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C5,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C5,100))*(1-T5/100)-U5))*F5*IF(D5="บอส",ตั้งค่า!$C$29,1),0)</f>
+        <v>28</v>
       </c>
       <c r="I5" s="25">
         <f>ROUND(INDEX(เลเวล!$F$5:$F$104,C5)*IF(D5="บอส",ตั้งค่า!$C$32,1),0)</f>
@@ -10441,8 +10441,8 @@
         <v>2</v>
       </c>
       <c r="N5" s="25">
-        <f>ROUNDUP(H5/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C5,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C5,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C5,100))/100)*MIN(95,MAX(5,80+INDEX(สายเลี้ยงตัว!$F$5:$F$104,MIN(C5,100))-S5))/100*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C5,100))*(1-T5/100)-U5)),0)</f>
-        <v>8</v>
+        <f>ROUNDUP(H5/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C5,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C5,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C5,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C5,100))*(1-T5/100)-U5)),0)</f>
+        <v>4</v>
       </c>
       <c r="O5" s="3" t="s">
         <v>129</v>
@@ -10503,8 +10503,8 @@
         <v>0.8</v>
       </c>
       <c r="H6" s="25">
-        <f>ROUND(INDEX(เลเวล!$H$5:$H$104,C6)*F6*IF(D6="บอส",ตั้งค่า!$C$29,1),0)</f>
-        <v>37</v>
+        <f>ROUND(ตั้งค่า!$C$20*(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C6,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C6,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C6,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C6,100))*(1-T6/100)-U6))*F6*IF(D6="บอส",ตั้งค่า!$C$29,1),0)</f>
+        <v>17</v>
       </c>
       <c r="I6" s="25">
         <f>ROUND(INDEX(เลเวล!$F$5:$F$104,C6)*IF(D6="บอส",ตั้งค่า!$C$32,1),0)</f>
@@ -10527,8 +10527,8 @@
         <v>9</v>
       </c>
       <c r="N6" s="25">
-        <f>ROUNDUP(H6/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C6,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C6,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C6,100))/100)*MIN(95,MAX(5,80+INDEX(สายเลี้ยงตัว!$F$5:$F$104,MIN(C6,100))-S6))/100*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C6,100))*(1-T6/100)-U6)),0)</f>
-        <v>8</v>
+        <f>ROUNDUP(H6/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C6,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C6,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C6,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C6,100))*(1-T6/100)-U6)),0)</f>
+        <v>3</v>
       </c>
       <c r="O6" s="3" t="s">
         <v>131</v>
@@ -10589,8 +10589,8 @@
         <v>1.1499999999999999</v>
       </c>
       <c r="H7" s="25">
-        <f>ROUND(INDEX(เลเวล!$H$5:$H$104,C7)*F7*IF(D7="บอส",ตั้งค่า!$C$29,1),0)</f>
-        <v>57</v>
+        <f>ROUND(ตั้งค่า!$C$20*(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C7,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C7,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C7,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C7,100))*(1-T7/100)-U7))*F7*IF(D7="บอส",ตั้งค่า!$C$29,1),0)</f>
+        <v>37</v>
       </c>
       <c r="I7" s="25">
         <f>ROUND(INDEX(เลเวล!$F$5:$F$104,C7)*IF(D7="บอส",ตั้งค่า!$C$32,1),0)</f>
@@ -10613,8 +10613,8 @@
         <v>2</v>
       </c>
       <c r="N7" s="25">
-        <f>ROUNDUP(H7/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C7,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C7,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C7,100))/100)*MIN(95,MAX(5,80+INDEX(สายเลี้ยงตัว!$F$5:$F$104,MIN(C7,100))-S7))/100*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C7,100))*(1-T7/100)-U7)),0)</f>
-        <v>10</v>
+        <f>ROUNDUP(H7/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C7,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C7,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C7,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C7,100))*(1-T7/100)-U7)),0)</f>
+        <v>6</v>
       </c>
       <c r="O7" s="3" t="s">
         <v>133</v>
@@ -10675,8 +10675,8 @@
         <v>1.2</v>
       </c>
       <c r="H8" s="25">
-        <f>ROUND(INDEX(เลเวล!$H$5:$H$104,C8)*F8*IF(D8="บอส",ตั้งค่า!$C$29,1),0)</f>
-        <v>101</v>
+        <f>ROUND(ตั้งค่า!$C$20*(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C8,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C8,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C8,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C8,100))*(1-T8/100)-U8))*F8*IF(D8="บอส",ตั้งค่า!$C$29,1),0)</f>
+        <v>39</v>
       </c>
       <c r="I8" s="25">
         <f>ROUND(INDEX(เลเวล!$F$5:$F$104,C8)*IF(D8="บอส",ตั้งค่า!$C$32,1),0)</f>
@@ -10699,8 +10699,8 @@
         <v>37</v>
       </c>
       <c r="N8" s="25">
-        <f>ROUNDUP(H8/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C8,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C8,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C8,100))/100)*MIN(95,MAX(5,80+INDEX(สายเลี้ยงตัว!$F$5:$F$104,MIN(C8,100))-S8))/100*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C8,100))*(1-T8/100)-U8)),0)</f>
-        <v>17</v>
+        <f>ROUNDUP(H8/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C8,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C8,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C8,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C8,100))*(1-T8/100)-U8)),0)</f>
+        <v>6</v>
       </c>
       <c r="O8" s="3" t="s">
         <v>135</v>
@@ -10761,8 +10761,8 @@
         <v>1</v>
       </c>
       <c r="H9" s="25">
-        <f>ROUND(INDEX(เลเวล!$H$5:$H$104,C9)*F9*IF(D9="บอส",ตั้งค่า!$C$29,1),0)</f>
-        <v>82</v>
+        <f>ROUND(ตั้งค่า!$C$20*(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C9,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C9,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C9,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C9,100))*(1-T9/100)-U9))*F9*IF(D9="บอส",ตั้งค่า!$C$29,1),0)</f>
+        <v>32</v>
       </c>
       <c r="I9" s="25">
         <f>ROUND(INDEX(เลเวล!$F$5:$F$104,C9)*IF(D9="บอส",ตั้งค่า!$C$32,1),0)</f>
@@ -10785,8 +10785,8 @@
         <v>53</v>
       </c>
       <c r="N9" s="25">
-        <f>ROUNDUP(H9/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C9,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C9,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C9,100))/100)*MIN(95,MAX(5,80+INDEX(สายเลี้ยงตัว!$F$5:$F$104,MIN(C9,100))-S9))/100*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C9,100))*(1-T9/100)-U9)),0)</f>
-        <v>13</v>
+        <f>ROUNDUP(H9/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C9,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C9,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C9,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C9,100))*(1-T9/100)-U9)),0)</f>
+        <v>4</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>137</v>
@@ -10847,8 +10847,8 @@
         <v>1.1499999999999999</v>
       </c>
       <c r="H10" s="25">
-        <f>ROUND(INDEX(เลเวล!$H$5:$H$104,C10)*F10*IF(D10="บอส",ตั้งค่า!$C$29,1),0)</f>
-        <v>125</v>
+        <f>ROUND(ตั้งค่า!$C$20*(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C10,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C10,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C10,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C10,100))*(1-T10/100)-U10))*F10*IF(D10="บอส",ตั้งค่า!$C$29,1),0)</f>
+        <v>53</v>
       </c>
       <c r="I10" s="25">
         <f>ROUND(INDEX(เลเวล!$F$5:$F$104,C10)*IF(D10="บอส",ตั้งค่า!$C$32,1),0)</f>
@@ -10871,8 +10871,8 @@
         <v>84</v>
       </c>
       <c r="N10" s="25">
-        <f>ROUNDUP(H10/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C10,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C10,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C10,100))/100)*MIN(95,MAX(5,80+INDEX(สายเลี้ยงตัว!$F$5:$F$104,MIN(C10,100))-S10))/100*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C10,100))*(1-T10/100)-U10)),0)</f>
-        <v>14</v>
+        <f>ROUNDUP(H10/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C10,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C10,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C10,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C10,100))*(1-T10/100)-U10)),0)</f>
+        <v>5</v>
       </c>
       <c r="O10" s="3" t="s">
         <v>140</v>
@@ -10933,8 +10933,8 @@
         <v>1</v>
       </c>
       <c r="H11" s="25">
-        <f>ROUND(INDEX(เลเวล!$H$5:$H$104,C11)*F11*IF(D11="บอส",ตั้งค่า!$C$29,1),0)</f>
-        <v>116</v>
+        <f>ROUND(ตั้งค่า!$C$20*(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C11,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C11,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C11,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C11,100))*(1-T11/100)-U11))*F11*IF(D11="บอส",ตั้งค่า!$C$29,1),0)</f>
+        <v>48</v>
       </c>
       <c r="I11" s="25">
         <f>ROUND(INDEX(เลเวล!$F$5:$F$104,C11)*IF(D11="บอส",ตั้งค่า!$C$32,1),0)</f>
@@ -10957,8 +10957,8 @@
         <v>99</v>
       </c>
       <c r="N11" s="25">
-        <f>ROUNDUP(H11/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C11,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C11,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C11,100))/100)*MIN(95,MAX(5,80+INDEX(สายเลี้ยงตัว!$F$5:$F$104,MIN(C11,100))-S11))/100*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C11,100))*(1-T11/100)-U11)),0)</f>
-        <v>12</v>
+        <f>ROUNDUP(H11/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C11,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C11,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C11,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C11,100))*(1-T11/100)-U11)),0)</f>
+        <v>5</v>
       </c>
       <c r="O11" s="3" t="s">
         <v>142</v>
@@ -11019,8 +11019,8 @@
         <v>1</v>
       </c>
       <c r="H12" s="25">
-        <f>ROUND(INDEX(เลเวล!$H$5:$H$104,C12)*F12*IF(D12="บอส",ตั้งค่า!$C$29,1),0)</f>
-        <v>5440</v>
+        <f>ROUND(ตั้งค่า!$C$20*(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C12,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C12,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C12,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C12,100))*(1-T12/100)-U12))*F12*IF(D12="บอส",ตั้งค่า!$C$29,1),0)</f>
+        <v>1888</v>
       </c>
       <c r="I12" s="25">
         <f>ROUND(INDEX(เลเวล!$F$5:$F$104,C12)*IF(D12="บอส",ตั้งค่า!$C$32,1),0)</f>
@@ -11043,8 +11043,8 @@
         <v>2580</v>
       </c>
       <c r="N12" s="25">
-        <f>ROUNDUP(H12/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C12,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C12,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C12,100))/100)*MIN(95,MAX(5,80+INDEX(สายเลี้ยงตัว!$F$5:$F$104,MIN(C12,100))-S12))/100*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C12,100))*(1-T12/100)-U12)),0)</f>
-        <v>538</v>
+        <f>ROUNDUP(H12/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C12,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C12,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C12,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C12,100))*(1-T12/100)-U12)),0)</f>
+        <v>161</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>145</v>
@@ -11105,8 +11105,8 @@
         <v>0.9</v>
       </c>
       <c r="H13" s="25">
-        <f>ROUND(INDEX(เลเวล!$H$5:$H$104,C13)*F13*IF(D13="บอส",ตั้งค่า!$C$29,1),0)</f>
-        <v>118</v>
+        <f>ROUND(ตั้งค่า!$C$20*(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C13,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C13,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C13,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C13,100))*(1-T13/100)-U13))*F13*IF(D13="บอส",ตั้งค่า!$C$29,1),0)</f>
+        <v>41</v>
       </c>
       <c r="I13" s="25">
         <f>ROUND(INDEX(เลเวล!$F$5:$F$104,C13)*IF(D13="บอส",ตั้งค่า!$C$32,1),0)</f>
@@ -11129,8 +11129,8 @@
         <v>144</v>
       </c>
       <c r="N13" s="25">
-        <f>ROUNDUP(H13/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C13,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C13,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C13,100))/100)*MIN(95,MAX(5,80+INDEX(สายเลี้ยงตัว!$F$5:$F$104,MIN(C13,100))-S13))/100*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C13,100))*(1-T13/100)-U13)),0)</f>
-        <v>11</v>
+        <f>ROUNDUP(H13/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C13,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C13,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C13,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C13,100))*(1-T13/100)-U13)),0)</f>
+        <v>4</v>
       </c>
       <c r="O13" s="3" t="s">
         <v>148</v>
@@ -11191,8 +11191,8 @@
         <v>1.05</v>
       </c>
       <c r="H14" s="25">
-        <f>ROUND(INDEX(เลเวล!$H$5:$H$104,C14)*F14*IF(D14="บอส",ตั้งค่า!$C$29,1),0)</f>
-        <v>175</v>
+        <f>ROUND(ตั้งค่า!$C$20*(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C14,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C14,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C14,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C14,100))*(1-T14/100)-U14))*F14*IF(D14="บอส",ตั้งค่า!$C$29,1),0)</f>
+        <v>55</v>
       </c>
       <c r="I14" s="25">
         <f>ROUND(INDEX(เลเวล!$F$5:$F$104,C14)*IF(D14="บอส",ตั้งค่า!$C$32,1),0)</f>
@@ -11215,8 +11215,8 @@
         <v>173</v>
       </c>
       <c r="N14" s="25">
-        <f>ROUNDUP(H14/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C14,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C14,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C14,100))/100)*MIN(95,MAX(5,80+INDEX(สายเลี้ยงตัว!$F$5:$F$104,MIN(C14,100))-S14))/100*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C14,100))*(1-T14/100)-U14)),0)</f>
-        <v>15</v>
+        <f>ROUNDUP(H14/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C14,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C14,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C14,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C14,100))*(1-T14/100)-U14)),0)</f>
+        <v>4</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>150</v>
@@ -11277,8 +11277,8 @@
         <v>1.05</v>
       </c>
       <c r="H15" s="25">
-        <f>ROUND(INDEX(เลเวล!$H$5:$H$104,C15)*F15*IF(D15="บอส",ตั้งค่า!$C$29,1),0)</f>
-        <v>208</v>
+        <f>ROUND(ตั้งค่า!$C$20*(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C15,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C15,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C15,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C15,100))*(1-T15/100)-U15))*F15*IF(D15="บอส",ตั้งค่า!$C$29,1),0)</f>
+        <v>60</v>
       </c>
       <c r="I15" s="25">
         <f>ROUND(INDEX(เลเวล!$F$5:$F$104,C15)*IF(D15="บอส",ตั้งค่า!$C$32,1),0)</f>
@@ -11301,8 +11301,8 @@
         <v>188</v>
       </c>
       <c r="N15" s="25">
-        <f>ROUNDUP(H15/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C15,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C15,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C15,100))/100)*MIN(95,MAX(5,80+INDEX(สายเลี้ยงตัว!$F$5:$F$104,MIN(C15,100))-S15))/100*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C15,100))*(1-T15/100)-U15)),0)</f>
-        <v>18</v>
+        <f>ROUNDUP(H15/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C15,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C15,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C15,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C15,100))*(1-T15/100)-U15)),0)</f>
+        <v>5</v>
       </c>
       <c r="O15" s="3" t="s">
         <v>152</v>
@@ -11363,8 +11363,8 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="H16" s="25">
-        <f>ROUND(INDEX(เลเวล!$H$5:$H$104,C16)*F16*IF(D16="บอส",ตั้งค่า!$C$29,1),0)</f>
-        <v>193</v>
+        <f>ROUND(ตั้งค่า!$C$20*(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C16,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C16,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C16,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C16,100))*(1-T16/100)-U16))*F16*IF(D16="บอส",ตั้งค่า!$C$29,1),0)</f>
+        <v>70</v>
       </c>
       <c r="I16" s="25">
         <f>ROUND(INDEX(เลเวล!$F$5:$F$104,C16)*IF(D16="บอส",ตั้งค่า!$C$32,1),0)</f>
@@ -11387,8 +11387,8 @@
         <v>217</v>
       </c>
       <c r="N16" s="25">
-        <f>ROUNDUP(H16/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C16,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C16,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C16,100))/100)*MIN(95,MAX(5,80+INDEX(สายเลี้ยงตัว!$F$5:$F$104,MIN(C16,100))-S16))/100*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C16,100))*(1-T16/100)-U16)),0)</f>
-        <v>12</v>
+        <f>ROUNDUP(H16/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C16,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C16,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C16,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C16,100))*(1-T16/100)-U16)),0)</f>
+        <v>4</v>
       </c>
       <c r="O16" s="3" t="s">
         <v>154</v>
@@ -11449,8 +11449,8 @@
         <v>1.25</v>
       </c>
       <c r="H17" s="25">
-        <f>ROUND(INDEX(เลเวล!$H$5:$H$104,C17)*F17*IF(D17="บอส",ตั้งค่า!$C$29,1),0)</f>
-        <v>344</v>
+        <f>ROUND(ตั้งค่า!$C$20*(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C17,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C17,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C17,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C17,100))*(1-T17/100)-U17))*F17*IF(D17="บอส",ตั้งค่า!$C$29,1),0)</f>
+        <v>112</v>
       </c>
       <c r="I17" s="25">
         <f>ROUND(INDEX(เลเวล!$F$5:$F$104,C17)*IF(D17="บอส",ตั้งค่า!$C$32,1),0)</f>
@@ -11473,8 +11473,8 @@
         <v>245</v>
       </c>
       <c r="N17" s="25">
-        <f>ROUNDUP(H17/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C17,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C17,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C17,100))/100)*MIN(95,MAX(5,80+INDEX(สายเลี้ยงตัว!$F$5:$F$104,MIN(C17,100))-S17))/100*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C17,100))*(1-T17/100)-U17)),0)</f>
-        <v>20</v>
+        <f>ROUNDUP(H17/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C17,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C17,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C17,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C17,100))*(1-T17/100)-U17)),0)</f>
+        <v>6</v>
       </c>
       <c r="O17" s="3" t="s">
         <v>156</v>
@@ -11535,8 +11535,8 @@
         <v>1</v>
       </c>
       <c r="H18" s="25">
-        <f>ROUND(INDEX(เลเวล!$H$5:$H$104,C18)*F18*IF(D18="บอส",ตั้งค่า!$C$29,1),0)</f>
-        <v>11000</v>
+        <f>ROUND(ตั้งค่า!$C$20*(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C18,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C18,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C18,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C18,100))*(1-T18/100)-U18))*F18*IF(D18="บอส",ตั้งค่า!$C$29,1),0)</f>
+        <v>3312</v>
       </c>
       <c r="I18" s="25">
         <f>ROUND(INDEX(เลเวล!$F$5:$F$104,C18)*IF(D18="บอส",ตั้งค่า!$C$32,1),0)</f>
@@ -11559,8 +11559,8 @@
         <v>5480</v>
       </c>
       <c r="N18" s="25">
-        <f>ROUNDUP(H18/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C18,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C18,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C18,100))/100)*MIN(95,MAX(5,80+INDEX(สายเลี้ยงตัว!$F$5:$F$104,MIN(C18,100))-S18))/100*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C18,100))*(1-T18/100)-U18)),0)</f>
-        <v>606</v>
+        <f>ROUNDUP(H18/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C18,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C18,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C18,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C18,100))*(1-T18/100)-U18)),0)</f>
+        <v>161</v>
       </c>
       <c r="O18" s="3" t="s">
         <v>158</v>
@@ -11621,8 +11621,8 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="H19" s="25">
-        <f>ROUND(INDEX(เลเวล!$H$5:$H$104,C19)*F19*IF(D19="บอส",ตั้งค่า!$C$29,1),0)</f>
-        <v>373</v>
+        <f>ROUND(ตั้งค่า!$C$20*(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C19,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C19,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C19,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C19,100))*(1-T19/100)-U19))*F19*IF(D19="บอส",ตั้งค่า!$C$29,1),0)</f>
+        <v>108</v>
       </c>
       <c r="I19" s="25">
         <f>ROUND(INDEX(เลเวล!$F$5:$F$104,C19)*IF(D19="บอส",ตั้งค่า!$C$32,1),0)</f>
@@ -11645,8 +11645,8 @@
         <v>302</v>
       </c>
       <c r="N19" s="25">
-        <f>ROUNDUP(H19/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C19,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C19,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C19,100))/100)*MIN(95,MAX(5,80+INDEX(สายเลี้ยงตัว!$F$5:$F$104,MIN(C19,100))-S19))/100*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C19,100))*(1-T19/100)-U19)),0)</f>
-        <v>19</v>
+        <f>ROUNDUP(H19/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C19,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C19,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C19,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C19,100))*(1-T19/100)-U19)),0)</f>
+        <v>5</v>
       </c>
       <c r="O19" s="3" t="s">
         <v>161</v>
@@ -11707,8 +11707,8 @@
         <v>0.9</v>
       </c>
       <c r="H20" s="25">
-        <f>ROUND(INDEX(เลเวล!$H$5:$H$104,C20)*F20*IF(D20="บอส",ตั้งค่า!$C$29,1),0)</f>
-        <v>277</v>
+        <f>ROUND(ตั้งค่า!$C$20*(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C20,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C20,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C20,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C20,100))*(1-T20/100)-U20))*F20*IF(D20="บอส",ตั้งค่า!$C$29,1),0)</f>
+        <v>74</v>
       </c>
       <c r="I20" s="25">
         <f>ROUND(INDEX(เลเวล!$F$5:$F$104,C20)*IF(D20="บอส",ตั้งค่า!$C$32,1),0)</f>
@@ -11731,8 +11731,8 @@
         <v>331</v>
       </c>
       <c r="N20" s="25">
-        <f>ROUNDUP(H20/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C20,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C20,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C20,100))/100)*MIN(95,MAX(5,80+INDEX(สายเลี้ยงตัว!$F$5:$F$104,MIN(C20,100))-S20))/100*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C20,100))*(1-T20/100)-U20)),0)</f>
-        <v>14</v>
+        <f>ROUNDUP(H20/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C20,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C20,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C20,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C20,100))*(1-T20/100)-U20)),0)</f>
+        <v>4</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>163</v>
@@ -11793,8 +11793,8 @@
         <v>1.05</v>
       </c>
       <c r="H21" s="25">
-        <f>ROUND(INDEX(เลเวล!$H$5:$H$104,C21)*F21*IF(D21="บอส",ตั้งค่า!$C$29,1),0)</f>
-        <v>348</v>
+        <f>ROUND(ตั้งค่า!$C$20*(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C21,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C21,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C21,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C21,100))*(1-T21/100)-U21))*F21*IF(D21="บอส",ตั้งค่า!$C$29,1),0)</f>
+        <v>104</v>
       </c>
       <c r="I21" s="25">
         <f>ROUND(INDEX(เลเวล!$F$5:$F$104,C21)*IF(D21="บอส",ตั้งค่า!$C$32,1),0)</f>
@@ -11817,8 +11817,8 @@
         <v>359</v>
       </c>
       <c r="N21" s="25">
-        <f>ROUNDUP(H21/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C21,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C21,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C21,100))/100)*MIN(95,MAX(5,80+INDEX(สายเลี้ยงตัว!$F$5:$F$104,MIN(C21,100))-S21))/100*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C21,100))*(1-T21/100)-U21)),0)</f>
-        <v>14</v>
+        <f>ROUNDUP(H21/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C21,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C21,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C21,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C21,100))*(1-T21/100)-U21)),0)</f>
+        <v>4</v>
       </c>
       <c r="O21" s="3" t="s">
         <v>165</v>
@@ -11879,8 +11879,8 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="H22" s="25">
-        <f>ROUND(INDEX(เลเวล!$H$5:$H$104,C22)*F22*IF(D22="บอส",ตั้งค่า!$C$29,1),0)</f>
-        <v>495</v>
+        <f>ROUND(ตั้งค่า!$C$20*(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C22,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C22,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C22,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C22,100))*(1-T22/100)-U22))*F22*IF(D22="บอส",ตั้งค่า!$C$29,1),0)</f>
+        <v>137</v>
       </c>
       <c r="I22" s="25">
         <f>ROUND(INDEX(เลเวล!$F$5:$F$104,C22)*IF(D22="บอส",ตั้งค่า!$C$32,1),0)</f>
@@ -11903,8 +11903,8 @@
         <v>402</v>
       </c>
       <c r="N22" s="25">
-        <f>ROUNDUP(H22/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C22,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C22,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C22,100))/100)*MIN(95,MAX(5,80+INDEX(สายเลี้ยงตัว!$F$5:$F$104,MIN(C22,100))-S22))/100*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C22,100))*(1-T22/100)-U22)),0)</f>
-        <v>18</v>
+        <f>ROUNDUP(H22/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C22,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C22,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C22,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C22,100))*(1-T22/100)-U22)),0)</f>
+        <v>5</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>167</v>
@@ -11965,8 +11965,8 @@
         <v>1.35</v>
       </c>
       <c r="H23" s="25">
-        <f>ROUND(INDEX(เลเวล!$H$5:$H$104,C23)*F23*IF(D23="บอส",ตั้งค่า!$C$29,1),0)</f>
-        <v>830</v>
+        <f>ROUND(ตั้งค่า!$C$20*(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C23,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C23,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C23,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C23,100))*(1-T23/100)-U23))*F23*IF(D23="บอส",ตั้งค่า!$C$29,1),0)</f>
+        <v>201</v>
       </c>
       <c r="I23" s="25">
         <f>ROUND(INDEX(เลเวล!$F$5:$F$104,C23)*IF(D23="บอส",ตั้งค่า!$C$32,1),0)</f>
@@ -11989,8 +11989,8 @@
         <v>444</v>
       </c>
       <c r="N23" s="25">
-        <f>ROUNDUP(H23/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C23,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C23,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C23,100))/100)*MIN(95,MAX(5,80+INDEX(สายเลี้ยงตัว!$F$5:$F$104,MIN(C23,100))-S23))/100*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C23,100))*(1-T23/100)-U23)),0)</f>
-        <v>30</v>
+        <f>ROUNDUP(H23/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C23,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C23,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C23,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C23,100))*(1-T23/100)-U23)),0)</f>
+        <v>7</v>
       </c>
       <c r="O23" s="3" t="s">
         <v>169</v>
@@ -12051,8 +12051,8 @@
         <v>1</v>
       </c>
       <c r="H24" s="25">
-        <f>ROUND(INDEX(เลเวล!$H$5:$H$104,C24)*F24*IF(D24="บอส",ตั้งค่า!$C$29,1),0)</f>
-        <v>23840</v>
+        <f>ROUND(ตั้งค่า!$C$20*(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C24,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C24,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C24,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C24,100))*(1-T24/100)-U24))*F24*IF(D24="บอส",ตั้งค่า!$C$29,1),0)</f>
+        <v>6546</v>
       </c>
       <c r="I24" s="25">
         <f>ROUND(INDEX(เลเวล!$F$5:$F$104,C24)*IF(D24="บอส",ตั้งค่า!$C$32,1),0)</f>
@@ -12075,8 +12075,8 @@
         <v>9740</v>
       </c>
       <c r="N24" s="25">
-        <f>ROUNDUP(H24/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C24,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C24,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C24,100))/100)*MIN(95,MAX(5,80+INDEX(สายเลี้ยงตัว!$F$5:$F$104,MIN(C24,100))-S24))/100*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C24,100))*(1-T24/100)-U24)),0)</f>
-        <v>644</v>
+        <f>ROUNDUP(H24/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C24,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C24,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C24,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C24,100))*(1-T24/100)-U24)),0)</f>
+        <v>160</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>171</v>
@@ -12137,8 +12137,8 @@
         <v>1.05</v>
       </c>
       <c r="H25" s="25">
-        <f>ROUND(INDEX(เลเวล!$H$5:$H$104,C25)*F25*IF(D25="บอส",ตั้งค่า!$C$29,1),0)</f>
-        <v>680</v>
+        <f>ROUND(ตั้งค่า!$C$20*(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C25,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C25,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C25,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C25,100))*(1-T25/100)-U25))*F25*IF(D25="บอส",ตั้งค่า!$C$29,1),0)</f>
+        <v>164</v>
       </c>
       <c r="I25" s="25">
         <f>ROUND(INDEX(เลเวล!$F$5:$F$104,C25)*IF(D25="บอส",ตั้งค่า!$C$32,1),0)</f>
@@ -12161,8 +12161,8 @@
         <v>529</v>
       </c>
       <c r="N25" s="25">
-        <f>ROUNDUP(H25/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C25,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C25,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C25,100))/100)*MIN(95,MAX(5,80+INDEX(สายเลี้ยงตัว!$F$5:$F$104,MIN(C25,100))-S25))/100*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C25,100))*(1-T25/100)-U25)),0)</f>
-        <v>18</v>
+        <f>ROUNDUP(H25/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C25,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C25,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C25,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C25,100))*(1-T25/100)-U25)),0)</f>
+        <v>4</v>
       </c>
       <c r="O25" s="3" t="s">
         <v>174</v>
@@ -12223,8 +12223,8 @@
         <v>1</v>
       </c>
       <c r="H26" s="25">
-        <f>ROUND(INDEX(เลเวล!$H$5:$H$104,C26)*F26*IF(D26="บอส",ตั้งค่า!$C$29,1),0)</f>
-        <v>618</v>
+        <f>ROUND(ตั้งค่า!$C$20*(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C26,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C26,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C26,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C26,100))*(1-T26/100)-U26))*F26*IF(D26="บอส",ตั้งค่า!$C$29,1),0)</f>
+        <v>138</v>
       </c>
       <c r="I26" s="25">
         <f>ROUND(INDEX(เลเวล!$F$5:$F$104,C26)*IF(D26="บอส",ตั้งค่า!$C$32,1),0)</f>
@@ -12247,8 +12247,8 @@
         <v>571</v>
       </c>
       <c r="N26" s="25">
-        <f>ROUNDUP(H26/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C26,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C26,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C26,100))/100)*MIN(95,MAX(5,80+INDEX(สายเลี้ยงตัว!$F$5:$F$104,MIN(C26,100))-S26))/100*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C26,100))*(1-T26/100)-U26)),0)</f>
-        <v>16</v>
+        <f>ROUNDUP(H26/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C26,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C26,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C26,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C26,100))*(1-T26/100)-U26)),0)</f>
+        <v>4</v>
       </c>
       <c r="O26" s="3" t="s">
         <v>176</v>
@@ -12309,8 +12309,8 @@
         <v>1</v>
       </c>
       <c r="H27" s="25">
-        <f>ROUND(INDEX(เลเวล!$H$5:$H$104,C27)*F27*IF(D27="บอส",ตั้งค่า!$C$29,1),0)</f>
-        <v>838</v>
+        <f>ROUND(ตั้งค่า!$C$20*(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C27,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C27,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C27,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C27,100))*(1-T27/100)-U27))*F27*IF(D27="บอส",ตั้งค่า!$C$29,1),0)</f>
+        <v>175</v>
       </c>
       <c r="I27" s="25">
         <f>ROUND(INDEX(เลเวล!$F$5:$F$104,C27)*IF(D27="บอส",ตั้งค่า!$C$32,1),0)</f>
@@ -12333,8 +12333,8 @@
         <v>599</v>
       </c>
       <c r="N27" s="25">
-        <f>ROUNDUP(H27/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C27,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C27,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C27,100))/100)*MIN(95,MAX(5,80+INDEX(สายเลี้ยงตัว!$F$5:$F$104,MIN(C27,100))-S27))/100*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C27,100))*(1-T27/100)-U27)),0)</f>
-        <v>21</v>
+        <f>ROUNDUP(H27/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C27,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C27,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C27,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C27,100))*(1-T27/100)-U27)),0)</f>
+        <v>4</v>
       </c>
       <c r="O27" s="3" t="s">
         <v>178</v>
@@ -12395,8 +12395,8 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="H28" s="25">
-        <f>ROUND(INDEX(เลเวล!$H$5:$H$104,C28)*F28*IF(D28="บอส",ตั้งค่า!$C$29,1),0)</f>
-        <v>1136</v>
+        <f>ROUND(ตั้งค่า!$C$20*(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C28,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C28,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C28,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C28,100))*(1-T28/100)-U28))*F28*IF(D28="บอส",ตั้งค่า!$C$29,1),0)</f>
+        <v>257</v>
       </c>
       <c r="I28" s="25">
         <f>ROUND(INDEX(เลเวล!$F$5:$F$104,C28)*IF(D28="บอส",ตั้งค่า!$C$32,1),0)</f>
@@ -12419,8 +12419,8 @@
         <v>641</v>
       </c>
       <c r="N28" s="25">
-        <f>ROUNDUP(H28/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C28,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C28,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C28,100))/100)*MIN(95,MAX(5,80+INDEX(สายเลี้ยงตัว!$F$5:$F$104,MIN(C28,100))-S28))/100*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C28,100))*(1-T28/100)-U28)),0)</f>
-        <v>23</v>
+        <f>ROUNDUP(H28/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C28,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C28,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C28,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C28,100))*(1-T28/100)-U28)),0)</f>
+        <v>5</v>
       </c>
       <c r="O28" s="3" t="s">
         <v>180</v>
@@ -12481,8 +12481,8 @@
         <v>1.3</v>
       </c>
       <c r="H29" s="25">
-        <f>ROUND(INDEX(เลเวล!$H$5:$H$104,C29)*F29*IF(D29="บอส",ตั้งค่า!$C$29,1),0)</f>
-        <v>1652</v>
+        <f>ROUND(ตั้งค่า!$C$20*(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C29,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C29,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C29,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C29,100))*(1-T29/100)-U29))*F29*IF(D29="บอส",ตั้งค่า!$C$29,1),0)</f>
+        <v>320</v>
       </c>
       <c r="I29" s="25">
         <f>ROUND(INDEX(เลเวล!$F$5:$F$104,C29)*IF(D29="บอส",ตั้งค่า!$C$32,1),0)</f>
@@ -12505,8 +12505,8 @@
         <v>697</v>
       </c>
       <c r="N29" s="25">
-        <f>ROUNDUP(H29/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C29,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C29,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C29,100))/100)*MIN(95,MAX(5,80+INDEX(สายเลี้ยงตัว!$F$5:$F$104,MIN(C29,100))-S29))/100*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C29,100))*(1-T29/100)-U29)),0)</f>
-        <v>33</v>
+        <f>ROUNDUP(H29/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C29,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C29,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C29,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C29,100))*(1-T29/100)-U29)),0)</f>
+        <v>6</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>182</v>
@@ -12567,8 +12567,8 @@
         <v>1</v>
       </c>
       <c r="H30" s="25">
-        <f>ROUND(INDEX(เลเวล!$H$5:$H$104,C30)*F30*IF(D30="บอส",ตั้งค่า!$C$29,1),0)</f>
-        <v>53200</v>
+        <f>ROUND(ตั้งค่า!$C$20*(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C30,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C30,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C30,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C30,100))*(1-T30/100)-U30))*F30*IF(D30="บอส",ตั้งค่า!$C$29,1),0)</f>
+        <v>10408</v>
       </c>
       <c r="I30" s="25">
         <f>ROUND(INDEX(เลเวล!$F$5:$F$104,C30)*IF(D30="บอส",ตั้งค่า!$C$32,1),0)</f>
@@ -12591,8 +12591,8 @@
         <v>15340</v>
       </c>
       <c r="N30" s="25">
-        <f>ROUNDUP(H30/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C30,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C30,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C30,100))/100)*MIN(95,MAX(5,80+INDEX(สายเลี้ยงตัว!$F$5:$F$104,MIN(C30,100))-S30))/100*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C30,100))*(1-T30/100)-U30)),0)</f>
-        <v>859</v>
+        <f>ROUNDUP(H30/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C30,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C30,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C30,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C30,100))*(1-T30/100)-U30)),0)</f>
+        <v>160</v>
       </c>
       <c r="O30" s="3" t="s">
         <v>184</v>
@@ -12653,8 +12653,8 @@
         <v>1.1499999999999999</v>
       </c>
       <c r="H31" s="25">
-        <f>ROUND(INDEX(เลเวล!$H$5:$H$104,C31)*F31*IF(D31="บอส",ตั้งค่า!$C$29,1),0)</f>
-        <v>1927</v>
+        <f>ROUND(ตั้งค่า!$C$20*(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C31,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C31,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C31,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C31,100))*(1-T31/100)-U31))*F31*IF(D31="บอส",ตั้งค่า!$C$29,1),0)</f>
+        <v>345</v>
       </c>
       <c r="I31" s="25">
         <f>ROUND(INDEX(เลเวล!$F$5:$F$104,C31)*IF(D31="บอส",ตั้งค่า!$C$32,1),0)</f>
@@ -12677,8 +12677,8 @@
         <v>809</v>
       </c>
       <c r="N31" s="25">
-        <f>ROUNDUP(H31/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C31,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C31,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C31,100))/100)*MIN(95,MAX(5,80+INDEX(สายเลี้ยงตัว!$F$5:$F$104,MIN(C31,100))-S31))/100*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C31,100))*(1-T31/100)-U31)),0)</f>
-        <v>31</v>
+        <f>ROUNDUP(H31/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C31,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C31,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C31,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C31,100))*(1-T31/100)-U31)),0)</f>
+        <v>6</v>
       </c>
       <c r="O31" s="3" t="s">
         <v>187</v>
@@ -12739,8 +12739,8 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="H32" s="25">
-        <f>ROUND(INDEX(เลเวล!$H$5:$H$104,C32)*F32*IF(D32="บอส",ตั้งค่า!$C$29,1),0)</f>
-        <v>1973</v>
+        <f>ROUND(ตั้งค่า!$C$20*(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C32,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C32,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C32,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C32,100))*(1-T32/100)-U32))*F32*IF(D32="บอส",ตั้งค่า!$C$29,1),0)</f>
+        <v>320</v>
       </c>
       <c r="I32" s="25">
         <f>ROUND(INDEX(เลเวล!$F$5:$F$104,C32)*IF(D32="บอส",ตั้งค่า!$C$32,1),0)</f>
@@ -12763,8 +12763,8 @@
         <v>851</v>
       </c>
       <c r="N32" s="25">
-        <f>ROUNDUP(H32/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C32,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C32,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C32,100))/100)*MIN(95,MAX(5,80+INDEX(สายเลี้ยงตัว!$F$5:$F$104,MIN(C32,100))-S32))/100*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C32,100))*(1-T32/100)-U32)),0)</f>
-        <v>32</v>
+        <f>ROUNDUP(H32/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C32,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C32,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C32,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C32,100))*(1-T32/100)-U32)),0)</f>
+        <v>5</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>189</v>
@@ -12825,8 +12825,8 @@
         <v>1.05</v>
       </c>
       <c r="H33" s="25">
-        <f>ROUND(INDEX(เลเวล!$H$5:$H$104,C33)*F33*IF(D33="บอส",ตั้งค่า!$C$29,1),0)</f>
-        <v>1643</v>
+        <f>ROUND(ตั้งค่า!$C$20*(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C33,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C33,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C33,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C33,100))*(1-T33/100)-U33))*F33*IF(D33="บอส",ตั้งค่า!$C$29,1),0)</f>
+        <v>280</v>
       </c>
       <c r="I33" s="25">
         <f>ROUND(INDEX(เลเวล!$F$5:$F$104,C33)*IF(D33="บอส",ตั้งค่า!$C$32,1),0)</f>
@@ -12849,8 +12849,8 @@
         <v>893</v>
       </c>
       <c r="N33" s="25">
-        <f>ROUNDUP(H33/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C33,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C33,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C33,100))/100)*MIN(95,MAX(5,80+INDEX(สายเลี้ยงตัว!$F$5:$F$104,MIN(C33,100))-S33))/100*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C33,100))*(1-T33/100)-U33)),0)</f>
-        <v>23</v>
+        <f>ROUNDUP(H33/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C33,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C33,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C33,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C33,100))*(1-T33/100)-U33)),0)</f>
+        <v>4</v>
       </c>
       <c r="O33" s="3" t="s">
         <v>191</v>
@@ -12911,8 +12911,8 @@
         <v>1.25</v>
       </c>
       <c r="H34" s="25">
-        <f>ROUND(INDEX(เลเวล!$H$5:$H$104,C34)*F34*IF(D34="บอส",ตั้งค่า!$C$29,1),0)</f>
-        <v>3030</v>
+        <f>ROUND(ตั้งค่า!$C$20*(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C34,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C34,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C34,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C34,100))*(1-T34/100)-U34))*F34*IF(D34="บอส",ตั้งค่า!$C$29,1),0)</f>
+        <v>467</v>
       </c>
       <c r="I34" s="25">
         <f>ROUND(INDEX(เลเวล!$F$5:$F$104,C34)*IF(D34="บอส",ตั้งค่า!$C$32,1),0)</f>
@@ -12935,8 +12935,8 @@
         <v>935</v>
       </c>
       <c r="N34" s="25">
-        <f>ROUNDUP(H34/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C34,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C34,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C34,100))/100)*MIN(95,MAX(5,80+INDEX(สายเลี้ยงตัว!$F$5:$F$104,MIN(C34,100))-S34))/100*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C34,100))*(1-T34/100)-U34)),0)</f>
-        <v>41</v>
+        <f>ROUNDUP(H34/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C34,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C34,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C34,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C34,100))*(1-T34/100)-U34)),0)</f>
+        <v>6</v>
       </c>
       <c r="O34" s="3" t="s">
         <v>193</v>
@@ -12997,8 +12997,8 @@
         <v>1.1499999999999999</v>
       </c>
       <c r="H35" s="25">
-        <f>ROUND(INDEX(เลเวล!$H$5:$H$104,C35)*F35*IF(D35="บอส",ตั้งค่า!$C$29,1),0)</f>
-        <v>2774</v>
+        <f>ROUND(ตั้งค่า!$C$20*(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C35,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C35,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C35,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C35,100))*(1-T35/100)-U35))*F35*IF(D35="บอส",ตั้งค่า!$C$29,1),0)</f>
+        <v>381</v>
       </c>
       <c r="I35" s="25">
         <f>ROUND(INDEX(เลเวล!$F$5:$F$104,C35)*IF(D35="บอส",ตั้งค่า!$C$32,1),0)</f>
@@ -13021,8 +13021,8 @@
         <v>992</v>
       </c>
       <c r="N35" s="25">
-        <f>ROUNDUP(H35/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C35,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C35,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C35,100))/100)*MIN(95,MAX(5,80+INDEX(สายเลี้ยงตัว!$F$5:$F$104,MIN(C35,100))-S35))/100*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C35,100))*(1-T35/100)-U35)),0)</f>
-        <v>37</v>
+        <f>ROUNDUP(H35/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C35,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C35,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C35,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C35,100))*(1-T35/100)-U35)),0)</f>
+        <v>5</v>
       </c>
       <c r="O35" s="3" t="s">
         <v>195</v>
@@ -13083,8 +13083,8 @@
         <v>1</v>
       </c>
       <c r="H36" s="25">
-        <f>ROUND(INDEX(เลเวล!$H$5:$H$104,C36)*F36*IF(D36="บอส",ตั้งค่า!$C$29,1),0)</f>
-        <v>105240</v>
+        <f>ROUND(ตั้งค่า!$C$20*(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C36,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C36,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C36,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C36,100))*(1-T36/100)-U36))*F36*IF(D36="บอส",ตั้งค่า!$C$29,1),0)</f>
+        <v>14720</v>
       </c>
       <c r="I36" s="25">
         <f>ROUND(INDEX(เลเวล!$F$5:$F$104,C36)*IF(D36="บอส",ตั้งค่า!$C$32,1),0)</f>
@@ -13107,8 +13107,8 @@
         <v>20960</v>
       </c>
       <c r="N36" s="25">
-        <f>ROUNDUP(H36/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C36,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C36,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C36,100))/100)*MIN(95,MAX(5,80+INDEX(สายเลี้ยงตัว!$F$5:$F$104,MIN(C36,100))-S36))/100*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C36,100))*(1-T36/100)-U36)),0)</f>
-        <v>1201</v>
+        <f>ROUNDUP(H36/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C36,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C36,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C36,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C36,100))*(1-T36/100)-U36)),0)</f>
+        <v>160</v>
       </c>
       <c r="O36" s="3" t="s">
         <v>197</v>
@@ -13169,8 +13169,8 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="H37" s="25">
-        <f>ROUND(INDEX(เลเวล!$H$5:$H$104,C37)*F37*IF(D37="บอส",ตั้งค่า!$C$29,1),0)</f>
-        <v>3703</v>
+        <f>ROUND(ตั้งค่า!$C$20*(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C37,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C37,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C37,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C37,100))*(1-T37/100)-U37))*F37*IF(D37="บอส",ตั้งค่า!$C$29,1),0)</f>
+        <v>435</v>
       </c>
       <c r="I37" s="25">
         <f>ROUND(INDEX(เลเวล!$F$5:$F$104,C37)*IF(D37="บอส",ตั้งค่า!$C$32,1),0)</f>
@@ -13193,8 +13193,8 @@
         <v>1118</v>
       </c>
       <c r="N37" s="25">
-        <f>ROUNDUP(H37/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C37,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C37,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C37,100))/100)*MIN(95,MAX(5,80+INDEX(สายเลี้ยงตัว!$F$5:$F$104,MIN(C37,100))-S37))/100*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C37,100))*(1-T37/100)-U37)),0)</f>
-        <v>43</v>
+        <f>ROUNDUP(H37/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C37,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C37,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C37,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C37,100))*(1-T37/100)-U37)),0)</f>
+        <v>5</v>
       </c>
       <c r="O37" s="3" t="s">
         <v>200</v>
@@ -13255,8 +13255,8 @@
         <v>1.05</v>
       </c>
       <c r="H38" s="25">
-        <f>ROUND(INDEX(เลเวล!$H$5:$H$104,C38)*F38*IF(D38="บอส",ตั้งค่า!$C$29,1),0)</f>
-        <v>3850</v>
+        <f>ROUND(ตั้งค่า!$C$20*(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C38,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C38,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C38,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C38,100))*(1-T38/100)-U38))*F38*IF(D38="บอส",ตั้งค่า!$C$29,1),0)</f>
+        <v>457</v>
       </c>
       <c r="I38" s="25">
         <f>ROUND(INDEX(เลเวล!$F$5:$F$104,C38)*IF(D38="บอส",ตั้งค่า!$C$32,1),0)</f>
@@ -13279,8 +13279,8 @@
         <v>1174</v>
       </c>
       <c r="N38" s="25">
-        <f>ROUNDUP(H38/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C38,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C38,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C38,100))/100)*MIN(95,MAX(5,80+INDEX(สายเลี้ยงตัว!$F$5:$F$104,MIN(C38,100))-S38))/100*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C38,100))*(1-T38/100)-U38)),0)</f>
-        <v>39</v>
+        <f>ROUNDUP(H38/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C38,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C38,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C38,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C38,100))*(1-T38/100)-U38)),0)</f>
+        <v>5</v>
       </c>
       <c r="O38" s="3" t="s">
         <v>202</v>
@@ -13341,8 +13341,8 @@
         <v>1</v>
       </c>
       <c r="H39" s="25">
-        <f>ROUND(INDEX(เลเวล!$H$5:$H$104,C39)*F39*IF(D39="บอส",ตั้งค่า!$C$29,1),0)</f>
-        <v>3563</v>
+        <f>ROUND(ตั้งค่า!$C$20*(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C39,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C39,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C39,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C39,100))*(1-T39/100)-U39))*F39*IF(D39="บอส",ตั้งค่า!$C$29,1),0)</f>
+        <v>374</v>
       </c>
       <c r="I39" s="25">
         <f>ROUND(INDEX(เลเวล!$F$5:$F$104,C39)*IF(D39="บอส",ตั้งค่า!$C$32,1),0)</f>
@@ -13365,8 +13365,8 @@
         <v>1230</v>
       </c>
       <c r="N39" s="25">
-        <f>ROUNDUP(H39/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C39,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C39,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C39,100))/100)*MIN(95,MAX(5,80+INDEX(สายเลี้ยงตัว!$F$5:$F$104,MIN(C39,100))-S39))/100*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C39,100))*(1-T39/100)-U39)),0)</f>
-        <v>36</v>
+        <f>ROUNDUP(H39/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C39,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C39,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C39,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C39,100))*(1-T39/100)-U39)),0)</f>
+        <v>4</v>
       </c>
       <c r="O39" s="3" t="s">
         <v>204</v>
@@ -13427,8 +13427,8 @@
         <v>1.05</v>
       </c>
       <c r="H40" s="25">
-        <f>ROUND(INDEX(เลเวล!$H$5:$H$104,C40)*F40*IF(D40="บอส",ตั้งค่า!$C$29,1),0)</f>
-        <v>4468</v>
+        <f>ROUND(ตั้งค่า!$C$20*(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C40,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C40,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C40,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C40,100))*(1-T40/100)-U40))*F40*IF(D40="บอส",ตั้งค่า!$C$29,1),0)</f>
+        <v>475</v>
       </c>
       <c r="I40" s="25">
         <f>ROUND(INDEX(เลเวล!$F$5:$F$104,C40)*IF(D40="บอส",ตั้งค่า!$C$32,1),0)</f>
@@ -13451,8 +13451,8 @@
         <v>1286</v>
       </c>
       <c r="N40" s="25">
-        <f>ROUNDUP(H40/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C40,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C40,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C40,100))/100)*MIN(95,MAX(5,80+INDEX(สายเลี้ยงตัว!$F$5:$F$104,MIN(C40,100))-S40))/100*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C40,100))*(1-T40/100)-U40)),0)</f>
-        <v>40</v>
+        <f>ROUNDUP(H40/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C40,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C40,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C40,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C40,100))*(1-T40/100)-U40)),0)</f>
+        <v>5</v>
       </c>
       <c r="O40" s="3" t="s">
         <v>206</v>
@@ -13513,8 +13513,8 @@
         <v>1.2</v>
       </c>
       <c r="H41" s="25">
-        <f>ROUND(INDEX(เลเวล!$H$5:$H$104,C41)*F41*IF(D41="บอส",ตั้งค่า!$C$29,1),0)</f>
-        <v>6549</v>
+        <f>ROUND(ตั้งค่า!$C$20*(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C41,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C41,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C41,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C41,100))*(1-T41/100)-U41))*F41*IF(D41="บอส",ตั้งค่า!$C$29,1),0)</f>
+        <v>611</v>
       </c>
       <c r="I41" s="25">
         <f>ROUND(INDEX(เลเวล!$F$5:$F$104,C41)*IF(D41="บอส",ตั้งค่า!$C$32,1),0)</f>
@@ -13537,8 +13537,8 @@
         <v>1342</v>
       </c>
       <c r="N41" s="25">
-        <f>ROUNDUP(H41/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C41,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C41,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C41,100))/100)*MIN(95,MAX(5,80+INDEX(สายเลี้ยงตัว!$F$5:$F$104,MIN(C41,100))-S41))/100*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C41,100))*(1-T41/100)-U41)),0)</f>
-        <v>59</v>
+        <f>ROUNDUP(H41/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C41,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C41,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C41,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C41,100))*(1-T41/100)-U41)),0)</f>
+        <v>6</v>
       </c>
       <c r="O41" s="3"/>
       <c r="P41">
@@ -13597,8 +13597,8 @@
         <v>1</v>
       </c>
       <c r="H42" s="25">
-        <f>ROUND(INDEX(เลเวล!$H$5:$H$104,C42)*F42*IF(D42="บอส",ตั้งค่า!$C$29,1),0)</f>
-        <v>226640</v>
+        <f>ROUND(ตั้งค่า!$C$20*(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C42,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C42,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C42,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C42,100))*(1-T42/100)-U42))*F42*IF(D42="บอส",ตั้งค่า!$C$29,1),0)</f>
+        <v>20785</v>
       </c>
       <c r="I42" s="25">
         <f>ROUND(INDEX(เลเวล!$F$5:$F$104,C42)*IF(D42="บอส",ตั้งค่า!$C$32,1),0)</f>
@@ -13621,8 +13621,8 @@
         <v>27960</v>
       </c>
       <c r="N42" s="25">
-        <f>ROUNDUP(H42/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C42,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C42,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C42,100))/100)*MIN(95,MAX(5,80+INDEX(สายเลี้ยงตัว!$F$5:$F$104,MIN(C42,100))-S42))/100*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C42,100))*(1-T42/100)-U42)),0)</f>
-        <v>1830</v>
+        <f>ROUNDUP(H42/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C42,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C42,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C42,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C42,100))*(1-T42/100)-U42)),0)</f>
+        <v>160</v>
       </c>
       <c r="O42" s="3" t="s">
         <v>209</v>
@@ -13683,8 +13683,8 @@
         <v>1.1499999999999999</v>
       </c>
       <c r="H43" s="25">
-        <f>ROUND(INDEX(เลเวล!$H$5:$H$104,C43)*F43*IF(D43="บอส",ตั้งค่า!$C$29,1),0)</f>
-        <v>81</v>
+        <f>ROUND(ตั้งค่า!$C$20*(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C43,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C43,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C43,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C43,100))*(1-T43/100)-U43))*F43*IF(D43="บอส",ตั้งค่า!$C$29,1),0)</f>
+        <v>37</v>
       </c>
       <c r="I43" s="25">
         <f>ROUND(INDEX(เลเวล!$F$5:$F$104,C43)*IF(D43="บอส",ตั้งค่า!$C$32,1),0)</f>
@@ -13707,8 +13707,8 @@
         <v>22</v>
       </c>
       <c r="N43">
-        <f>ROUNDUP(H43/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C43,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C43,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C43,100))/100)*MIN(95,MAX(5,80+INDEX(สายเลี้ยงตัว!$F$5:$F$104,MIN(C43,100))-S43))/100*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C43,100))*(1-T43/100)-U43)),0)</f>
-        <v>14</v>
+        <f>ROUNDUP(H43/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C43,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C43,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C43,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C43,100))*(1-T43/100)-U43)),0)</f>
+        <v>6</v>
       </c>
       <c r="P43">
         <f t="shared" si="0"/>
@@ -13766,8 +13766,8 @@
         <v>1</v>
       </c>
       <c r="H44" s="25">
-        <f>ROUND(INDEX(เลเวล!$H$5:$H$104,C44)*F44*IF(D44="บอส",ตั้งค่า!$C$29,1),0)</f>
-        <v>136</v>
+        <f>ROUND(ตั้งค่า!$C$20*(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C44,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C44,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C44,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C44,100))*(1-T44/100)-U44))*F44*IF(D44="บอส",ตั้งค่า!$C$29,1),0)</f>
+        <v>47</v>
       </c>
       <c r="I44" s="25">
         <f>ROUND(INDEX(เลเวล!$F$5:$F$104,C44)*IF(D44="บอส",ตั้งค่า!$C$32,1),0)</f>
@@ -13790,8 +13790,8 @@
         <v>129</v>
       </c>
       <c r="N44">
-        <f>ROUNDUP(H44/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C44,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C44,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C44,100))/100)*MIN(95,MAX(5,80+INDEX(สายเลี้ยงตัว!$F$5:$F$104,MIN(C44,100))-S44))/100*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C44,100))*(1-T44/100)-U44)),0)</f>
-        <v>14</v>
+        <f>ROUNDUP(H44/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C44,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C44,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C44,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C44,100))*(1-T44/100)-U44)),0)</f>
+        <v>4</v>
       </c>
       <c r="P44">
         <f t="shared" si="0"/>
@@ -13849,8 +13849,8 @@
         <v>1</v>
       </c>
       <c r="H45" s="25">
-        <f>ROUND(INDEX(เลเวล!$H$5:$H$104,C45)*F45*IF(D45="บอส",ตั้งค่า!$C$29,1),0)</f>
-        <v>161</v>
+        <f>ROUND(ตั้งค่า!$C$20*(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C45,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C45,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C45,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C45,100))*(1-T45/100)-U45))*F45*IF(D45="บอส",ตั้งค่า!$C$29,1),0)</f>
+        <v>51</v>
       </c>
       <c r="I45" s="25">
         <f>ROUND(INDEX(เลเวล!$F$5:$F$104,C45)*IF(D45="บอส",ตั้งค่า!$C$32,1),0)</f>
@@ -13873,8 +13873,8 @@
         <v>159</v>
       </c>
       <c r="N45">
-        <f>ROUNDUP(H45/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C45,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C45,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C45,100))/100)*MIN(95,MAX(5,80+INDEX(สายเลี้ยงตัว!$F$5:$F$104,MIN(C45,100))-S45))/100*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C45,100))*(1-T45/100)-U45)),0)</f>
-        <v>15</v>
+        <f>ROUNDUP(H45/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C45,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C45,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C45,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C45,100))*(1-T45/100)-U45)),0)</f>
+        <v>4</v>
       </c>
       <c r="P45">
         <f t="shared" si="0"/>

--- a/balance/siam-legends-balance.xlsx
+++ b/balance/siam-legends-balance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kenio\Downloads\siam-legends-online (2)\siam-legends-online\balance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42D6F4DE-367B-4747-97BF-9481E4944414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E4E3A6A-AB8E-4143-B59D-A6974C96638F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -208,7 +208,7 @@
     <t>วินาที/ที</t>
   </si>
   <si>
-    <t>ตรงกับ PLAYER_ASPD_MS ในเกม</t>
+    <t>ไม่ใช้แล้ว: เวลาต่อการฆ่าใช้ความเร็วตีของสายตีจากชีตสายเลี้ยงตัว (คอลัมน์ ตีทุก ms)</t>
   </si>
   <si>
     <t>มอนปกติ (เทียบกับผู้เล่นเลเวลเท่ากัน)</t>
@@ -1591,301 +1591,301 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9.4444444444444445E-3</c:v>
+                  <c:v>1.2055555555555554E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.4555555555555553E-2</c:v>
+                  <c:v>2.8933333333333332E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.533333333333333E-2</c:v>
+                  <c:v>5.0623333333333333E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7.5555555555555542E-2</c:v>
+                  <c:v>8.1953333333333322E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.1171111111111111</c:v>
+                  <c:v>0.12290444444444444</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.17188888888888887</c:v>
+                  <c:v>0.17825777777777777</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.24177777777777776</c:v>
+                  <c:v>0.2480188888888889</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.33055555555555555</c:v>
+                  <c:v>0.3369833333333333</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.44011111111111112</c:v>
+                  <c:v>0.44758777777777775</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.57233333333333336</c:v>
+                  <c:v>0.57977111111111113</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.73099999999999998</c:v>
+                  <c:v>0.73831777777777785</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.9161111111111111</c:v>
+                  <c:v>0.92328888888888894</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.1333333333333333</c:v>
+                  <c:v>1.139288888888889</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.3826666666666667</c:v>
+                  <c:v>1.3887733333333334</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.667888888888889</c:v>
+                  <c:v>1.6741088888888889</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.9908888888888889</c:v>
+                  <c:v>1.995411111111111</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2.3535555555555554</c:v>
+                  <c:v>2.3573077777777778</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2.7577777777777777</c:v>
+                  <c:v>2.7621566666666668</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3.2073333333333331</c:v>
+                  <c:v>3.2121033333333333</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3.7041111111111107</c:v>
+                  <c:v>3.7096855555555557</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>4.25</c:v>
+                  <c:v>4.25725</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>4.8487777777777774</c:v>
+                  <c:v>4.8571400000000002</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>5.5023333333333326</c:v>
+                  <c:v>5.5120000000000005</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>6.2125555555555545</c:v>
+                  <c:v>6.2238888888888892</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>6.9832222222222216</c:v>
+                  <c:v>6.9947822222222227</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>7.8162222222222217</c:v>
+                  <c:v>7.827341111111112</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>8.7115555555555559</c:v>
+                  <c:v>8.7243100000000009</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>9.6748888888888889</c:v>
+                  <c:v>9.6876255555555559</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>10.708111111111112</c:v>
+                  <c:v>10.719608888888889</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>11.813111111111112</c:v>
+                  <c:v>11.824960000000001</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>12.991777777777779</c:v>
+                  <c:v>13.003060000000001</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>14.247888888888889</c:v>
+                  <c:v>14.259113333333335</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>15.581444444444445</c:v>
+                  <c:v>15.593046666666668</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>16.998111111111111</c:v>
+                  <c:v>17.007824444444445</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>18.497888888888887</c:v>
+                  <c:v>18.507501111111111</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>20.084555555555553</c:v>
+                  <c:v>20.094372222222223</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>21.758111111111109</c:v>
+                  <c:v>21.769945555555555</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>23.524222222222221</c:v>
+                  <c:v>23.537251111111111</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>25.384777777777778</c:v>
+                  <c:v>25.397073333333331</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>27.339777777777776</c:v>
+                  <c:v>27.35324</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>29.394888888888886</c:v>
+                  <c:v>29.405660000000001</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>31.548222222222218</c:v>
+                  <c:v>31.56134888888889</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>33.80544444444444</c:v>
+                  <c:v>33.81914888888889</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>36.16844444444444</c:v>
+                  <c:v>36.184704444444442</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>38.640999999999998</c:v>
+                  <c:v>38.657913333333333</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>41.225000000000001</c:v>
+                  <c:v>41.241036666666666</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>43.920444444444449</c:v>
+                  <c:v>43.936332222222219</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>46.731111111111119</c:v>
+                  <c:v>46.747376666666661</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>49.658888888888896</c:v>
+                  <c:v>49.676136666666658</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>52.707555555555565</c:v>
+                  <c:v>52.726179999999992</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>55.880888888888897</c:v>
+                  <c:v>55.897391111111105</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>59.177000000000007</c:v>
+                  <c:v>59.194367777777771</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>62.601555555555564</c:v>
+                  <c:v>62.616989999999994</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>66.154555555555561</c:v>
+                  <c:v>66.171523333333326</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>69.841666666666669</c:v>
+                  <c:v>69.859196666666662</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>73.664777777777786</c:v>
+                  <c:v>73.681557777777769</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>77.622000000000014</c:v>
+                  <c:v>77.640828888888876</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>81.720888888888908</c:v>
+                  <c:v>81.741578888888881</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>85.963333333333352</c:v>
+                  <c:v>85.981323333333322</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>90.347444444444463</c:v>
+                  <c:v>90.36724333333332</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>94.880777777777794</c:v>
+                  <c:v>94.90120222222221</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>99.565222222222232</c:v>
+                  <c:v>99.585276666666658</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>104.39888888888891</c:v>
+                  <c:v>104.41952111111111</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>109.38744444444445</c:v>
+                  <c:v>109.40613444444445</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>114.5308888888889</c:v>
+                  <c:v>114.54965444444444</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>119.8348888888889</c:v>
+                  <c:v>119.85443444444444</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>125.30133333333335</c:v>
+                  <c:v>125.32041777777776</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>130.93022222222223</c:v>
+                  <c:v>130.94978666666665</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>136.72722222222222</c:v>
+                  <c:v>136.74471999999997</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>142.69422222222224</c:v>
+                  <c:v>142.70972888888886</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>148.82933333333335</c:v>
+                  <c:v>148.84523333333331</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>155.14011111111114</c:v>
+                  <c:v>155.15689999999998</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>161.62844444444448</c:v>
+                  <c:v>161.6451422222222</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>168.29244444444447</c:v>
+                  <c:v>168.31211999999999</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>175.1396666666667</c:v>
+                  <c:v>175.15765999999999</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>182.17200000000003</c:v>
+                  <c:v>182.18624666666665</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>189.38755555555559</c:v>
+                  <c:v>189.40356666666665</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>196.79200000000003</c:v>
+                  <c:v>196.80813555555554</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>204.38533333333336</c:v>
+                  <c:v>204.40339999999998</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>212.17322222222225</c:v>
+                  <c:v>212.1926133333333</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>220.15755555555558</c:v>
+                  <c:v>220.17790999999997</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>228.33833333333337</c:v>
+                  <c:v>228.35909888888887</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>236.72122222222225</c:v>
+                  <c:v>236.74125888888886</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>245.30811111111115</c:v>
+                  <c:v>245.32578555555554</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>254.09711111111113</c:v>
+                  <c:v>254.11711666666665</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>263.09577777777781</c:v>
+                  <c:v>263.11505</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>272.30600000000004</c:v>
+                  <c:v>272.32380000000001</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>281.7258888888889</c:v>
+                  <c:v>281.74347999999998</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>291.363</c:v>
+                  <c:v>291.37851333333333</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>301.21922222222224</c:v>
+                  <c:v>301.23320444444443</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>311.29077777777781</c:v>
+                  <c:v>311.30964888888889</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>321.58711111111114</c:v>
+                  <c:v>321.60531888888886</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>332.11011111111117</c:v>
+                  <c:v>332.12692555555554</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>342.85600000000005</c:v>
+                  <c:v>342.87599222222224</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>353.83422222222225</c:v>
+                  <c:v>353.85504777777777</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>365.04666666666668</c:v>
+                  <c:v>365.06465888888886</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>376.48955555555557</c:v>
+                  <c:v>376.50852999999995</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>388.17044444444446</c:v>
+                  <c:v>388.19103666666661</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>400.09311111111111</c:v>
+                  <c:v>400.11194333333327</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1893,7 +1893,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-6676-4525-BF4E-3358D49622A5}"/>
+              <c16:uniqueId val="{00000000-1FF2-4680-B170-1F166DABB7BE}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="C35" s="20">
         <f>INDEX(เลเวล!$R$5:$R$104,10)*60</f>
-        <v>26.406666666666666</v>
+        <v>26.855266666666665</v>
       </c>
       <c r="D35" s="21" t="s">
         <v>32</v>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="C36" s="22">
         <f>INDEX(เลเวล!$R$5:$R$104,20)</f>
-        <v>3.2073333333333331</v>
+        <v>3.2121033333333333</v>
       </c>
       <c r="D36" s="21" t="s">
         <v>27</v>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="C37" s="22">
         <f>INDEX(เลเวล!$R$5:$R$104,30)</f>
-        <v>10.708111111111112</v>
+        <v>10.719608888888889</v>
       </c>
       <c r="D37" s="21" t="s">
         <v>27</v>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="C38" s="22">
         <f>INDEX(เลเวล!$R$5:$R$104,50)</f>
-        <v>49.658888888888896</v>
+        <v>49.676136666666658</v>
       </c>
       <c r="D38" s="21" t="s">
         <v>27</v>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="C39" s="22">
         <f>INDEX(เลเวล!$R$5:$R$104,C6)</f>
-        <v>400.09311111111111</v>
+        <v>400.11194333333327</v>
       </c>
       <c r="D39" s="21" t="s">
         <v>27</v>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="C40" s="20">
         <f>C39/2</f>
-        <v>200.04655555555556</v>
+        <v>200.05597166666664</v>
       </c>
       <c r="D40" s="21" t="s">
         <v>83</v>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="C42" s="23">
         <f>INDEX(เลเวล!$P$5:$P$104,50)</f>
-        <v>1614</v>
+        <v>1293</v>
       </c>
       <c r="D42" s="21" t="s">
         <v>85</v>
@@ -3025,8 +3025,8 @@
         <v>8</v>
       </c>
       <c r="J5" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A5,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.68</v>
       </c>
       <c r="K5" s="27">
         <f>ตั้งค่า!$C$10*A5^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="L5" s="25">
         <f t="shared" ref="L5:L36" si="1">K5*60/J5</f>
-        <v>5.9374573401768194</v>
+        <v>4.6514642757145594</v>
       </c>
       <c r="M5" s="25">
         <f t="shared" ref="M5:M36" si="2">MAX(1,ROUND(B5/L5,0))</f>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="Q5" s="27">
         <f t="shared" ref="Q5:Q36" si="4">P5*J5/60</f>
-        <v>0.56666666666666665</v>
+        <v>0.72333333333333327</v>
       </c>
       <c r="R5" s="26">
         <f>0</f>
@@ -3098,8 +3098,8 @@
         <v>9</v>
       </c>
       <c r="J6" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A6,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.68</v>
       </c>
       <c r="K6" s="27">
         <f>ตั้งค่า!$C$10*A6^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -3107,31 +3107,31 @@
       </c>
       <c r="L6" s="25">
         <f t="shared" si="1"/>
-        <v>7.86747641953081</v>
+        <v>6.1634607894941835</v>
       </c>
       <c r="M6" s="25">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="N6" s="25">
         <f>MAX(1,ROUND(M6*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O6" s="25">
         <f>MAX(1,ROUND(M6*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P6" s="25">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q6" s="27">
         <f t="shared" si="4"/>
-        <v>0.90666666666666662</v>
+        <v>1.0126666666666666</v>
       </c>
       <c r="R6" s="26">
         <f t="shared" ref="R6:R37" si="6">R5+Q5/60</f>
-        <v>9.4444444444444445E-3</v>
+        <v>1.2055555555555554E-2</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -3171,8 +3171,8 @@
         <v>10</v>
       </c>
       <c r="J7" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A7,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.6760000000000002</v>
       </c>
       <c r="K7" s="27">
         <f>ตั้งค่า!$C$10*A7^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -3180,31 +3180,31 @@
       </c>
       <c r="L7" s="25">
         <f t="shared" si="1"/>
-        <v>11.08417488512079</v>
+        <v>8.6874584161850361</v>
       </c>
       <c r="M7" s="25">
         <f t="shared" si="2"/>
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="N7" s="25">
         <f>MAX(1,ROUND(M7*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="O7" s="25">
         <f>MAX(1,ROUND(M7*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="P7" s="25">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q7" s="27">
         <f t="shared" si="4"/>
-        <v>1.2466666666666666</v>
+        <v>1.3014000000000001</v>
       </c>
       <c r="R7" s="26">
         <f t="shared" si="6"/>
-        <v>2.4555555555555553E-2</v>
+        <v>2.8933333333333332E-2</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -3244,8 +3244,8 @@
         <v>11</v>
       </c>
       <c r="J8" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A8,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.6760000000000002</v>
       </c>
       <c r="K8" s="27">
         <f>ตั้งค่า!$C$10*A8^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -3253,31 +3253,31 @@
       </c>
       <c r="L8" s="25">
         <f t="shared" si="1"/>
-        <v>15.587552736946765</v>
+        <v>12.217076833937067</v>
       </c>
       <c r="M8" s="25">
         <f t="shared" si="2"/>
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="N8" s="25">
         <f>MAX(1,ROUND(M8*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="O8" s="25">
         <f>MAX(1,ROUND(M8*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="P8" s="25">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Q8" s="27">
         <f t="shared" si="4"/>
-        <v>1.8133333333333332</v>
+        <v>1.8797999999999999</v>
       </c>
       <c r="R8" s="26">
         <f t="shared" si="6"/>
-        <v>4.533333333333333E-2</v>
+        <v>5.0623333333333333E-2</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -3317,8 +3317,8 @@
         <v>12</v>
       </c>
       <c r="J9" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A9,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.6720000000000006</v>
       </c>
       <c r="K9" s="27">
         <f>ตั้งค่า!$C$10*A9^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -3326,31 +3326,31 @@
       </c>
       <c r="L9" s="25">
         <f t="shared" si="1"/>
-        <v>21.377609975008735</v>
+        <v>16.762886050514226</v>
       </c>
       <c r="M9" s="25">
         <f t="shared" si="2"/>
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="N9" s="25">
         <f>MAX(1,ROUND(M9*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="O9" s="25">
         <f>MAX(1,ROUND(M9*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="P9" s="25">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="Q9" s="27">
         <f t="shared" si="4"/>
-        <v>2.4933333333333332</v>
+        <v>2.457066666666667</v>
       </c>
       <c r="R9" s="26">
         <f t="shared" si="6"/>
-        <v>7.5555555555555542E-2</v>
+        <v>8.1953333333333322E-2</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -3390,8 +3390,8 @@
         <v>14</v>
       </c>
       <c r="J10" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A10,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.6639999999999997</v>
       </c>
       <c r="K10" s="27">
         <f>ตั้งค่า!$C$10*A10^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -3399,31 +3399,31 @@
       </c>
       <c r="L10" s="25">
         <f t="shared" si="1"/>
-        <v>28.454346599306696</v>
+        <v>22.332589667045884</v>
       </c>
       <c r="M10" s="25">
         <f t="shared" si="2"/>
-        <v>114</v>
+        <v>145</v>
       </c>
       <c r="N10" s="25">
         <f>MAX(1,ROUND(M10*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="O10" s="25">
         <f>MAX(1,ROUND(M10*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="P10" s="25">
         <f t="shared" si="3"/>
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="Q10" s="27">
         <f t="shared" si="4"/>
-        <v>3.2866666666666666</v>
+        <v>3.3211999999999997</v>
       </c>
       <c r="R10" s="26">
         <f t="shared" si="6"/>
-        <v>0.1171111111111111</v>
+        <v>0.12290444444444444</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -3463,8 +3463,8 @@
         <v>15</v>
       </c>
       <c r="J11" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A11,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.66</v>
       </c>
       <c r="K11" s="27">
         <f>ตั้งค่า!$C$10*A11^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -3472,31 +3472,31 @@
       </c>
       <c r="L11" s="25">
         <f t="shared" si="1"/>
-        <v>36.817762609840649</v>
+        <v>28.910021448835611</v>
       </c>
       <c r="M11" s="25">
         <f t="shared" si="2"/>
-        <v>140</v>
+        <v>178</v>
       </c>
       <c r="N11" s="25">
         <f>MAX(1,ROUND(M11*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="O11" s="25">
         <f>MAX(1,ROUND(M11*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="P11" s="25">
         <f t="shared" si="3"/>
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="Q11" s="27">
         <f t="shared" si="4"/>
-        <v>4.1933333333333334</v>
+        <v>4.1856666666666671</v>
       </c>
       <c r="R11" s="26">
         <f t="shared" si="6"/>
-        <v>0.17188888888888887</v>
+        <v>0.17825777777777777</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -3536,8 +3536,8 @@
         <v>16</v>
       </c>
       <c r="J12" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A12,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.6559999999999988</v>
       </c>
       <c r="K12" s="27">
         <f>ตั้งค่า!$C$10*A12^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -3545,31 +3545,31 @@
       </c>
       <c r="L12" s="25">
         <f t="shared" si="1"/>
-        <v>46.467858006610591</v>
+        <v>36.504324681718124</v>
       </c>
       <c r="M12" s="25">
         <f t="shared" si="2"/>
-        <v>165</v>
+        <v>210</v>
       </c>
       <c r="N12" s="25">
         <f>MAX(1,ROUND(M12*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="O12" s="25">
         <f>MAX(1,ROUND(M12*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="P12" s="25">
         <f t="shared" si="3"/>
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="Q12" s="27">
         <f t="shared" si="4"/>
-        <v>5.3266666666666662</v>
+        <v>5.3378666666666659</v>
       </c>
       <c r="R12" s="26">
         <f t="shared" si="6"/>
-        <v>0.24177777777777776</v>
+        <v>0.2480188888888889</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -3609,8 +3609,8 @@
         <v>17</v>
       </c>
       <c r="J13" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A13,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.6559999999999988</v>
       </c>
       <c r="K13" s="27">
         <f>ตั้งค่า!$C$10*A13^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -3618,31 +3618,31 @@
       </c>
       <c r="L13" s="25">
         <f t="shared" si="1"/>
-        <v>57.404632789616535</v>
+        <v>45.096060879088782</v>
       </c>
       <c r="M13" s="25">
         <f t="shared" si="2"/>
-        <v>190</v>
+        <v>242</v>
       </c>
       <c r="N13" s="25">
         <f>MAX(1,ROUND(M13*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="O13" s="25">
         <f>MAX(1,ROUND(M13*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>114</v>
+        <v>145</v>
       </c>
       <c r="P13" s="25">
         <f t="shared" si="3"/>
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="Q13" s="27">
         <f t="shared" si="4"/>
-        <v>6.5733333333333333</v>
+        <v>6.6362666666666659</v>
       </c>
       <c r="R13" s="26">
         <f t="shared" si="6"/>
-        <v>0.33055555555555555</v>
+        <v>0.3369833333333333</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -3682,8 +3682,8 @@
         <v>18</v>
       </c>
       <c r="J14" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A14,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.652000000000001</v>
       </c>
       <c r="K14" s="27">
         <f>ตั้งค่า!$C$10*A14^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -3691,31 +3691,31 @@
       </c>
       <c r="L14" s="25">
         <f t="shared" si="1"/>
-        <v>69.628086958858461</v>
+        <v>54.72387786872833</v>
       </c>
       <c r="M14" s="25">
         <f t="shared" si="2"/>
-        <v>215</v>
+        <v>274</v>
       </c>
       <c r="N14" s="25">
         <f>MAX(1,ROUND(M14*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="O14" s="25">
         <f>MAX(1,ROUND(M14*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>129</v>
+        <v>164</v>
       </c>
       <c r="P14" s="25">
         <f t="shared" si="3"/>
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="Q14" s="27">
         <f t="shared" si="4"/>
-        <v>7.9333333333333336</v>
+        <v>7.9310000000000009</v>
       </c>
       <c r="R14" s="26">
         <f t="shared" si="6"/>
-        <v>0.44011111111111112</v>
+        <v>0.44758777777777775</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -3755,8 +3755,8 @@
         <v>19</v>
       </c>
       <c r="J15" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A15,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.6479999999999997</v>
       </c>
       <c r="K15" s="27">
         <f>ตั้งค่า!$C$10*A15^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -3764,31 +3764,31 @@
       </c>
       <c r="L15" s="25">
         <f t="shared" si="1"/>
-        <v>83.138220514336382</v>
+        <v>65.37232880405729</v>
       </c>
       <c r="M15" s="25">
         <f t="shared" si="2"/>
-        <v>240</v>
+        <v>305</v>
       </c>
       <c r="N15" s="25">
         <f>MAX(1,ROUND(M15*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>96</v>
+        <v>122</v>
       </c>
       <c r="O15" s="25">
         <f>MAX(1,ROUND(M15*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>144</v>
+        <v>183</v>
       </c>
       <c r="P15" s="25">
         <f t="shared" si="3"/>
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="Q15" s="27">
         <f t="shared" si="4"/>
-        <v>9.52</v>
+        <v>9.5128000000000004</v>
       </c>
       <c r="R15" s="26">
         <f t="shared" si="6"/>
-        <v>0.57233333333333336</v>
+        <v>0.57977111111111113</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -3828,8 +3828,8 @@
         <v>21</v>
       </c>
       <c r="J16" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A16,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.6479999999999997</v>
       </c>
       <c r="K16" s="27">
         <f>ตั้งค่า!$C$10*A16^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -3837,31 +3837,31 @@
       </c>
       <c r="L16" s="25">
         <f t="shared" si="1"/>
-        <v>97.935033456050292</v>
+        <v>77.007195594489133</v>
       </c>
       <c r="M16" s="25">
         <f t="shared" si="2"/>
-        <v>265</v>
+        <v>337</v>
       </c>
       <c r="N16" s="25">
         <f>MAX(1,ROUND(M16*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="O16" s="25">
         <f>MAX(1,ROUND(M16*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>159</v>
+        <v>202</v>
       </c>
       <c r="P16" s="25">
         <f t="shared" si="3"/>
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="Q16" s="27">
         <f t="shared" si="4"/>
-        <v>11.106666666666666</v>
+        <v>11.098266666666666</v>
       </c>
       <c r="R16" s="26">
         <f t="shared" si="6"/>
-        <v>0.73099999999999998</v>
+        <v>0.73831777777777785</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -3901,8 +3901,8 @@
         <v>22</v>
       </c>
       <c r="J17" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A17,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.64</v>
       </c>
       <c r="K17" s="27">
         <f>ตั้งค่า!$C$10*A17^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -3910,31 +3910,31 @@
       </c>
       <c r="L17" s="25">
         <f t="shared" si="1"/>
-        <v>114.01852578400022</v>
+        <v>89.736802700370532</v>
       </c>
       <c r="M17" s="25">
         <f t="shared" si="2"/>
-        <v>289</v>
+        <v>367</v>
       </c>
       <c r="N17" s="25">
         <f>MAX(1,ROUND(M17*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>116</v>
+        <v>147</v>
       </c>
       <c r="O17" s="25">
         <f>MAX(1,ROUND(M17*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>173</v>
+        <v>220</v>
       </c>
       <c r="P17" s="25">
         <f t="shared" si="3"/>
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="Q17" s="27">
         <f t="shared" si="4"/>
-        <v>13.033333333333333</v>
+        <v>12.96</v>
       </c>
       <c r="R17" s="26">
         <f t="shared" si="6"/>
-        <v>0.9161111111111111</v>
+        <v>0.92328888888888894</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -3974,8 +3974,8 @@
         <v>23</v>
       </c>
       <c r="J18" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A18,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.6359999999999992</v>
       </c>
       <c r="K18" s="27">
         <f>ตั้งค่า!$C$10*A18^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -3983,31 +3983,31 @@
       </c>
       <c r="L18" s="25">
         <f t="shared" si="1"/>
-        <v>131.38869749818613</v>
+        <v>103.45566732140641</v>
       </c>
       <c r="M18" s="25">
         <f t="shared" si="2"/>
-        <v>313</v>
+        <v>398</v>
       </c>
       <c r="N18" s="25">
         <f>MAX(1,ROUND(M18*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>125</v>
+        <v>159</v>
       </c>
       <c r="O18" s="25">
         <f>MAX(1,ROUND(M18*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>188</v>
+        <v>239</v>
       </c>
       <c r="P18" s="25">
         <f t="shared" si="3"/>
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="Q18" s="27">
         <f t="shared" si="4"/>
-        <v>14.96</v>
+        <v>14.969066666666665</v>
       </c>
       <c r="R18" s="26">
         <f t="shared" si="6"/>
-        <v>1.1333333333333333</v>
+        <v>1.139288888888889</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -4047,8 +4047,8 @@
         <v>25</v>
       </c>
       <c r="J19" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A19,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.6319999999999997</v>
       </c>
       <c r="K19" s="27">
         <f>ตั้งค่า!$C$10*A19^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -4056,31 +4056,31 @@
       </c>
       <c r="L19" s="25">
         <f t="shared" si="1"/>
-        <v>150.04554859860804</v>
+        <v>118.20084922040485</v>
       </c>
       <c r="M19" s="25">
         <f t="shared" si="2"/>
-        <v>337</v>
+        <v>428</v>
       </c>
       <c r="N19" s="25">
         <f>MAX(1,ROUND(M19*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>135</v>
+        <v>171</v>
       </c>
       <c r="O19" s="25">
         <f>MAX(1,ROUND(M19*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>202</v>
+        <v>257</v>
       </c>
       <c r="P19" s="25">
         <f t="shared" si="3"/>
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="Q19" s="27">
         <f t="shared" si="4"/>
-        <v>17.113333333333333</v>
+        <v>17.120133333333332</v>
       </c>
       <c r="R19" s="26">
         <f t="shared" si="6"/>
-        <v>1.3826666666666667</v>
+        <v>1.3887733333333334</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -4120,8 +4120,8 @@
         <v>26</v>
       </c>
       <c r="J20" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A20,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.6319999999999997</v>
       </c>
       <c r="K20" s="27">
         <f>ตั้งค่า!$C$10*A20^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -4129,31 +4129,31 @@
       </c>
       <c r="L20" s="25">
         <f t="shared" si="1"/>
-        <v>169.98907908526593</v>
+        <v>133.91169344066361</v>
       </c>
       <c r="M20" s="25">
         <f t="shared" si="2"/>
-        <v>361</v>
+        <v>459</v>
       </c>
       <c r="N20" s="25">
         <f>MAX(1,ROUND(M20*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>144</v>
+        <v>184</v>
       </c>
       <c r="O20" s="25">
         <f>MAX(1,ROUND(M20*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="P20" s="25">
         <f t="shared" si="3"/>
-        <v>171</v>
+        <v>134</v>
       </c>
       <c r="Q20" s="27">
         <f t="shared" si="4"/>
-        <v>19.38</v>
+        <v>19.278133333333333</v>
       </c>
       <c r="R20" s="26">
         <f t="shared" si="6"/>
-        <v>1.667888888888889</v>
+        <v>1.6741088888888889</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -4193,8 +4193,8 @@
         <v>28</v>
       </c>
       <c r="J21" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A21,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.6280000000000001</v>
       </c>
       <c r="K21" s="27">
         <f>ตั้งค่า!$C$10*A21^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -4202,31 +4202,31 @@
       </c>
       <c r="L21" s="25">
         <f t="shared" si="1"/>
-        <v>191.21928895815981</v>
+        <v>150.70597646215654</v>
       </c>
       <c r="M21" s="25">
         <f t="shared" si="2"/>
-        <v>385</v>
+        <v>489</v>
       </c>
       <c r="N21" s="25">
         <f>MAX(1,ROUND(M21*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>154</v>
+        <v>196</v>
       </c>
       <c r="O21" s="25">
         <f>MAX(1,ROUND(M21*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>231</v>
+        <v>293</v>
       </c>
       <c r="P21" s="25">
         <f t="shared" si="3"/>
-        <v>192</v>
+        <v>151</v>
       </c>
       <c r="Q21" s="27">
         <f t="shared" si="4"/>
-        <v>21.759999999999998</v>
+        <v>21.713799999999999</v>
       </c>
       <c r="R21" s="26">
         <f t="shared" si="6"/>
-        <v>1.9908888888888889</v>
+        <v>1.995411111111111</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -4266,8 +4266,8 @@
         <v>29</v>
       </c>
       <c r="J22" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A22,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.6239999999999988</v>
       </c>
       <c r="K22" s="27">
         <f>ตั้งค่า!$C$10*A22^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -4275,31 +4275,31 @@
       </c>
       <c r="L22" s="25">
         <f t="shared" si="1"/>
-        <v>213.73617821728971</v>
+        <v>168.53038171122103</v>
       </c>
       <c r="M22" s="25">
         <f t="shared" si="2"/>
-        <v>409</v>
+        <v>519</v>
       </c>
       <c r="N22" s="25">
         <f>MAX(1,ROUND(M22*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>164</v>
+        <v>208</v>
       </c>
       <c r="O22" s="25">
         <f>MAX(1,ROUND(M22*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>245</v>
+        <v>311</v>
       </c>
       <c r="P22" s="25">
         <f t="shared" si="3"/>
-        <v>214</v>
+        <v>169</v>
       </c>
       <c r="Q22" s="27">
         <f t="shared" si="4"/>
-        <v>24.253333333333334</v>
+        <v>24.290933333333331</v>
       </c>
       <c r="R22" s="26">
         <f t="shared" si="6"/>
-        <v>2.3535555555555554</v>
+        <v>2.3573077777777778</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -4339,8 +4339,8 @@
         <v>31</v>
       </c>
       <c r="J23" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A23,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.6159999999999997</v>
       </c>
       <c r="K23" s="27">
         <f>ตั้งค่า!$C$10*A23^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -4348,31 +4348,31 @@
       </c>
       <c r="L23" s="25">
         <f t="shared" si="1"/>
-        <v>237.53974686265556</v>
+        <v>187.47333782103735</v>
       </c>
       <c r="M23" s="25">
         <f t="shared" si="2"/>
-        <v>433</v>
+        <v>549</v>
       </c>
       <c r="N23" s="25">
         <f>MAX(1,ROUND(M23*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>173</v>
+        <v>220</v>
       </c>
       <c r="O23" s="25">
         <f>MAX(1,ROUND(M23*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>260</v>
+        <v>329</v>
       </c>
       <c r="P23" s="25">
         <f t="shared" si="3"/>
-        <v>238</v>
+        <v>188</v>
       </c>
       <c r="Q23" s="27">
         <f t="shared" si="4"/>
-        <v>26.973333333333333</v>
+        <v>26.9968</v>
       </c>
       <c r="R23" s="26">
         <f t="shared" si="6"/>
-        <v>2.7577777777777777</v>
+        <v>2.7621566666666668</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -4412,8 +4412,8 @@
         <v>32</v>
       </c>
       <c r="J24" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A24,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.6120000000000001</v>
       </c>
       <c r="K24" s="27">
         <f>ตั้งค่า!$C$10*A24^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -4421,31 +4421,31 @@
       </c>
       <c r="L24" s="25">
         <f t="shared" si="1"/>
-        <v>262.62999489425744</v>
+        <v>207.37157051567004</v>
       </c>
       <c r="M24" s="25">
         <f t="shared" si="2"/>
-        <v>457</v>
+        <v>579</v>
       </c>
       <c r="N24" s="25">
         <f>MAX(1,ROUND(M24*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>183</v>
+        <v>232</v>
       </c>
       <c r="O24" s="25">
         <f>MAX(1,ROUND(M24*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>274</v>
+        <v>347</v>
       </c>
       <c r="P24" s="25">
         <f t="shared" si="3"/>
-        <v>263</v>
+        <v>208</v>
       </c>
       <c r="Q24" s="27">
         <f t="shared" si="4"/>
-        <v>29.806666666666665</v>
+        <v>29.854933333333335</v>
       </c>
       <c r="R24" s="26">
         <f t="shared" si="6"/>
-        <v>3.2073333333333331</v>
+        <v>3.2121033333333333</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -4485,8 +4485,8 @@
         <v>34</v>
       </c>
       <c r="J25" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A25,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.6080000000000005</v>
       </c>
       <c r="K25" s="27">
         <f>ตั้งค่า!$C$10*A25^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -4494,31 +4494,31 @@
       </c>
       <c r="L25" s="25">
         <f t="shared" si="1"/>
-        <v>289.00692231209524</v>
+        <v>228.30472487479642</v>
       </c>
       <c r="M25" s="25">
         <f t="shared" si="2"/>
-        <v>481</v>
+        <v>608</v>
       </c>
       <c r="N25" s="25">
         <f>MAX(1,ROUND(M25*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>192</v>
+        <v>243</v>
       </c>
       <c r="O25" s="25">
         <f>MAX(1,ROUND(M25*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>289</v>
+        <v>365</v>
       </c>
       <c r="P25" s="25">
         <f t="shared" si="3"/>
-        <v>289</v>
+        <v>229</v>
       </c>
       <c r="Q25" s="27">
         <f t="shared" si="4"/>
-        <v>32.753333333333337</v>
+        <v>32.853866666666669</v>
       </c>
       <c r="R25" s="26">
         <f t="shared" si="6"/>
-        <v>3.7041111111111107</v>
+        <v>3.7096855555555557</v>
       </c>
     </row>
     <row r="26" spans="1:18">
@@ -4558,8 +4558,8 @@
         <v>35</v>
       </c>
       <c r="J26" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A26,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.6039999999999992</v>
       </c>
       <c r="K26" s="27">
         <f>ตั้งค่า!$C$10*A26^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -4567,31 +4567,31 @@
       </c>
       <c r="L26" s="25">
         <f t="shared" si="1"/>
-        <v>316.67052911616906</v>
+        <v>250.27424430380634</v>
       </c>
       <c r="M26" s="25">
         <f t="shared" si="2"/>
-        <v>504</v>
+        <v>638</v>
       </c>
       <c r="N26" s="25">
         <f>MAX(1,ROUND(M26*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>202</v>
+        <v>255</v>
       </c>
       <c r="O26" s="25">
         <f>MAX(1,ROUND(M26*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>302</v>
+        <v>383</v>
       </c>
       <c r="P26" s="25">
         <f t="shared" si="3"/>
-        <v>317</v>
+        <v>251</v>
       </c>
       <c r="Q26" s="27">
         <f t="shared" si="4"/>
-        <v>35.926666666666662</v>
+        <v>35.993399999999994</v>
       </c>
       <c r="R26" s="26">
         <f t="shared" si="6"/>
-        <v>4.25</v>
+        <v>4.25725</v>
       </c>
     </row>
     <row r="27" spans="1:18">
@@ -4631,8 +4631,8 @@
         <v>37</v>
       </c>
       <c r="J27" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A27,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.6039999999999992</v>
       </c>
       <c r="K27" s="27">
         <f>ตั้งค่า!$C$10*A27^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -4640,31 +4640,31 @@
       </c>
       <c r="L27" s="25">
         <f t="shared" si="1"/>
-        <v>345.62081530647896</v>
+        <v>273.15452627662216</v>
       </c>
       <c r="M27" s="25">
         <f t="shared" si="2"/>
-        <v>528</v>
+        <v>668</v>
       </c>
       <c r="N27" s="25">
         <f>MAX(1,ROUND(M27*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>211</v>
+        <v>267</v>
       </c>
       <c r="O27" s="25">
         <f>MAX(1,ROUND(M27*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>317</v>
+        <v>401</v>
       </c>
       <c r="P27" s="25">
         <f t="shared" si="3"/>
-        <v>346</v>
+        <v>274</v>
       </c>
       <c r="Q27" s="27">
         <f t="shared" si="4"/>
-        <v>39.213333333333331</v>
+        <v>39.291599999999995</v>
       </c>
       <c r="R27" s="26">
         <f t="shared" si="6"/>
-        <v>4.8487777777777774</v>
+        <v>4.8571400000000002</v>
       </c>
     </row>
     <row r="28" spans="1:18">
@@ -4704,8 +4704,8 @@
         <v>39</v>
       </c>
       <c r="J28" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A28,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.6</v>
       </c>
       <c r="K28" s="27">
         <f>ตั้งค่า!$C$10*A28^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -4713,31 +4713,31 @@
       </c>
       <c r="L28" s="25">
         <f t="shared" si="1"/>
-        <v>375.85778088302476</v>
+        <v>297.18987325634521</v>
       </c>
       <c r="M28" s="25">
         <f t="shared" si="2"/>
-        <v>552</v>
+        <v>698</v>
       </c>
       <c r="N28" s="25">
         <f>MAX(1,ROUND(M28*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>221</v>
+        <v>279</v>
       </c>
       <c r="O28" s="25">
         <f>MAX(1,ROUND(M28*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>331</v>
+        <v>419</v>
       </c>
       <c r="P28" s="25">
         <f t="shared" si="3"/>
-        <v>376</v>
+        <v>298</v>
       </c>
       <c r="Q28" s="27">
         <f t="shared" si="4"/>
-        <v>42.61333333333333</v>
+        <v>42.713333333333331</v>
       </c>
       <c r="R28" s="26">
         <f t="shared" si="6"/>
-        <v>5.5023333333333326</v>
+        <v>5.5120000000000005</v>
       </c>
     </row>
     <row r="29" spans="1:18">
@@ -4777,8 +4777,8 @@
         <v>41</v>
       </c>
       <c r="J29" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A29,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.5919999999999987</v>
       </c>
       <c r="K29" s="27">
         <f>ตั้งค่า!$C$10*A29^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -4786,31 +4786,31 @@
       </c>
       <c r="L29" s="25">
         <f t="shared" si="1"/>
-        <v>407.38142584580663</v>
+        <v>322.41546738262167</v>
       </c>
       <c r="M29" s="25">
         <f t="shared" si="2"/>
-        <v>575</v>
+        <v>727</v>
       </c>
       <c r="N29" s="25">
         <f>MAX(1,ROUND(M29*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>230</v>
+        <v>291</v>
       </c>
       <c r="O29" s="25">
         <f>MAX(1,ROUND(M29*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>345</v>
+        <v>436</v>
       </c>
       <c r="P29" s="25">
         <f t="shared" si="3"/>
-        <v>408</v>
+        <v>323</v>
       </c>
       <c r="Q29" s="27">
         <f t="shared" si="4"/>
-        <v>46.24</v>
+        <v>46.253599999999992</v>
       </c>
       <c r="R29" s="26">
         <f t="shared" si="6"/>
-        <v>6.2125555555555545</v>
+        <v>6.2238888888888892</v>
       </c>
     </row>
     <row r="30" spans="1:18">
@@ -4850,8 +4850,8 @@
         <v>42</v>
       </c>
       <c r="J30" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A30,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.588000000000001</v>
       </c>
       <c r="K30" s="27">
         <f>ตั้งค่า!$C$10*A30^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -4859,31 +4859,31 @@
       </c>
       <c r="L30" s="25">
         <f t="shared" si="1"/>
-        <v>440.19175019482446</v>
+        <v>348.54493494699648</v>
       </c>
       <c r="M30" s="25">
         <f t="shared" si="2"/>
-        <v>599</v>
+        <v>756</v>
       </c>
       <c r="N30" s="25">
         <f>MAX(1,ROUND(M30*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>240</v>
+        <v>302</v>
       </c>
       <c r="O30" s="25">
         <f>MAX(1,ROUND(M30*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>359</v>
+        <v>454</v>
       </c>
       <c r="P30" s="25">
         <f t="shared" si="3"/>
-        <v>441</v>
+        <v>349</v>
       </c>
       <c r="Q30" s="27">
         <f t="shared" si="4"/>
-        <v>49.98</v>
+        <v>49.95353333333334</v>
       </c>
       <c r="R30" s="26">
         <f t="shared" si="6"/>
-        <v>6.9832222222222216</v>
+        <v>6.9947822222222227</v>
       </c>
     </row>
     <row r="31" spans="1:18">
@@ -4923,8 +4923,8 @@
         <v>44</v>
       </c>
       <c r="J31" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A31,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.588000000000001</v>
       </c>
       <c r="K31" s="27">
         <f>ตั้งค่า!$C$10*A31^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -4932,31 +4932,31 @@
       </c>
       <c r="L31" s="25">
         <f t="shared" si="1"/>
-        <v>474.28875393007826</v>
+        <v>375.54302826321981</v>
       </c>
       <c r="M31" s="25">
         <f t="shared" si="2"/>
-        <v>623</v>
+        <v>786</v>
       </c>
       <c r="N31" s="25">
         <f>MAX(1,ROUND(M31*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="O31" s="25">
         <f>MAX(1,ROUND(M31*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>374</v>
+        <v>472</v>
       </c>
       <c r="P31" s="25">
         <f t="shared" si="3"/>
-        <v>474</v>
+        <v>376</v>
       </c>
       <c r="Q31" s="27">
         <f t="shared" si="4"/>
-        <v>53.72</v>
+        <v>53.818133333333336</v>
       </c>
       <c r="R31" s="26">
         <f t="shared" si="6"/>
-        <v>7.8162222222222217</v>
+        <v>7.827341111111112</v>
       </c>
     </row>
     <row r="32" spans="1:18">
@@ -4996,8 +4996,8 @@
         <v>46</v>
       </c>
       <c r="J32" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A32,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.5839999999999996</v>
       </c>
       <c r="K32" s="27">
         <f>ตั้งค่า!$C$10*A32^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -5005,31 +5005,31 @@
       </c>
       <c r="L32" s="25">
         <f t="shared" si="1"/>
-        <v>509.67243705156801</v>
+        <v>403.74796970534283</v>
       </c>
       <c r="M32" s="25">
         <f t="shared" si="2"/>
-        <v>646</v>
+        <v>816</v>
       </c>
       <c r="N32" s="25">
         <f>MAX(1,ROUND(M32*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>258</v>
+        <v>326</v>
       </c>
       <c r="O32" s="25">
         <f>MAX(1,ROUND(M32*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>388</v>
+        <v>490</v>
       </c>
       <c r="P32" s="25">
         <f t="shared" si="3"/>
-        <v>510</v>
+        <v>404</v>
       </c>
       <c r="Q32" s="27">
         <f t="shared" si="4"/>
-        <v>57.8</v>
+        <v>57.798933333333331</v>
       </c>
       <c r="R32" s="26">
         <f t="shared" si="6"/>
-        <v>8.7115555555555559</v>
+        <v>8.7243100000000009</v>
       </c>
     </row>
     <row r="33" spans="1:18">
@@ -5069,8 +5069,8 @@
         <v>48</v>
       </c>
       <c r="J33" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A33,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.58</v>
       </c>
       <c r="K33" s="27">
         <f>ตั้งค่า!$C$10*A33^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -5078,31 +5078,31 @@
       </c>
       <c r="L33" s="25">
         <f t="shared" si="1"/>
-        <v>546.34279955929378</v>
+        <v>432.9989553616781</v>
       </c>
       <c r="M33" s="25">
         <f t="shared" si="2"/>
-        <v>670</v>
+        <v>845</v>
       </c>
       <c r="N33" s="25">
         <f>MAX(1,ROUND(M33*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>268</v>
+        <v>338</v>
       </c>
       <c r="O33" s="25">
         <f>MAX(1,ROUND(M33*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>402</v>
+        <v>507</v>
       </c>
       <c r="P33" s="25">
         <f t="shared" si="3"/>
-        <v>547</v>
+        <v>433</v>
       </c>
       <c r="Q33" s="27">
         <f t="shared" si="4"/>
-        <v>61.993333333333332</v>
+        <v>61.918999999999997</v>
       </c>
       <c r="R33" s="26">
         <f t="shared" si="6"/>
-        <v>9.6748888888888889</v>
+        <v>9.6876255555555559</v>
       </c>
     </row>
     <row r="34" spans="1:18">
@@ -5142,8 +5142,8 @@
         <v>50</v>
       </c>
       <c r="J34" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A34,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.5760000000000005</v>
       </c>
       <c r="K34" s="27">
         <f>ตั้งค่า!$C$10*A34^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -5151,31 +5151,31 @@
       </c>
       <c r="L34" s="25">
         <f t="shared" si="1"/>
-        <v>584.29984145325557</v>
+        <v>463.29744891349554</v>
       </c>
       <c r="M34" s="25">
         <f t="shared" si="2"/>
-        <v>693</v>
+        <v>874</v>
       </c>
       <c r="N34" s="25">
         <f>MAX(1,ROUND(M34*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>277</v>
+        <v>350</v>
       </c>
       <c r="O34" s="25">
         <f>MAX(1,ROUND(M34*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>416</v>
+        <v>524</v>
       </c>
       <c r="P34" s="25">
         <f t="shared" si="3"/>
-        <v>585</v>
+        <v>464</v>
       </c>
       <c r="Q34" s="27">
         <f t="shared" si="4"/>
-        <v>66.3</v>
+        <v>66.321066666666667</v>
       </c>
       <c r="R34" s="26">
         <f t="shared" si="6"/>
-        <v>10.708111111111112</v>
+        <v>10.719608888888889</v>
       </c>
     </row>
     <row r="35" spans="1:18">
@@ -5215,8 +5215,8 @@
         <v>52</v>
       </c>
       <c r="J35" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A35,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.5679999999999996</v>
       </c>
       <c r="K35" s="27">
         <f>ตั้งค่า!$C$10*A35^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -5224,31 +5224,31 @@
       </c>
       <c r="L35" s="25">
         <f t="shared" si="1"/>
-        <v>623.54356273345331</v>
+        <v>494.87584343924868</v>
       </c>
       <c r="M35" s="25">
         <f t="shared" si="2"/>
-        <v>717</v>
+        <v>903</v>
       </c>
       <c r="N35" s="25">
         <f>MAX(1,ROUND(M35*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>287</v>
+        <v>361</v>
       </c>
       <c r="O35" s="25">
         <f>MAX(1,ROUND(M35*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>430</v>
+        <v>542</v>
       </c>
       <c r="P35" s="25">
         <f t="shared" si="3"/>
-        <v>624</v>
+        <v>495</v>
       </c>
       <c r="Q35" s="27">
         <f t="shared" si="4"/>
-        <v>70.72</v>
+        <v>70.685999999999993</v>
       </c>
       <c r="R35" s="26">
         <f t="shared" si="6"/>
-        <v>11.813111111111112</v>
+        <v>11.824960000000001</v>
       </c>
     </row>
     <row r="36" spans="1:18">
@@ -5288,8 +5288,8 @@
         <v>54</v>
       </c>
       <c r="J36" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A36,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.5640000000000001</v>
       </c>
       <c r="K36" s="27">
         <f>ตั้งค่า!$C$10*A36^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -5297,31 +5297,31 @@
       </c>
       <c r="L36" s="25">
         <f t="shared" si="1"/>
-        <v>664.07396339988713</v>
+        <v>527.28899475936851</v>
       </c>
       <c r="M36" s="25">
         <f t="shared" si="2"/>
-        <v>740</v>
+        <v>932</v>
       </c>
       <c r="N36" s="25">
         <f>MAX(1,ROUND(M36*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>296</v>
+        <v>373</v>
       </c>
       <c r="O36" s="25">
         <f>MAX(1,ROUND(M36*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>444</v>
+        <v>559</v>
       </c>
       <c r="P36" s="25">
         <f t="shared" si="3"/>
-        <v>665</v>
+        <v>528</v>
       </c>
       <c r="Q36" s="27">
         <f t="shared" si="4"/>
-        <v>75.36666666666666</v>
+        <v>75.363200000000006</v>
       </c>
       <c r="R36" s="26">
         <f t="shared" si="6"/>
-        <v>12.991777777777779</v>
+        <v>13.003060000000001</v>
       </c>
     </row>
     <row r="37" spans="1:18">
@@ -5361,8 +5361,8 @@
         <v>56</v>
       </c>
       <c r="J37" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A37,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.5599999999999987</v>
       </c>
       <c r="K37" s="27">
         <f>ตั้งค่า!$C$10*A37^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -5370,31 +5370,31 @@
       </c>
       <c r="L37" s="25">
         <f t="shared" ref="L37:L68" si="8">K37*60/J37</f>
-        <v>705.89104345255691</v>
+        <v>560.75456722866682</v>
       </c>
       <c r="M37" s="25">
         <f t="shared" ref="M37:M68" si="9">MAX(1,ROUND(B37/L37,0))</f>
-        <v>764</v>
+        <v>961</v>
       </c>
       <c r="N37" s="25">
         <f>MAX(1,ROUND(M37*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>306</v>
+        <v>384</v>
       </c>
       <c r="O37" s="25">
         <f>MAX(1,ROUND(M37*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>458</v>
+        <v>577</v>
       </c>
       <c r="P37" s="25">
         <f t="shared" ref="P37:P68" si="10">ROUNDUP(B37/M37,0)</f>
-        <v>706</v>
+        <v>561</v>
       </c>
       <c r="Q37" s="27">
         <f t="shared" ref="Q37:Q68" si="11">P37*J37/60</f>
-        <v>80.013333333333335</v>
+        <v>80.035999999999987</v>
       </c>
       <c r="R37" s="26">
         <f t="shared" si="6"/>
-        <v>14.247888888888889</v>
+        <v>14.259113333333335</v>
       </c>
     </row>
     <row r="38" spans="1:18">
@@ -5434,8 +5434,8 @@
         <v>59</v>
       </c>
       <c r="J38" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A38,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.5599999999999987</v>
       </c>
       <c r="K38" s="27">
         <f>ตั้งค่า!$C$10*A38^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -5443,31 +5443,31 @@
       </c>
       <c r="L38" s="25">
         <f t="shared" si="8"/>
-        <v>748.99480289146265</v>
+        <v>594.99587145583484</v>
       </c>
       <c r="M38" s="25">
         <f t="shared" si="9"/>
-        <v>787</v>
+        <v>991</v>
       </c>
       <c r="N38" s="25">
         <f>MAX(1,ROUND(M38*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>315</v>
+        <v>396</v>
       </c>
       <c r="O38" s="25">
         <f>MAX(1,ROUND(M38*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>472</v>
+        <v>595</v>
       </c>
       <c r="P38" s="25">
         <f t="shared" si="10"/>
-        <v>750</v>
+        <v>595</v>
       </c>
       <c r="Q38" s="27">
         <f t="shared" si="11"/>
-        <v>85</v>
+        <v>84.886666666666642</v>
       </c>
       <c r="R38" s="26">
         <f t="shared" ref="R38:R69" si="13">R37+Q37/60</f>
-        <v>15.581444444444445</v>
+        <v>15.593046666666668</v>
       </c>
     </row>
     <row r="39" spans="1:18">
@@ -5507,8 +5507,8 @@
         <v>61</v>
       </c>
       <c r="J39" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A39,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.5560000000000009</v>
       </c>
       <c r="K39" s="27">
         <f>ตั้งค่า!$C$10*A39^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -5516,31 +5516,31 @@
       </c>
       <c r="L39" s="25">
         <f t="shared" si="8"/>
-        <v>793.38524171660447</v>
+        <v>630.55395554849338</v>
       </c>
       <c r="M39" s="25">
         <f t="shared" si="9"/>
-        <v>811</v>
+        <v>1020</v>
       </c>
       <c r="N39" s="25">
         <f>MAX(1,ROUND(M39*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>324</v>
+        <v>408</v>
       </c>
       <c r="O39" s="25">
         <f>MAX(1,ROUND(M39*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>487</v>
+        <v>612</v>
       </c>
       <c r="P39" s="25">
         <f t="shared" si="10"/>
-        <v>794</v>
+        <v>631</v>
       </c>
       <c r="Q39" s="27">
         <f t="shared" si="11"/>
-        <v>89.986666666666665</v>
+        <v>89.98060000000001</v>
       </c>
       <c r="R39" s="26">
         <f t="shared" si="13"/>
-        <v>16.998111111111111</v>
+        <v>17.007824444444445</v>
       </c>
     </row>
     <row r="40" spans="1:18">
@@ -5580,8 +5580,8 @@
         <v>63</v>
       </c>
       <c r="J40" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A40,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.5519999999999996</v>
       </c>
       <c r="K40" s="27">
         <f>ตั้งค่า!$C$10*A40^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -5589,31 +5589,31 @@
       </c>
       <c r="L40" s="25">
         <f t="shared" si="8"/>
-        <v>839.06235992798213</v>
+        <v>667.16838722056582</v>
       </c>
       <c r="M40" s="25">
         <f t="shared" si="9"/>
-        <v>834</v>
+        <v>1049</v>
       </c>
       <c r="N40" s="25">
         <f>MAX(1,ROUND(M40*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>334</v>
+        <v>420</v>
       </c>
       <c r="O40" s="25">
         <f>MAX(1,ROUND(M40*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>500</v>
+        <v>629</v>
       </c>
       <c r="P40" s="25">
         <f t="shared" si="10"/>
-        <v>840</v>
+        <v>668</v>
       </c>
       <c r="Q40" s="27">
         <f t="shared" si="11"/>
-        <v>95.2</v>
+        <v>95.212266666666665</v>
       </c>
       <c r="R40" s="26">
         <f t="shared" si="13"/>
-        <v>18.497888888888887</v>
+        <v>18.507501111111111</v>
       </c>
     </row>
     <row r="41" spans="1:18">
@@ -5653,8 +5653,8 @@
         <v>66</v>
       </c>
       <c r="J41" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A41,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.5440000000000005</v>
       </c>
       <c r="K41" s="27">
         <f>ตั้งค่า!$C$10*A41^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -5662,31 +5662,31 @@
       </c>
       <c r="L41" s="25">
         <f t="shared" si="8"/>
-        <v>886.02615752559586</v>
+        <v>705.17063098947233</v>
       </c>
       <c r="M41" s="25">
         <f t="shared" si="9"/>
-        <v>858</v>
+        <v>1077</v>
       </c>
       <c r="N41" s="25">
         <f>MAX(1,ROUND(M41*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>343</v>
+        <v>431</v>
       </c>
       <c r="O41" s="25">
         <f>MAX(1,ROUND(M41*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>515</v>
+        <v>646</v>
       </c>
       <c r="P41" s="25">
         <f t="shared" si="10"/>
-        <v>886</v>
+        <v>706</v>
       </c>
       <c r="Q41" s="27">
         <f t="shared" si="11"/>
-        <v>100.41333333333334</v>
+        <v>100.53440000000001</v>
       </c>
       <c r="R41" s="26">
         <f t="shared" si="13"/>
-        <v>20.084555555555553</v>
+        <v>20.094372222222223</v>
       </c>
     </row>
     <row r="42" spans="1:18">
@@ -5726,8 +5726,8 @@
         <v>68</v>
       </c>
       <c r="J42" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A42,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.5399999999999991</v>
       </c>
       <c r="K42" s="27">
         <f>ตั้งค่า!$C$10*A42^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -5735,31 +5735,31 @@
       </c>
       <c r="L42" s="25">
         <f t="shared" si="8"/>
-        <v>934.27663450944556</v>
+        <v>743.92050523000353</v>
       </c>
       <c r="M42" s="25">
         <f t="shared" si="9"/>
-        <v>881</v>
+        <v>1106</v>
       </c>
       <c r="N42" s="25">
         <f>MAX(1,ROUND(M42*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>352</v>
+        <v>442</v>
       </c>
       <c r="O42" s="25">
         <f>MAX(1,ROUND(M42*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>529</v>
+        <v>664</v>
       </c>
       <c r="P42" s="25">
         <f t="shared" si="10"/>
-        <v>935</v>
+        <v>745</v>
       </c>
       <c r="Q42" s="27">
         <f t="shared" si="11"/>
-        <v>105.96666666666667</v>
+        <v>106.03833333333333</v>
       </c>
       <c r="R42" s="26">
         <f t="shared" si="13"/>
-        <v>21.758111111111109</v>
+        <v>21.769945555555555</v>
       </c>
     </row>
     <row r="43" spans="1:18">
@@ -5799,8 +5799,8 @@
         <v>70</v>
       </c>
       <c r="J43" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A43,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.5399999999999991</v>
       </c>
       <c r="K43" s="27">
         <f>ตั้งค่า!$C$10*A43^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -5808,31 +5808,31 @@
       </c>
       <c r="L43" s="25">
         <f t="shared" si="8"/>
-        <v>983.81379087953133</v>
+        <v>783.36461100477914</v>
       </c>
       <c r="M43" s="25">
         <f t="shared" si="9"/>
-        <v>904</v>
+        <v>1136</v>
       </c>
       <c r="N43" s="25">
         <f>MAX(1,ROUND(M43*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>362</v>
+        <v>454</v>
       </c>
       <c r="O43" s="25">
         <f>MAX(1,ROUND(M43*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>542</v>
+        <v>682</v>
       </c>
       <c r="P43" s="25">
         <f t="shared" si="10"/>
-        <v>985</v>
+        <v>784</v>
       </c>
       <c r="Q43" s="27">
         <f t="shared" si="11"/>
-        <v>111.63333333333334</v>
+        <v>111.58933333333333</v>
       </c>
       <c r="R43" s="26">
         <f t="shared" si="13"/>
-        <v>23.524222222222221</v>
+        <v>23.537251111111111</v>
       </c>
     </row>
     <row r="44" spans="1:18">
@@ -5872,8 +5872,8 @@
         <v>73</v>
       </c>
       <c r="J44" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A44,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.5359999999999996</v>
       </c>
       <c r="K44" s="27">
         <f>ตั้งค่า!$C$10*A44^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -5881,31 +5881,31 @@
       </c>
       <c r="L44" s="25">
         <f t="shared" si="8"/>
-        <v>1034.6376266358532</v>
+        <v>824.21929019725883</v>
       </c>
       <c r="M44" s="25">
         <f t="shared" si="9"/>
-        <v>928</v>
+        <v>1165</v>
       </c>
       <c r="N44" s="25">
         <f>MAX(1,ROUND(M44*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>371</v>
+        <v>466</v>
       </c>
       <c r="O44" s="25">
         <f>MAX(1,ROUND(M44*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>557</v>
+        <v>699</v>
       </c>
       <c r="P44" s="25">
         <f t="shared" si="10"/>
-        <v>1035</v>
+        <v>825</v>
       </c>
       <c r="Q44" s="27">
         <f t="shared" si="11"/>
-        <v>117.3</v>
+        <v>117.36999999999999</v>
       </c>
       <c r="R44" s="26">
         <f t="shared" si="13"/>
-        <v>25.384777777777778</v>
+        <v>25.397073333333331</v>
       </c>
     </row>
     <row r="45" spans="1:18">
@@ -5945,8 +5945,8 @@
         <v>76</v>
       </c>
       <c r="J45" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A45,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.532</v>
       </c>
       <c r="K45" s="27">
         <f>ตั้งค่า!$C$10*A45^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -5954,31 +5954,31 @@
       </c>
       <c r="L45" s="25">
         <f t="shared" si="8"/>
-        <v>1086.7481417784109</v>
+        <v>866.13775950459365</v>
       </c>
       <c r="M45" s="25">
         <f t="shared" si="9"/>
-        <v>951</v>
+        <v>1194</v>
       </c>
       <c r="N45" s="25">
         <f>MAX(1,ROUND(M45*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>380</v>
+        <v>478</v>
       </c>
       <c r="O45" s="25">
         <f>MAX(1,ROUND(M45*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>571</v>
+        <v>716</v>
       </c>
       <c r="P45" s="25">
         <f t="shared" si="10"/>
-        <v>1088</v>
+        <v>866</v>
       </c>
       <c r="Q45" s="27">
         <f t="shared" si="11"/>
-        <v>123.30666666666666</v>
+        <v>123.1452</v>
       </c>
       <c r="R45" s="26">
         <f t="shared" si="13"/>
-        <v>27.339777777777776</v>
+        <v>27.35324</v>
       </c>
     </row>
     <row r="46" spans="1:18">
@@ -6018,8 +6018,8 @@
         <v>78</v>
       </c>
       <c r="J46" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A46,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.5279999999999987</v>
       </c>
       <c r="K46" s="27">
         <f>ตั้งค่า!$C$10*A46^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -6027,31 +6027,31 @@
       </c>
       <c r="L46" s="25">
         <f t="shared" si="8"/>
-        <v>1140.1453363072044</v>
+        <v>909.12151581718945</v>
       </c>
       <c r="M46" s="25">
         <f t="shared" si="9"/>
-        <v>975</v>
+        <v>1222</v>
       </c>
       <c r="N46" s="25">
         <f>MAX(1,ROUND(M46*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>390</v>
+        <v>489</v>
       </c>
       <c r="O46" s="25">
         <f>MAX(1,ROUND(M46*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>585</v>
+        <v>733</v>
       </c>
       <c r="P46" s="25">
         <f t="shared" si="10"/>
-        <v>1140</v>
+        <v>910</v>
       </c>
       <c r="Q46" s="27">
         <f t="shared" si="11"/>
-        <v>129.19999999999999</v>
+        <v>129.34133333333332</v>
       </c>
       <c r="R46" s="26">
         <f t="shared" si="13"/>
-        <v>29.394888888888886</v>
+        <v>29.405660000000001</v>
       </c>
     </row>
     <row r="47" spans="1:18">
@@ -6091,8 +6091,8 @@
         <v>81</v>
       </c>
       <c r="J47" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A47,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.52</v>
       </c>
       <c r="K47" s="27">
         <f>ตั้งค่า!$C$10*A47^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -6100,31 +6100,31 @@
       </c>
       <c r="L47" s="25">
         <f t="shared" si="8"/>
-        <v>1194.829210222234</v>
+        <v>953.61955745436524</v>
       </c>
       <c r="M47" s="25">
         <f t="shared" si="9"/>
-        <v>998</v>
+        <v>1251</v>
       </c>
       <c r="N47" s="25">
         <f>MAX(1,ROUND(M47*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>399</v>
+        <v>500</v>
       </c>
       <c r="O47" s="25">
         <f>MAX(1,ROUND(M47*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>599</v>
+        <v>751</v>
       </c>
       <c r="P47" s="25">
         <f t="shared" si="10"/>
-        <v>1195</v>
+        <v>954</v>
       </c>
       <c r="Q47" s="27">
         <f t="shared" si="11"/>
-        <v>135.43333333333334</v>
+        <v>135.46799999999999</v>
       </c>
       <c r="R47" s="26">
         <f t="shared" si="13"/>
-        <v>31.548222222222218</v>
+        <v>31.56134888888889</v>
       </c>
     </row>
     <row r="48" spans="1:18">
@@ -6164,8 +6164,8 @@
         <v>84</v>
       </c>
       <c r="J48" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A48,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.516</v>
       </c>
       <c r="K48" s="27">
         <f>ตั้งค่า!$C$10*A48^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -6173,31 +6173,31 @@
       </c>
       <c r="L48" s="25">
         <f t="shared" si="8"/>
-        <v>1250.7997635234999</v>
+        <v>998.75979238607306</v>
       </c>
       <c r="M48" s="25">
         <f t="shared" si="9"/>
-        <v>1022</v>
+        <v>1279</v>
       </c>
       <c r="N48" s="25">
         <f>MAX(1,ROUND(M48*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>409</v>
+        <v>512</v>
       </c>
       <c r="O48" s="25">
         <f>MAX(1,ROUND(M48*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>613</v>
+        <v>767</v>
       </c>
       <c r="P48" s="25">
         <f t="shared" si="10"/>
-        <v>1251</v>
+        <v>1000</v>
       </c>
       <c r="Q48" s="27">
         <f t="shared" si="11"/>
-        <v>141.78</v>
+        <v>141.93333333333334</v>
       </c>
       <c r="R48" s="26">
         <f t="shared" si="13"/>
-        <v>33.80544444444444</v>
+        <v>33.81914888888889</v>
       </c>
     </row>
     <row r="49" spans="1:18">
@@ -6237,8 +6237,8 @@
         <v>87</v>
       </c>
       <c r="J49" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A49,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.5120000000000005</v>
       </c>
       <c r="K49" s="27">
         <f>ตั้งค่า!$C$10*A49^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -6246,31 +6246,31 @@
       </c>
       <c r="L49" s="25">
         <f t="shared" si="8"/>
-        <v>1308.0569962110017</v>
+        <v>1044.9703447174354</v>
       </c>
       <c r="M49" s="25">
         <f t="shared" si="9"/>
-        <v>1045</v>
+        <v>1308</v>
       </c>
       <c r="N49" s="25">
         <f>MAX(1,ROUND(M49*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>418</v>
+        <v>523</v>
       </c>
       <c r="O49" s="25">
         <f>MAX(1,ROUND(M49*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>627</v>
+        <v>785</v>
       </c>
       <c r="P49" s="25">
         <f t="shared" si="10"/>
-        <v>1309</v>
+        <v>1046</v>
       </c>
       <c r="Q49" s="27">
         <f t="shared" si="11"/>
-        <v>148.35333333333332</v>
+        <v>148.39253333333332</v>
       </c>
       <c r="R49" s="26">
         <f t="shared" si="13"/>
-        <v>36.16844444444444</v>
+        <v>36.184704444444442</v>
       </c>
     </row>
     <row r="50" spans="1:18">
@@ -6310,8 +6310,8 @@
         <v>90</v>
       </c>
       <c r="J50" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A50,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.5079999999999991</v>
       </c>
       <c r="K50" s="27">
         <f>ตั้งค่า!$C$10*A50^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -6319,31 +6319,31 @@
       </c>
       <c r="L50" s="25">
         <f t="shared" si="8"/>
-        <v>1366.600908284739</v>
+        <v>1092.2527240639665</v>
       </c>
       <c r="M50" s="25">
         <f t="shared" si="9"/>
-        <v>1068</v>
+        <v>1337</v>
       </c>
       <c r="N50" s="25">
         <f>MAX(1,ROUND(M50*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>427</v>
+        <v>535</v>
       </c>
       <c r="O50" s="25">
         <f>MAX(1,ROUND(M50*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>641</v>
+        <v>802</v>
       </c>
       <c r="P50" s="25">
         <f t="shared" si="10"/>
-        <v>1368</v>
+        <v>1093</v>
       </c>
       <c r="Q50" s="27">
         <f t="shared" si="11"/>
-        <v>155.04</v>
+        <v>154.98739999999998</v>
       </c>
       <c r="R50" s="26">
         <f t="shared" si="13"/>
-        <v>38.640999999999998</v>
+        <v>38.657913333333333</v>
       </c>
     </row>
     <row r="51" spans="1:18">
@@ -6383,8 +6383,8 @@
         <v>93</v>
       </c>
       <c r="J51" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A51,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.5039999999999996</v>
       </c>
       <c r="K51" s="27">
         <f>ตั้งค่า!$C$10*A51^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -6392,31 +6392,31 @@
       </c>
       <c r="L51" s="25">
         <f t="shared" si="8"/>
-        <v>1426.4314997447127</v>
+        <v>1140.6084428814731</v>
       </c>
       <c r="M51" s="25">
         <f t="shared" si="9"/>
-        <v>1092</v>
+        <v>1365</v>
       </c>
       <c r="N51" s="25">
         <f>MAX(1,ROUND(M51*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>437</v>
+        <v>546</v>
       </c>
       <c r="O51" s="25">
         <f>MAX(1,ROUND(M51*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>655</v>
+        <v>819</v>
       </c>
       <c r="P51" s="25">
         <f t="shared" si="10"/>
-        <v>1427</v>
+        <v>1141</v>
       </c>
       <c r="Q51" s="27">
         <f t="shared" si="11"/>
-        <v>161.72666666666666</v>
+        <v>161.71773333333334</v>
       </c>
       <c r="R51" s="26">
         <f t="shared" si="13"/>
-        <v>41.225000000000001</v>
+        <v>41.241036666666666</v>
       </c>
     </row>
     <row r="52" spans="1:18">
@@ -6456,8 +6456,8 @@
         <v>96</v>
       </c>
       <c r="J52" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A52,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.5039999999999996</v>
       </c>
       <c r="K52" s="27">
         <f>ตั้งค่า!$C$10*A52^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -6465,31 +6465,31 @@
       </c>
       <c r="L52" s="25">
         <f t="shared" si="8"/>
-        <v>1487.5487705909225</v>
+        <v>1189.4792615261374</v>
       </c>
       <c r="M52" s="25">
         <f t="shared" si="9"/>
-        <v>1115</v>
+        <v>1395</v>
       </c>
       <c r="N52" s="25">
         <f>MAX(1,ROUND(M52*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>446</v>
+        <v>558</v>
       </c>
       <c r="O52" s="25">
         <f>MAX(1,ROUND(M52*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>669</v>
+        <v>837</v>
       </c>
       <c r="P52" s="25">
         <f t="shared" si="10"/>
-        <v>1488</v>
+        <v>1190</v>
       </c>
       <c r="Q52" s="27">
         <f t="shared" si="11"/>
-        <v>168.64</v>
+        <v>168.66266666666667</v>
       </c>
       <c r="R52" s="26">
         <f t="shared" si="13"/>
-        <v>43.920444444444449</v>
+        <v>43.936332222222219</v>
       </c>
     </row>
     <row r="53" spans="1:18">
@@ -6529,8 +6529,8 @@
         <v>99</v>
       </c>
       <c r="J53" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A53,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.4960000000000004</v>
       </c>
       <c r="K53" s="27">
         <f>ตั้งค่า!$C$10*A53^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -6538,31 +6538,31 @@
       </c>
       <c r="L53" s="25">
         <f t="shared" si="8"/>
-        <v>1549.9527208233681</v>
+        <v>1240.5459629942211</v>
       </c>
       <c r="M53" s="25">
         <f t="shared" si="9"/>
-        <v>1139</v>
+        <v>1423</v>
       </c>
       <c r="N53" s="25">
         <f>MAX(1,ROUND(M53*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>456</v>
+        <v>569</v>
       </c>
       <c r="O53" s="25">
         <f>MAX(1,ROUND(M53*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>683</v>
+        <v>854</v>
       </c>
       <c r="P53" s="25">
         <f t="shared" si="10"/>
-        <v>1550</v>
+        <v>1241</v>
       </c>
       <c r="Q53" s="27">
         <f t="shared" si="11"/>
-        <v>175.66666666666666</v>
+        <v>175.72560000000001</v>
       </c>
       <c r="R53" s="26">
         <f t="shared" si="13"/>
-        <v>46.731111111111119</v>
+        <v>46.747376666666661</v>
       </c>
     </row>
     <row r="54" spans="1:18">
@@ -6602,8 +6602,8 @@
         <v>102</v>
       </c>
       <c r="J54" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A54,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.4920000000000009</v>
       </c>
       <c r="K54" s="27">
         <f>ตั้งค่า!$C$10*A54^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -6611,31 +6611,31 @@
       </c>
       <c r="L54" s="25">
         <f t="shared" si="8"/>
-        <v>1613.6433504420497</v>
+        <v>1292.1308034627812</v>
       </c>
       <c r="M54" s="25">
         <f t="shared" si="9"/>
-        <v>1162</v>
+        <v>1451</v>
       </c>
       <c r="N54" s="25">
         <f>MAX(1,ROUND(M54*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>465</v>
+        <v>580</v>
       </c>
       <c r="O54" s="25">
         <f>MAX(1,ROUND(M54*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>697</v>
+        <v>871</v>
       </c>
       <c r="P54" s="25">
         <f t="shared" si="10"/>
-        <v>1614</v>
+        <v>1293</v>
       </c>
       <c r="Q54" s="27">
         <f t="shared" si="11"/>
-        <v>182.92</v>
+        <v>183.0026</v>
       </c>
       <c r="R54" s="26">
         <f t="shared" si="13"/>
-        <v>49.658888888888896</v>
+        <v>49.676136666666658</v>
       </c>
     </row>
     <row r="55" spans="1:18">
@@ -6675,8 +6675,8 @@
         <v>105</v>
       </c>
       <c r="J55" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A55,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.4879999999999995</v>
       </c>
       <c r="K55" s="27">
         <f>ตั้งค่า!$C$10*A55^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -6684,31 +6684,31 @@
       </c>
       <c r="L55" s="25">
         <f t="shared" si="8"/>
-        <v>1678.6206594469675</v>
+        <v>1344.7950617624151</v>
       </c>
       <c r="M55" s="25">
         <f t="shared" si="9"/>
-        <v>1185</v>
+        <v>1480</v>
       </c>
       <c r="N55" s="25">
         <f>MAX(1,ROUND(M55*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>474</v>
+        <v>592</v>
       </c>
       <c r="O55" s="25">
         <f>MAX(1,ROUND(M55*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>711</v>
+        <v>888</v>
       </c>
       <c r="P55" s="25">
         <f t="shared" si="10"/>
-        <v>1680</v>
+        <v>1345</v>
       </c>
       <c r="Q55" s="27">
         <f t="shared" si="11"/>
-        <v>190.4</v>
+        <v>190.27266666666665</v>
       </c>
       <c r="R55" s="26">
         <f t="shared" si="13"/>
-        <v>52.707555555555565</v>
+        <v>52.726179999999992</v>
       </c>
     </row>
     <row r="56" spans="1:18">
@@ -6748,8 +6748,8 @@
         <v>109</v>
       </c>
       <c r="J56" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A56,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.484</v>
       </c>
       <c r="K56" s="27">
         <f>ตั้งค่า!$C$10*A56^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -6757,31 +6757,31 @@
       </c>
       <c r="L56" s="25">
         <f t="shared" si="8"/>
-        <v>1744.8846478381211</v>
+        <v>1398.5402646510165</v>
       </c>
       <c r="M56" s="25">
         <f t="shared" si="9"/>
-        <v>1209</v>
+        <v>1508</v>
       </c>
       <c r="N56" s="25">
         <f>MAX(1,ROUND(M56*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>484</v>
+        <v>603</v>
       </c>
       <c r="O56" s="25">
         <f>MAX(1,ROUND(M56*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>725</v>
+        <v>905</v>
       </c>
       <c r="P56" s="25">
         <f t="shared" si="10"/>
-        <v>1745</v>
+        <v>1399</v>
       </c>
       <c r="Q56" s="27">
         <f t="shared" si="11"/>
-        <v>197.76666666666668</v>
+        <v>197.8186</v>
       </c>
       <c r="R56" s="26">
         <f t="shared" si="13"/>
-        <v>55.880888888888897</v>
+        <v>55.897391111111105</v>
       </c>
     </row>
     <row r="57" spans="1:18">
@@ -6821,8 +6821,8 @@
         <v>112</v>
       </c>
       <c r="J57" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A57,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.48</v>
       </c>
       <c r="K57" s="27">
         <f>ตั้งค่า!$C$10*A57^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -6830,31 +6830,31 @@
       </c>
       <c r="L57" s="25">
         <f t="shared" si="8"/>
-        <v>1812.4353156155107</v>
+        <v>1453.3679417671547</v>
       </c>
       <c r="M57" s="25">
         <f t="shared" si="9"/>
-        <v>1232</v>
+        <v>1537</v>
       </c>
       <c r="N57" s="25">
         <f>MAX(1,ROUND(M57*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>493</v>
+        <v>615</v>
       </c>
       <c r="O57" s="25">
         <f>MAX(1,ROUND(M57*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>739</v>
+        <v>922</v>
       </c>
       <c r="P57" s="25">
         <f t="shared" si="10"/>
-        <v>1813</v>
+        <v>1453</v>
       </c>
       <c r="Q57" s="27">
         <f t="shared" si="11"/>
-        <v>205.47333333333333</v>
+        <v>205.35733333333334</v>
       </c>
       <c r="R57" s="26">
         <f t="shared" si="13"/>
-        <v>59.177000000000007</v>
+        <v>59.194367777777771</v>
       </c>
     </row>
     <row r="58" spans="1:18">
@@ -6894,8 +6894,8 @@
         <v>116</v>
       </c>
       <c r="J58" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A58,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.48</v>
       </c>
       <c r="K58" s="27">
         <f>ตั้งค่า!$C$10*A58^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -6903,31 +6903,31 @@
       </c>
       <c r="L58" s="25">
         <f t="shared" si="8"/>
-        <v>1881.2726627791362</v>
+        <v>1508.5677012851563</v>
       </c>
       <c r="M58" s="25">
         <f t="shared" si="9"/>
-        <v>1256</v>
+        <v>1566</v>
       </c>
       <c r="N58" s="25">
         <f>MAX(1,ROUND(M58*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>502</v>
+        <v>626</v>
       </c>
       <c r="O58" s="25">
         <f>MAX(1,ROUND(M58*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>754</v>
+        <v>940</v>
       </c>
       <c r="P58" s="25">
         <f t="shared" si="10"/>
-        <v>1881</v>
+        <v>1509</v>
       </c>
       <c r="Q58" s="27">
         <f t="shared" si="11"/>
-        <v>213.17999999999998</v>
+        <v>213.27200000000002</v>
       </c>
       <c r="R58" s="26">
         <f t="shared" si="13"/>
-        <v>62.601555555555564</v>
+        <v>62.616989999999994</v>
       </c>
     </row>
     <row r="59" spans="1:18">
@@ -6967,8 +6967,8 @@
         <v>119</v>
       </c>
       <c r="J59" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A59,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.4720000000000013</v>
       </c>
       <c r="K59" s="27">
         <f>ตั้งค่า!$C$10*A59^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -6976,31 +6976,31 @@
       </c>
       <c r="L59" s="25">
         <f t="shared" si="8"/>
-        <v>1951.396689328998</v>
+        <v>1566.2768516804986</v>
       </c>
       <c r="M59" s="25">
         <f t="shared" si="9"/>
-        <v>1279</v>
+        <v>1593</v>
       </c>
       <c r="N59" s="25">
         <f>MAX(1,ROUND(M59*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>512</v>
+        <v>637</v>
       </c>
       <c r="O59" s="25">
         <f>MAX(1,ROUND(M59*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>767</v>
+        <v>956</v>
       </c>
       <c r="P59" s="25">
         <f t="shared" si="10"/>
-        <v>1952</v>
+        <v>1567</v>
       </c>
       <c r="Q59" s="27">
         <f t="shared" si="11"/>
-        <v>221.22666666666666</v>
+        <v>221.26040000000003</v>
       </c>
       <c r="R59" s="26">
         <f t="shared" si="13"/>
-        <v>66.154555555555561</v>
+        <v>66.171523333333326</v>
       </c>
     </row>
     <row r="60" spans="1:18">
@@ -7040,8 +7040,8 @@
         <v>123</v>
       </c>
       <c r="J60" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A60,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.468</v>
       </c>
       <c r="K60" s="27">
         <f>ตั้งค่า!$C$10*A60^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -7049,31 +7049,31 @@
       </c>
       <c r="L60" s="25">
         <f t="shared" si="8"/>
-        <v>2022.8073952650957</v>
+        <v>1624.361158219491</v>
       </c>
       <c r="M60" s="25">
         <f t="shared" si="9"/>
-        <v>1302</v>
+        <v>1622</v>
       </c>
       <c r="N60" s="25">
         <f>MAX(1,ROUND(M60*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>521</v>
+        <v>649</v>
       </c>
       <c r="O60" s="25">
         <f>MAX(1,ROUND(M60*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>781</v>
+        <v>973</v>
       </c>
       <c r="P60" s="25">
         <f t="shared" si="10"/>
-        <v>2024</v>
+        <v>1625</v>
       </c>
       <c r="Q60" s="27">
         <f t="shared" si="11"/>
-        <v>229.38666666666666</v>
+        <v>229.34166666666667</v>
       </c>
       <c r="R60" s="26">
         <f t="shared" si="13"/>
-        <v>69.841666666666669</v>
+        <v>69.859196666666662</v>
       </c>
     </row>
     <row r="61" spans="1:18">
@@ -7113,8 +7113,8 @@
         <v>127</v>
       </c>
       <c r="J61" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A61,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.4640000000000004</v>
       </c>
       <c r="K61" s="27">
         <f>ตั้งค่า!$C$10*A61^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -7122,31 +7122,31 @@
       </c>
       <c r="L61" s="25">
         <f t="shared" si="8"/>
-        <v>2095.5047805874292</v>
+        <v>1683.5340864832842</v>
       </c>
       <c r="M61" s="25">
         <f t="shared" si="9"/>
-        <v>1326</v>
+        <v>1650</v>
       </c>
       <c r="N61" s="25">
         <f>MAX(1,ROUND(M61*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>530</v>
+        <v>660</v>
       </c>
       <c r="O61" s="25">
         <f>MAX(1,ROUND(M61*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>796</v>
+        <v>990</v>
       </c>
       <c r="P61" s="25">
         <f t="shared" si="10"/>
-        <v>2095</v>
+        <v>1684</v>
       </c>
       <c r="Q61" s="27">
         <f t="shared" si="11"/>
-        <v>237.43333333333334</v>
+        <v>237.55626666666666</v>
       </c>
       <c r="R61" s="26">
         <f t="shared" si="13"/>
-        <v>73.664777777777786</v>
+        <v>73.681557777777769</v>
       </c>
     </row>
     <row r="62" spans="1:18">
@@ -7186,8 +7186,8 @@
         <v>130</v>
       </c>
       <c r="J62" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A62,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.4600000000000009</v>
       </c>
       <c r="K62" s="27">
         <f>ตั้งค่า!$C$10*A62^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -7195,31 +7195,31 @@
       </c>
       <c r="L62" s="25">
         <f t="shared" si="8"/>
-        <v>2169.488845295999</v>
+        <v>1743.797180616169</v>
       </c>
       <c r="M62" s="25">
         <f t="shared" si="9"/>
-        <v>1349</v>
+        <v>1678</v>
       </c>
       <c r="N62" s="25">
         <f>MAX(1,ROUND(M62*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>540</v>
+        <v>671</v>
       </c>
       <c r="O62" s="25">
         <f>MAX(1,ROUND(M62*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>809</v>
+        <v>1007</v>
       </c>
       <c r="P62" s="25">
         <f t="shared" si="10"/>
-        <v>2170</v>
+        <v>1745</v>
       </c>
       <c r="Q62" s="27">
         <f t="shared" si="11"/>
-        <v>245.93333333333334</v>
+        <v>246.04500000000002</v>
       </c>
       <c r="R62" s="26">
         <f t="shared" si="13"/>
-        <v>77.622000000000014</v>
+        <v>77.640828888888876</v>
       </c>
     </row>
     <row r="63" spans="1:18">
@@ -7259,8 +7259,8 @@
         <v>134</v>
       </c>
       <c r="J63" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A63,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.4559999999999995</v>
       </c>
       <c r="K63" s="27">
         <f>ตั้งค่า!$C$10*A63^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -7268,31 +7268,31 @@
       </c>
       <c r="L63" s="25">
         <f t="shared" si="8"/>
-        <v>2244.7595893908042</v>
+        <v>1805.1519876841851</v>
       </c>
       <c r="M63" s="25">
         <f t="shared" si="9"/>
-        <v>1372</v>
+        <v>1707</v>
       </c>
       <c r="N63" s="25">
         <f>MAX(1,ROUND(M63*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>549</v>
+        <v>683</v>
       </c>
       <c r="O63" s="25">
         <f>MAX(1,ROUND(M63*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>823</v>
+        <v>1024</v>
       </c>
       <c r="P63" s="25">
         <f t="shared" si="10"/>
-        <v>2246</v>
+        <v>1805</v>
       </c>
       <c r="Q63" s="27">
         <f t="shared" si="11"/>
-        <v>254.54666666666665</v>
+        <v>254.38466666666667</v>
       </c>
       <c r="R63" s="26">
         <f t="shared" si="13"/>
-        <v>81.720888888888908</v>
+        <v>81.741578888888881</v>
       </c>
     </row>
     <row r="64" spans="1:18">
@@ -7332,8 +7332,8 @@
         <v>138</v>
       </c>
       <c r="J64" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A64,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.4480000000000004</v>
       </c>
       <c r="K64" s="27">
         <f>ตั้งค่า!$C$10*A64^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -7341,31 +7341,31 @@
       </c>
       <c r="L64" s="25">
         <f t="shared" si="8"/>
-        <v>2321.3170128718461</v>
+        <v>1868.4843380123762</v>
       </c>
       <c r="M64" s="25">
         <f t="shared" si="9"/>
-        <v>1396</v>
+        <v>1734</v>
       </c>
       <c r="N64" s="25">
         <f>MAX(1,ROUND(M64*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>558</v>
+        <v>694</v>
       </c>
       <c r="O64" s="25">
         <f>MAX(1,ROUND(M64*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>838</v>
+        <v>1040</v>
       </c>
       <c r="P64" s="25">
         <f t="shared" si="10"/>
-        <v>2321</v>
+        <v>1869</v>
       </c>
       <c r="Q64" s="27">
         <f t="shared" si="11"/>
-        <v>263.04666666666668</v>
+        <v>263.15519999999998</v>
       </c>
       <c r="R64" s="26">
         <f t="shared" si="13"/>
-        <v>85.963333333333352</v>
+        <v>85.981323333333322</v>
       </c>
     </row>
     <row r="65" spans="1:18">
@@ -7405,8 +7405,8 @@
         <v>143</v>
       </c>
       <c r="J65" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A65,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.4439999999999991</v>
       </c>
       <c r="K65" s="27">
         <f>ตั้งค่า!$C$10*A65^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -7414,31 +7414,31 @@
       </c>
       <c r="L65" s="25">
         <f t="shared" si="8"/>
-        <v>2399.1611157391239</v>
+        <v>1932.0577436080107</v>
       </c>
       <c r="M65" s="25">
         <f t="shared" si="9"/>
-        <v>1419</v>
+        <v>1762</v>
       </c>
       <c r="N65" s="25">
         <f>MAX(1,ROUND(M65*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>568</v>
+        <v>705</v>
       </c>
       <c r="O65" s="25">
         <f>MAX(1,ROUND(M65*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>851</v>
+        <v>1057</v>
       </c>
       <c r="P65" s="25">
         <f t="shared" si="10"/>
-        <v>2400</v>
+        <v>1933</v>
       </c>
       <c r="Q65" s="27">
         <f t="shared" si="11"/>
-        <v>272</v>
+        <v>272.03753333333333</v>
       </c>
       <c r="R65" s="26">
         <f t="shared" si="13"/>
-        <v>90.347444444444463</v>
+        <v>90.36724333333332</v>
       </c>
     </row>
     <row r="66" spans="1:18">
@@ -7478,8 +7478,8 @@
         <v>147</v>
       </c>
       <c r="J66" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A66,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.4439999999999991</v>
       </c>
       <c r="K66" s="27">
         <f>ตั้งค่า!$C$10*A66^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -7487,31 +7487,31 @@
       </c>
       <c r="L66" s="25">
         <f t="shared" si="8"/>
-        <v>2478.2918979926371</v>
+        <v>1995.7822011309729</v>
       </c>
       <c r="M66" s="25">
         <f t="shared" si="9"/>
-        <v>1442</v>
+        <v>1791</v>
       </c>
       <c r="N66" s="25">
         <f>MAX(1,ROUND(M66*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>577</v>
+        <v>716</v>
       </c>
       <c r="O66" s="25">
         <f>MAX(1,ROUND(M66*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>865</v>
+        <v>1075</v>
       </c>
       <c r="P66" s="25">
         <f t="shared" si="10"/>
-        <v>2480</v>
+        <v>1997</v>
       </c>
       <c r="Q66" s="27">
         <f t="shared" si="11"/>
-        <v>281.06666666666666</v>
+        <v>281.04446666666661</v>
       </c>
       <c r="R66" s="26">
         <f t="shared" si="13"/>
-        <v>94.880777777777794</v>
+        <v>94.90120222222221</v>
       </c>
     </row>
     <row r="67" spans="1:18">
@@ -7551,8 +7551,8 @@
         <v>151</v>
       </c>
       <c r="J67" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A67,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.4400000000000013</v>
       </c>
       <c r="K67" s="27">
         <f>ตั้งค่า!$C$10*A67^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -7560,31 +7560,31 @@
       </c>
       <c r="L67" s="25">
         <f t="shared" si="8"/>
-        <v>2558.7093596323871</v>
+        <v>2061.5193892772782</v>
       </c>
       <c r="M67" s="25">
         <f t="shared" si="9"/>
-        <v>1466</v>
+        <v>1819</v>
       </c>
       <c r="N67" s="25">
         <f>MAX(1,ROUND(M67*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>586</v>
+        <v>728</v>
       </c>
       <c r="O67" s="25">
         <f>MAX(1,ROUND(M67*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>880</v>
+        <v>1091</v>
       </c>
       <c r="P67" s="25">
         <f t="shared" si="10"/>
-        <v>2559</v>
+        <v>2062</v>
       </c>
       <c r="Q67" s="27">
         <f t="shared" si="11"/>
-        <v>290.02000000000004</v>
+        <v>290.05466666666672</v>
       </c>
       <c r="R67" s="26">
         <f t="shared" si="13"/>
-        <v>99.565222222222232</v>
+        <v>99.585276666666658</v>
       </c>
     </row>
     <row r="68" spans="1:18">
@@ -7624,8 +7624,8 @@
         <v>155</v>
       </c>
       <c r="J68" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A68,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.4359999999999999</v>
       </c>
       <c r="K68" s="27">
         <f>ตั้งค่า!$C$10*A68^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -7633,31 +7633,31 @@
       </c>
       <c r="L68" s="25">
         <f t="shared" si="8"/>
-        <v>2640.4135006583724</v>
+        <v>2128.3560697578155</v>
       </c>
       <c r="M68" s="25">
         <f t="shared" si="9"/>
-        <v>1489</v>
+        <v>1848</v>
       </c>
       <c r="N68" s="25">
         <f>MAX(1,ROUND(M68*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>596</v>
+        <v>739</v>
       </c>
       <c r="O68" s="25">
         <f>MAX(1,ROUND(M68*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>893</v>
+        <v>1109</v>
       </c>
       <c r="P68" s="25">
         <f t="shared" si="10"/>
-        <v>2641</v>
+        <v>2128</v>
       </c>
       <c r="Q68" s="27">
         <f t="shared" si="11"/>
-        <v>299.31333333333333</v>
+        <v>299.1968</v>
       </c>
       <c r="R68" s="26">
         <f t="shared" si="13"/>
-        <v>104.39888888888891</v>
+        <v>104.41952111111111</v>
       </c>
     </row>
     <row r="69" spans="1:18">
@@ -7697,8 +7697,8 @@
         <v>160</v>
       </c>
       <c r="J69" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A69,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.4320000000000004</v>
       </c>
       <c r="K69" s="27">
         <f>ตั้งค่า!$C$10*A69^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -7706,31 +7706,31 @@
       </c>
       <c r="L69" s="25">
         <f t="shared" ref="L69:L100" si="15">K69*60/J69</f>
-        <v>2723.4043210705936</v>
+        <v>2196.2938073149949</v>
       </c>
       <c r="M69" s="25">
         <f t="shared" ref="M69:M100" si="16">MAX(1,ROUND(B69/L69,0))</f>
-        <v>1513</v>
+        <v>1876</v>
       </c>
       <c r="N69" s="25">
         <f>MAX(1,ROUND(M69*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>605</v>
+        <v>750</v>
       </c>
       <c r="O69" s="25">
         <f>MAX(1,ROUND(M69*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>908</v>
+        <v>1126</v>
       </c>
       <c r="P69" s="25">
         <f t="shared" ref="P69:P104" si="17">ROUNDUP(B69/M69,0)</f>
-        <v>2723</v>
+        <v>2196</v>
       </c>
       <c r="Q69" s="27">
         <f t="shared" ref="Q69:Q100" si="18">P69*J69/60</f>
-        <v>308.60666666666663</v>
+        <v>308.61120000000005</v>
       </c>
       <c r="R69" s="26">
         <f t="shared" si="13"/>
-        <v>109.38744444444445</v>
+        <v>109.40613444444445</v>
       </c>
     </row>
     <row r="70" spans="1:18">
@@ -7770,8 +7770,8 @@
         <v>165</v>
       </c>
       <c r="J70" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A70,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.4239999999999995</v>
       </c>
       <c r="K70" s="27">
         <f>ตั้งค่า!$C$10*A70^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -7779,31 +7779,31 @@
       </c>
       <c r="L70" s="25">
         <f t="shared" si="15"/>
-        <v>2807.6818208690511</v>
+        <v>2266.4098269123397</v>
       </c>
       <c r="M70" s="25">
         <f t="shared" si="16"/>
-        <v>1536</v>
+        <v>1903</v>
       </c>
       <c r="N70" s="25">
         <f>MAX(1,ROUND(M70*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>614</v>
+        <v>761</v>
       </c>
       <c r="O70" s="25">
         <f>MAX(1,ROUND(M70*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>922</v>
+        <v>1142</v>
       </c>
       <c r="P70" s="25">
         <f t="shared" si="17"/>
-        <v>2808</v>
+        <v>2267</v>
       </c>
       <c r="Q70" s="27">
         <f t="shared" si="18"/>
-        <v>318.23999999999995</v>
+        <v>318.28679999999997</v>
       </c>
       <c r="R70" s="26">
         <f t="shared" ref="R70:R104" si="20">R69+Q69/60</f>
-        <v>114.5308888888889</v>
+        <v>114.54965444444444</v>
       </c>
     </row>
     <row r="71" spans="1:18">
@@ -7843,8 +7843,8 @@
         <v>169</v>
       </c>
       <c r="J71" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A71,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.42</v>
       </c>
       <c r="K71" s="27">
         <f>ตั้งค่า!$C$10*A71^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -7852,31 +7852,31 @@
       </c>
       <c r="L71" s="25">
         <f t="shared" si="15"/>
-        <v>2893.2460000537449</v>
+        <v>2336.5882185707205</v>
       </c>
       <c r="M71" s="25">
         <f t="shared" si="16"/>
-        <v>1559</v>
+        <v>1931</v>
       </c>
       <c r="N71" s="25">
         <f>MAX(1,ROUND(M71*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>624</v>
+        <v>772</v>
       </c>
       <c r="O71" s="25">
         <f>MAX(1,ROUND(M71*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>935</v>
+        <v>1159</v>
       </c>
       <c r="P71" s="25">
         <f t="shared" si="17"/>
-        <v>2894</v>
+        <v>2337</v>
       </c>
       <c r="Q71" s="27">
         <f t="shared" si="18"/>
-        <v>327.98666666666668</v>
+        <v>327.959</v>
       </c>
       <c r="R71" s="26">
         <f t="shared" si="20"/>
-        <v>119.8348888888889</v>
+        <v>119.85443444444444</v>
       </c>
     </row>
     <row r="72" spans="1:18">
@@ -7916,8 +7916,8 @@
         <v>174</v>
       </c>
       <c r="J72" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A72,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.4160000000000004</v>
       </c>
       <c r="K72" s="27">
         <f>ตั้งค่า!$C$10*A72^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -7925,31 +7925,31 @@
       </c>
       <c r="L72" s="25">
         <f t="shared" si="15"/>
-        <v>2980.0968586246745</v>
+        <v>2407.8729371016857</v>
       </c>
       <c r="M72" s="25">
         <f t="shared" si="16"/>
-        <v>1583</v>
+        <v>1959</v>
       </c>
       <c r="N72" s="25">
         <f>MAX(1,ROUND(M72*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>633</v>
+        <v>784</v>
       </c>
       <c r="O72" s="25">
         <f>MAX(1,ROUND(M72*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>950</v>
+        <v>1175</v>
       </c>
       <c r="P72" s="25">
         <f t="shared" si="17"/>
-        <v>2980</v>
+        <v>2408</v>
       </c>
       <c r="Q72" s="27">
         <f t="shared" si="18"/>
-        <v>337.73333333333335</v>
+        <v>337.76213333333334</v>
       </c>
       <c r="R72" s="26">
         <f t="shared" si="20"/>
-        <v>125.30133333333335</v>
+        <v>125.32041777777776</v>
       </c>
     </row>
     <row r="73" spans="1:18">
@@ -7989,8 +7989,8 @@
         <v>179</v>
       </c>
       <c r="J73" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A73,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.411999999999999</v>
       </c>
       <c r="K73" s="27">
         <f>ตั้งค่า!$C$10*A73^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -7998,31 +7998,31 @@
       </c>
       <c r="L73" s="25">
         <f t="shared" si="15"/>
-        <v>3068.23439658184</v>
+        <v>2480.2655607176075</v>
       </c>
       <c r="M73" s="25">
         <f t="shared" si="16"/>
-        <v>1606</v>
+        <v>1987</v>
       </c>
       <c r="N73" s="25">
         <f>MAX(1,ROUND(M73*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>642</v>
+        <v>795</v>
       </c>
       <c r="O73" s="25">
         <f>MAX(1,ROUND(M73*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>964</v>
+        <v>1192</v>
       </c>
       <c r="P73" s="25">
         <f t="shared" si="17"/>
-        <v>3069</v>
+        <v>2480</v>
       </c>
       <c r="Q73" s="27">
         <f t="shared" si="18"/>
-        <v>347.82</v>
+        <v>347.69599999999997</v>
       </c>
       <c r="R73" s="26">
         <f t="shared" si="20"/>
-        <v>130.93022222222223</v>
+        <v>130.94978666666665</v>
       </c>
     </row>
     <row r="74" spans="1:18">
@@ -8062,8 +8062,8 @@
         <v>184</v>
       </c>
       <c r="J74" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A74,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.4080000000000013</v>
       </c>
       <c r="K74" s="27">
         <f>ตั้งค่า!$C$10*A74^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -8071,31 +8071,31 @@
       </c>
       <c r="L74" s="25">
         <f t="shared" si="15"/>
-        <v>3157.6586139252413</v>
+        <v>2553.7676706341149</v>
       </c>
       <c r="M74" s="25">
         <f t="shared" si="16"/>
-        <v>1629</v>
+        <v>2015</v>
       </c>
       <c r="N74" s="25">
         <f>MAX(1,ROUND(M74*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>652</v>
+        <v>806</v>
       </c>
       <c r="O74" s="25">
         <f>MAX(1,ROUND(M74*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>977</v>
+        <v>1209</v>
       </c>
       <c r="P74" s="25">
         <f t="shared" si="17"/>
-        <v>3159</v>
+        <v>2554</v>
       </c>
       <c r="Q74" s="27">
         <f t="shared" si="18"/>
-        <v>358.02000000000004</v>
+        <v>357.90053333333339</v>
       </c>
       <c r="R74" s="26">
         <f t="shared" si="20"/>
-        <v>136.72722222222222</v>
+        <v>136.74471999999997</v>
       </c>
     </row>
     <row r="75" spans="1:18">
@@ -8135,8 +8135,8 @@
         <v>189</v>
       </c>
       <c r="J75" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A75,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.4080000000000013</v>
       </c>
       <c r="K75" s="27">
         <f>ตั้งค่า!$C$10*A75^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -8144,31 +8144,31 @@
       </c>
       <c r="L75" s="25">
         <f t="shared" si="15"/>
-        <v>3248.3695106548794</v>
+        <v>2627.1304320234508</v>
       </c>
       <c r="M75" s="25">
         <f t="shared" si="16"/>
-        <v>1653</v>
+        <v>2044</v>
       </c>
       <c r="N75" s="25">
         <f>MAX(1,ROUND(M75*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>661</v>
+        <v>818</v>
       </c>
       <c r="O75" s="25">
         <f>MAX(1,ROUND(M75*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>992</v>
+        <v>1226</v>
       </c>
       <c r="P75" s="25">
         <f t="shared" si="17"/>
-        <v>3248</v>
+        <v>2627</v>
       </c>
       <c r="Q75" s="27">
         <f t="shared" si="18"/>
-        <v>368.10666666666663</v>
+        <v>368.13026666666673</v>
       </c>
       <c r="R75" s="26">
         <f t="shared" si="20"/>
-        <v>142.69422222222224</v>
+        <v>142.70972888888886</v>
       </c>
     </row>
     <row r="76" spans="1:18">
@@ -8208,8 +8208,8 @@
         <v>194</v>
       </c>
       <c r="J76" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A76,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.4</v>
       </c>
       <c r="K76" s="27">
         <f>ตั้งค่า!$C$10*A76^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -8217,31 +8217,31 @@
       </c>
       <c r="L76" s="25">
         <f t="shared" si="15"/>
-        <v>3340.3670867707528</v>
+        <v>2704.1066892906092</v>
       </c>
       <c r="M76" s="25">
         <f t="shared" si="16"/>
-        <v>1676</v>
+        <v>2070</v>
       </c>
       <c r="N76" s="25">
         <f>MAX(1,ROUND(M76*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>670</v>
+        <v>828</v>
       </c>
       <c r="O76" s="25">
         <f>MAX(1,ROUND(M76*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>1006</v>
+        <v>1242</v>
       </c>
       <c r="P76" s="25">
         <f t="shared" si="17"/>
-        <v>3341</v>
+        <v>2705</v>
       </c>
       <c r="Q76" s="27">
         <f t="shared" si="18"/>
-        <v>378.64666666666665</v>
+        <v>378.7</v>
       </c>
       <c r="R76" s="26">
         <f t="shared" si="20"/>
-        <v>148.82933333333335</v>
+        <v>148.84523333333331</v>
       </c>
     </row>
     <row r="77" spans="1:18">
@@ -8281,8 +8281,8 @@
         <v>200</v>
       </c>
       <c r="J77" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A77,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.3960000000000008</v>
       </c>
       <c r="K77" s="27">
         <f>ตั้งค่า!$C$10*A77^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -8290,31 +8290,31 @@
       </c>
       <c r="L77" s="25">
         <f t="shared" si="15"/>
-        <v>3433.6513422728622</v>
+        <v>2780.9467755425749</v>
       </c>
       <c r="M77" s="25">
         <f t="shared" si="16"/>
-        <v>1699</v>
+        <v>2098</v>
       </c>
       <c r="N77" s="25">
         <f>MAX(1,ROUND(M77*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>680</v>
+        <v>839</v>
       </c>
       <c r="O77" s="25">
         <f>MAX(1,ROUND(M77*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>1019</v>
+        <v>1259</v>
       </c>
       <c r="P77" s="25">
         <f t="shared" si="17"/>
-        <v>3435</v>
+        <v>2782</v>
       </c>
       <c r="Q77" s="27">
         <f t="shared" si="18"/>
-        <v>389.3</v>
+        <v>389.29453333333339</v>
       </c>
       <c r="R77" s="26">
         <f t="shared" si="20"/>
-        <v>155.14011111111114</v>
+        <v>155.15689999999998</v>
       </c>
     </row>
     <row r="78" spans="1:18">
@@ -8354,8 +8354,8 @@
         <v>205</v>
       </c>
       <c r="J78" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A78,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.3919999999999995</v>
       </c>
       <c r="K78" s="27">
         <f>ตั้งค่า!$C$10*A78^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -8363,31 +8363,31 @@
       </c>
       <c r="L78" s="25">
         <f t="shared" si="15"/>
-        <v>3528.2222771612078</v>
+        <v>2858.9027031334858</v>
       </c>
       <c r="M78" s="25">
         <f t="shared" si="16"/>
-        <v>1723</v>
+        <v>2126</v>
       </c>
       <c r="N78" s="25">
         <f>MAX(1,ROUND(M78*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>689</v>
+        <v>850</v>
       </c>
       <c r="O78" s="25">
         <f>MAX(1,ROUND(M78*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>1034</v>
+        <v>1276</v>
       </c>
       <c r="P78" s="25">
         <f t="shared" si="17"/>
-        <v>3528</v>
+        <v>2860</v>
       </c>
       <c r="Q78" s="27">
         <f t="shared" si="18"/>
-        <v>399.84</v>
+        <v>400.01866666666666</v>
       </c>
       <c r="R78" s="26">
         <f t="shared" si="20"/>
-        <v>161.62844444444448</v>
+        <v>161.6451422222222</v>
       </c>
     </row>
     <row r="79" spans="1:18">
@@ -8427,8 +8427,8 @@
         <v>211</v>
       </c>
       <c r="J79" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A79,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.3879999999999999</v>
       </c>
       <c r="K79" s="27">
         <f>ตั้งค่า!$C$10*A79^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -8436,31 +8436,31 @@
       </c>
       <c r="L79" s="25">
         <f t="shared" si="15"/>
-        <v>3624.0798914357892</v>
+        <v>2937.9760684028811</v>
       </c>
       <c r="M79" s="25">
         <f t="shared" si="16"/>
-        <v>1746</v>
+        <v>2154</v>
       </c>
       <c r="N79" s="25">
         <f>MAX(1,ROUND(M79*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>698</v>
+        <v>862</v>
       </c>
       <c r="O79" s="25">
         <f>MAX(1,ROUND(M79*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>1048</v>
+        <v>1292</v>
       </c>
       <c r="P79" s="25">
         <f t="shared" si="17"/>
-        <v>3625</v>
+        <v>2938</v>
       </c>
       <c r="Q79" s="27">
         <f t="shared" si="18"/>
-        <v>410.83333333333331</v>
+        <v>410.73239999999998</v>
       </c>
       <c r="R79" s="26">
         <f t="shared" si="20"/>
-        <v>168.29244444444447</v>
+        <v>168.31211999999999</v>
       </c>
     </row>
     <row r="80" spans="1:18">
@@ -8500,8 +8500,8 @@
         <v>216</v>
       </c>
       <c r="J80" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A80,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.3840000000000003</v>
       </c>
       <c r="K80" s="27">
         <f>ตั้งค่า!$C$10*A80^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -8509,31 +8509,31 @@
       </c>
       <c r="L80" s="25">
         <f t="shared" si="15"/>
-        <v>3721.2241850966066</v>
+        <v>3018.1684707367513</v>
       </c>
       <c r="M80" s="25">
         <f t="shared" si="16"/>
-        <v>1769</v>
+        <v>2182</v>
       </c>
       <c r="N80" s="25">
         <f>MAX(1,ROUND(M80*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>708</v>
+        <v>873</v>
       </c>
       <c r="O80" s="25">
         <f>MAX(1,ROUND(M80*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>1061</v>
+        <v>1309</v>
       </c>
       <c r="P80" s="25">
         <f t="shared" si="17"/>
-        <v>3723</v>
+        <v>3018</v>
       </c>
       <c r="Q80" s="27">
         <f t="shared" si="18"/>
-        <v>421.93999999999994</v>
+        <v>421.71519999999998</v>
       </c>
       <c r="R80" s="26">
         <f t="shared" si="20"/>
-        <v>175.1396666666667</v>
+        <v>175.15765999999999</v>
       </c>
     </row>
     <row r="81" spans="1:18">
@@ -8573,8 +8573,8 @@
         <v>222</v>
       </c>
       <c r="J81" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A81,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.3760000000000012</v>
       </c>
       <c r="K81" s="27">
         <f>ตั้งค่า!$C$10*A81^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -8582,31 +8582,31 @@
       </c>
       <c r="L81" s="25">
         <f t="shared" si="15"/>
-        <v>3819.6551581436597</v>
+        <v>3100.9616852169152</v>
       </c>
       <c r="M81" s="25">
         <f t="shared" si="16"/>
-        <v>1793</v>
+        <v>2208</v>
       </c>
       <c r="N81" s="25">
         <f>MAX(1,ROUND(M81*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>717</v>
+        <v>883</v>
       </c>
       <c r="O81" s="25">
         <f>MAX(1,ROUND(M81*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>1076</v>
+        <v>1325</v>
       </c>
       <c r="P81" s="25">
         <f t="shared" si="17"/>
-        <v>3820</v>
+        <v>3102</v>
       </c>
       <c r="Q81" s="27">
         <f t="shared" si="18"/>
-        <v>432.93333333333334</v>
+        <v>433.03920000000005</v>
       </c>
       <c r="R81" s="26">
         <f t="shared" si="20"/>
-        <v>182.17200000000003</v>
+        <v>182.18624666666665</v>
       </c>
     </row>
     <row r="82" spans="1:18">
@@ -8646,8 +8646,8 @@
         <v>228</v>
       </c>
       <c r="J82" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A82,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.3719999999999999</v>
       </c>
       <c r="K82" s="27">
         <f>ตั้งค่า!$C$10*A82^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -8655,31 +8655,31 @@
       </c>
       <c r="L82" s="25">
         <f t="shared" si="15"/>
-        <v>3919.3728105769496</v>
+        <v>3183.4370654471159</v>
       </c>
       <c r="M82" s="25">
         <f t="shared" si="16"/>
-        <v>1816</v>
+        <v>2236</v>
       </c>
       <c r="N82" s="25">
         <f>MAX(1,ROUND(M82*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>726</v>
+        <v>894</v>
       </c>
       <c r="O82" s="25">
         <f>MAX(1,ROUND(M82*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>1090</v>
+        <v>1342</v>
       </c>
       <c r="P82" s="25">
         <f t="shared" si="17"/>
-        <v>3920</v>
+        <v>3184</v>
       </c>
       <c r="Q82" s="27">
         <f t="shared" si="18"/>
-        <v>444.26666666666665</v>
+        <v>444.27413333333334</v>
       </c>
       <c r="R82" s="26">
         <f t="shared" si="20"/>
-        <v>189.38755555555559</v>
+        <v>189.40356666666665</v>
       </c>
     </row>
     <row r="83" spans="1:18">
@@ -8719,8 +8719,8 @@
         <v>234</v>
       </c>
       <c r="J83" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A83,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.3719999999999999</v>
       </c>
       <c r="K83" s="27">
         <f>ตั้งค่า!$C$10*A83^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -8728,31 +8728,31 @@
       </c>
       <c r="L83" s="25">
         <f t="shared" si="15"/>
-        <v>4020.3771423964749</v>
+        <v>3265.4759398346905</v>
       </c>
       <c r="M83" s="25">
         <f t="shared" si="16"/>
-        <v>1840</v>
+        <v>2265</v>
       </c>
       <c r="N83" s="25">
         <f>MAX(1,ROUND(M83*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>736</v>
+        <v>906</v>
       </c>
       <c r="O83" s="25">
         <f>MAX(1,ROUND(M83*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>1104</v>
+        <v>1359</v>
       </c>
       <c r="P83" s="25">
         <f t="shared" si="17"/>
-        <v>4020</v>
+        <v>3266</v>
       </c>
       <c r="Q83" s="27">
         <f t="shared" si="18"/>
-        <v>455.6</v>
+        <v>455.71586666666667</v>
       </c>
       <c r="R83" s="26">
         <f t="shared" si="20"/>
-        <v>196.79200000000003</v>
+        <v>196.80813555555554</v>
       </c>
     </row>
     <row r="84" spans="1:18">
@@ -8792,8 +8792,8 @@
         <v>240</v>
       </c>
       <c r="J84" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A84,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.3680000000000003</v>
       </c>
       <c r="K84" s="27">
         <f>ตั้งค่า!$C$10*A84^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -8801,31 +8801,31 @@
       </c>
       <c r="L84" s="25">
         <f t="shared" si="15"/>
-        <v>4122.6681536022361</v>
+        <v>3350.1605454702685</v>
       </c>
       <c r="M84" s="25">
         <f t="shared" si="16"/>
-        <v>1863</v>
+        <v>2292</v>
       </c>
       <c r="N84" s="25">
         <f>MAX(1,ROUND(M84*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>745</v>
+        <v>917</v>
       </c>
       <c r="O84" s="25">
         <f>MAX(1,ROUND(M84*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>1118</v>
+        <v>1375</v>
       </c>
       <c r="P84" s="25">
         <f t="shared" si="17"/>
-        <v>4123</v>
+        <v>3351</v>
       </c>
       <c r="Q84" s="27">
         <f t="shared" si="18"/>
-        <v>467.27333333333331</v>
+        <v>467.3528</v>
       </c>
       <c r="R84" s="26">
         <f t="shared" si="20"/>
-        <v>204.38533333333336</v>
+        <v>204.40339999999998</v>
       </c>
     </row>
     <row r="85" spans="1:18">
@@ -8865,8 +8865,8 @@
         <v>247</v>
       </c>
       <c r="J85" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A85,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.3640000000000008</v>
       </c>
       <c r="K85" s="27">
         <f>ตั้งค่า!$C$10*A85^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -8874,31 +8874,31 @@
       </c>
       <c r="L85" s="25">
         <f t="shared" si="15"/>
-        <v>4226.2458441942335</v>
+        <v>3435.972231052222</v>
       </c>
       <c r="M85" s="25">
         <f t="shared" si="16"/>
-        <v>1886</v>
+        <v>2320</v>
       </c>
       <c r="N85" s="25">
         <f>MAX(1,ROUND(M85*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>754</v>
+        <v>928</v>
       </c>
       <c r="O85" s="25">
         <f>MAX(1,ROUND(M85*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>1132</v>
+        <v>1392</v>
       </c>
       <c r="P85" s="25">
         <f t="shared" si="17"/>
-        <v>4227</v>
+        <v>3437</v>
       </c>
       <c r="Q85" s="27">
         <f t="shared" si="18"/>
-        <v>479.06</v>
+        <v>479.11780000000005</v>
       </c>
       <c r="R85" s="26">
         <f t="shared" si="20"/>
-        <v>212.17322222222225</v>
+        <v>212.1926133333333</v>
       </c>
     </row>
     <row r="86" spans="1:18">
@@ -8938,8 +8938,8 @@
         <v>253</v>
       </c>
       <c r="J86" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A86,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.36</v>
       </c>
       <c r="K86" s="27">
         <f>ตั้งค่า!$C$10*A86^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -8947,31 +8947,31 @@
       </c>
       <c r="L86" s="25">
         <f t="shared" si="15"/>
-        <v>4331.1102141724677</v>
+        <v>3522.9126143986578</v>
       </c>
       <c r="M86" s="25">
         <f t="shared" si="16"/>
-        <v>1910</v>
+        <v>2348</v>
       </c>
       <c r="N86" s="25">
         <f>MAX(1,ROUND(M86*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>764</v>
+        <v>939</v>
       </c>
       <c r="O86" s="25">
         <f>MAX(1,ROUND(M86*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>1146</v>
+        <v>1409</v>
       </c>
       <c r="P86" s="25">
         <f t="shared" si="17"/>
-        <v>4331</v>
+        <v>3523</v>
       </c>
       <c r="Q86" s="27">
         <f t="shared" si="18"/>
-        <v>490.84666666666664</v>
+        <v>490.87133333333333</v>
       </c>
       <c r="R86" s="26">
         <f t="shared" si="20"/>
-        <v>220.15755555555558</v>
+        <v>220.17790999999997</v>
       </c>
     </row>
     <row r="87" spans="1:18">
@@ -9011,8 +9011,8 @@
         <v>260</v>
       </c>
       <c r="J87" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A87,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.3520000000000003</v>
       </c>
       <c r="K87" s="27">
         <f>ตั้งค่า!$C$10*A87^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -9020,31 +9020,31 @@
       </c>
       <c r="L87" s="25">
         <f t="shared" si="15"/>
-        <v>4437.261263536936</v>
+        <v>3612.7127145655131</v>
       </c>
       <c r="M87" s="25">
         <f t="shared" si="16"/>
-        <v>1933</v>
+        <v>2374</v>
       </c>
       <c r="N87" s="25">
         <f>MAX(1,ROUND(M87*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>773</v>
+        <v>950</v>
       </c>
       <c r="O87" s="25">
         <f>MAX(1,ROUND(M87*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>1160</v>
+        <v>1424</v>
       </c>
       <c r="P87" s="25">
         <f t="shared" si="17"/>
-        <v>4438</v>
+        <v>3613</v>
       </c>
       <c r="Q87" s="27">
         <f t="shared" si="18"/>
-        <v>502.9733333333333</v>
+        <v>502.92960000000005</v>
       </c>
       <c r="R87" s="26">
         <f t="shared" si="20"/>
-        <v>228.33833333333337</v>
+        <v>228.35909888888887</v>
       </c>
     </row>
     <row r="88" spans="1:18">
@@ -9084,8 +9084,8 @@
         <v>267</v>
       </c>
       <c r="J88" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A88,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.347999999999999</v>
       </c>
       <c r="K88" s="27">
         <f>ตั้งค่า!$C$10*A88^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -9093,31 +9093,31 @@
       </c>
       <c r="L88" s="25">
         <f t="shared" si="15"/>
-        <v>4544.6989922876419</v>
+        <v>3701.9589299899339</v>
       </c>
       <c r="M88" s="25">
         <f t="shared" si="16"/>
-        <v>1956</v>
+        <v>2402</v>
       </c>
       <c r="N88" s="25">
         <f>MAX(1,ROUND(M88*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>782</v>
+        <v>961</v>
       </c>
       <c r="O88" s="25">
         <f>MAX(1,ROUND(M88*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>1174</v>
+        <v>1441</v>
       </c>
       <c r="P88" s="25">
         <f t="shared" si="17"/>
-        <v>4546</v>
+        <v>3702</v>
       </c>
       <c r="Q88" s="27">
         <f t="shared" si="18"/>
-        <v>515.21333333333337</v>
+        <v>515.07159999999988</v>
       </c>
       <c r="R88" s="26">
         <f t="shared" si="20"/>
-        <v>236.72122222222225</v>
+        <v>236.74125888888886</v>
       </c>
     </row>
     <row r="89" spans="1:18">
@@ -9157,8 +9157,8 @@
         <v>274</v>
       </c>
       <c r="J89" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A89,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.3440000000000012</v>
       </c>
       <c r="K89" s="27">
         <f>ตั้งค่า!$C$10*A89^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -9166,31 +9166,31 @@
       </c>
       <c r="L89" s="25">
         <f t="shared" si="15"/>
-        <v>4653.4234004245827</v>
+        <v>3792.3393004418936</v>
       </c>
       <c r="M89" s="25">
         <f t="shared" si="16"/>
-        <v>1980</v>
+        <v>2429</v>
       </c>
       <c r="N89" s="25">
         <f>MAX(1,ROUND(M89*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>792</v>
+        <v>972</v>
       </c>
       <c r="O89" s="25">
         <f>MAX(1,ROUND(M89*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>1188</v>
+        <v>1457</v>
       </c>
       <c r="P89" s="25">
         <f t="shared" si="17"/>
-        <v>4653</v>
+        <v>3793</v>
       </c>
       <c r="Q89" s="27">
         <f t="shared" si="18"/>
-        <v>527.33999999999992</v>
+        <v>527.47986666666679</v>
       </c>
       <c r="R89" s="26">
         <f t="shared" si="20"/>
-        <v>245.30811111111115</v>
+        <v>245.32578555555554</v>
       </c>
     </row>
     <row r="90" spans="1:18">
@@ -9230,8 +9230,8 @@
         <v>281</v>
       </c>
       <c r="J90" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A90,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.34</v>
       </c>
       <c r="K90" s="27">
         <f>ตั้งค่า!$C$10*A90^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -9239,31 +9239,31 @@
       </c>
       <c r="L90" s="25">
         <f t="shared" si="15"/>
-        <v>4763.4344879477603</v>
+        <v>3883.8554577991331</v>
       </c>
       <c r="M90" s="25">
         <f t="shared" si="16"/>
-        <v>2003</v>
+        <v>2457</v>
       </c>
       <c r="N90" s="25">
         <f>MAX(1,ROUND(M90*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>801</v>
+        <v>983</v>
       </c>
       <c r="O90" s="25">
         <f>MAX(1,ROUND(M90*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>1202</v>
+        <v>1474</v>
       </c>
       <c r="P90" s="25">
         <f t="shared" si="17"/>
-        <v>4764</v>
+        <v>3884</v>
       </c>
       <c r="Q90" s="27">
         <f t="shared" si="18"/>
-        <v>539.91999999999996</v>
+        <v>539.87599999999998</v>
       </c>
       <c r="R90" s="26">
         <f t="shared" si="20"/>
-        <v>254.09711111111113</v>
+        <v>254.11711666666665</v>
       </c>
     </row>
     <row r="91" spans="1:18">
@@ -9303,8 +9303,8 @@
         <v>288</v>
       </c>
       <c r="J91" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A91,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.34</v>
       </c>
       <c r="K91" s="27">
         <f>ตั้งค่า!$C$10*A91^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -9312,31 +9312,31 @@
       </c>
       <c r="L91" s="25">
         <f t="shared" si="15"/>
-        <v>4874.7322548571738</v>
+        <v>3974.6018384926601</v>
       </c>
       <c r="M91" s="25">
         <f t="shared" si="16"/>
-        <v>2026</v>
+        <v>2485</v>
       </c>
       <c r="N91" s="25">
         <f>MAX(1,ROUND(M91*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>810</v>
+        <v>994</v>
       </c>
       <c r="O91" s="25">
         <f>MAX(1,ROUND(M91*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>1216</v>
+        <v>1491</v>
       </c>
       <c r="P91" s="25">
         <f t="shared" si="17"/>
-        <v>4876</v>
+        <v>3975</v>
       </c>
       <c r="Q91" s="27">
         <f t="shared" si="18"/>
-        <v>552.61333333333323</v>
+        <v>552.52499999999998</v>
       </c>
       <c r="R91" s="26">
         <f t="shared" si="20"/>
-        <v>263.09577777777781</v>
+        <v>263.11505</v>
       </c>
     </row>
     <row r="92" spans="1:18">
@@ -9376,8 +9376,8 @@
         <v>295</v>
       </c>
       <c r="J92" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A92,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.3360000000000003</v>
       </c>
       <c r="K92" s="27">
         <f>ตั้งค่า!$C$10*A92^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -9385,31 +9385,31 @@
       </c>
       <c r="L92" s="25">
         <f t="shared" si="15"/>
-        <v>4987.316701152823</v>
+        <v>4068.3485566025902</v>
       </c>
       <c r="M92" s="25">
         <f t="shared" si="16"/>
-        <v>2050</v>
+        <v>2513</v>
       </c>
       <c r="N92" s="25">
         <f>MAX(1,ROUND(M92*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>820</v>
+        <v>1005</v>
       </c>
       <c r="O92" s="25">
         <f>MAX(1,ROUND(M92*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>1230</v>
+        <v>1508</v>
       </c>
       <c r="P92" s="25">
         <f t="shared" si="17"/>
-        <v>4987</v>
+        <v>4068</v>
       </c>
       <c r="Q92" s="27">
         <f t="shared" si="18"/>
-        <v>565.19333333333327</v>
+        <v>565.18079999999998</v>
       </c>
       <c r="R92" s="26">
         <f t="shared" si="20"/>
-        <v>272.30600000000004</v>
+        <v>272.32380000000001</v>
       </c>
     </row>
     <row r="93" spans="1:18">
@@ -9449,8 +9449,8 @@
         <v>303</v>
       </c>
       <c r="J93" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A93,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.3279999999999994</v>
       </c>
       <c r="K93" s="27">
         <f>ตั้งค่า!$C$10*A93^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -9458,31 +9458,31 @@
       </c>
       <c r="L93" s="25">
         <f t="shared" si="15"/>
-        <v>5101.1878268347091</v>
+        <v>4165.2350171080725</v>
       </c>
       <c r="M93" s="25">
         <f t="shared" si="16"/>
-        <v>2073</v>
+        <v>2539</v>
       </c>
       <c r="N93" s="25">
         <f>MAX(1,ROUND(M93*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>829</v>
+        <v>1016</v>
       </c>
       <c r="O93" s="25">
         <f>MAX(1,ROUND(M93*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>1244</v>
+        <v>1523</v>
       </c>
       <c r="P93" s="25">
         <f t="shared" si="17"/>
-        <v>5102</v>
+        <v>4165</v>
       </c>
       <c r="Q93" s="27">
         <f t="shared" si="18"/>
-        <v>578.22666666666669</v>
+        <v>578.10199999999998</v>
       </c>
       <c r="R93" s="26">
         <f t="shared" si="20"/>
-        <v>281.7258888888889</v>
+        <v>281.74347999999998</v>
       </c>
     </row>
     <row r="94" spans="1:18">
@@ -9522,8 +9522,8 @@
         <v>310</v>
       </c>
       <c r="J94" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A94,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.3239999999999998</v>
       </c>
       <c r="K94" s="27">
         <f>ตั้งค่า!$C$10*A94^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -9531,31 +9531,31 @@
       </c>
       <c r="L94" s="25">
         <f t="shared" si="15"/>
-        <v>5216.3456319028301</v>
+        <v>4261.3107036207648</v>
       </c>
       <c r="M94" s="25">
         <f t="shared" si="16"/>
-        <v>2096</v>
+        <v>2566</v>
       </c>
       <c r="N94" s="25">
         <f>MAX(1,ROUND(M94*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>838</v>
+        <v>1026</v>
       </c>
       <c r="O94" s="25">
         <f>MAX(1,ROUND(M94*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>1258</v>
+        <v>1540</v>
       </c>
       <c r="P94" s="25">
         <f t="shared" si="17"/>
-        <v>5218</v>
+        <v>4262</v>
       </c>
       <c r="Q94" s="27">
         <f t="shared" si="18"/>
-        <v>591.37333333333333</v>
+        <v>591.28146666666669</v>
       </c>
       <c r="R94" s="26">
         <f t="shared" si="20"/>
-        <v>291.363</v>
+        <v>291.37851333333333</v>
       </c>
     </row>
     <row r="95" spans="1:18">
@@ -9595,8 +9595,8 @@
         <v>318</v>
       </c>
       <c r="J95" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A95,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.32</v>
       </c>
       <c r="K95" s="27">
         <f>ตั้งค่า!$C$10*A95^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -9604,31 +9604,31 @@
       </c>
       <c r="L95" s="25">
         <f t="shared" si="15"/>
-        <v>5332.7901163571869</v>
+        <v>4358.5303835611621</v>
       </c>
       <c r="M95" s="25">
         <f t="shared" si="16"/>
-        <v>2120</v>
+        <v>2593</v>
       </c>
       <c r="N95" s="25">
         <f>MAX(1,ROUND(M95*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>848</v>
+        <v>1037</v>
       </c>
       <c r="O95" s="25">
         <f>MAX(1,ROUND(M95*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>1272</v>
+        <v>1556</v>
       </c>
       <c r="P95" s="25">
         <f t="shared" si="17"/>
-        <v>5332</v>
+        <v>4360</v>
       </c>
       <c r="Q95" s="27">
         <f t="shared" si="18"/>
-        <v>604.29333333333329</v>
+        <v>604.5866666666667</v>
       </c>
       <c r="R95" s="26">
         <f t="shared" si="20"/>
-        <v>301.21922222222224</v>
+        <v>301.23320444444443</v>
       </c>
     </row>
     <row r="96" spans="1:18">
@@ -9668,8 +9668,8 @@
         <v>326</v>
       </c>
       <c r="J96" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A96,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.3159999999999989</v>
       </c>
       <c r="K96" s="27">
         <f>ตั้งค่า!$C$10*A96^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -9677,31 +9677,31 @@
       </c>
       <c r="L96" s="25">
         <f t="shared" si="15"/>
-        <v>5450.5212801977814</v>
+        <v>4456.8957077134337</v>
       </c>
       <c r="M96" s="25">
         <f t="shared" si="16"/>
-        <v>2143</v>
+        <v>2621</v>
       </c>
       <c r="N96" s="25">
         <f>MAX(1,ROUND(M96*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>857</v>
+        <v>1048</v>
       </c>
       <c r="O96" s="25">
         <f>MAX(1,ROUND(M96*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>1286</v>
+        <v>1573</v>
       </c>
       <c r="P96" s="25">
         <f t="shared" si="17"/>
-        <v>5451</v>
+        <v>4457</v>
       </c>
       <c r="Q96" s="27">
         <f t="shared" si="18"/>
-        <v>617.78</v>
+        <v>617.74019999999996</v>
       </c>
       <c r="R96" s="26">
         <f t="shared" si="20"/>
-        <v>311.29077777777781</v>
+        <v>311.30964888888889</v>
       </c>
     </row>
     <row r="97" spans="1:18">
@@ -9741,8 +9741,8 @@
         <v>334</v>
       </c>
       <c r="J97" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A97,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.3120000000000012</v>
       </c>
       <c r="K97" s="27">
         <f>ตั้งค่า!$C$10*A97^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -9750,31 +9750,31 @@
       </c>
       <c r="L97" s="25">
         <f t="shared" si="15"/>
-        <v>5569.539123424609</v>
+        <v>4556.4083300393813</v>
       </c>
       <c r="M97" s="25">
         <f t="shared" si="16"/>
-        <v>2166</v>
+        <v>2648</v>
       </c>
       <c r="N97" s="25">
         <f>MAX(1,ROUND(M97*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>866</v>
+        <v>1059</v>
       </c>
       <c r="O97" s="25">
         <f>MAX(1,ROUND(M97*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>1300</v>
+        <v>1589</v>
       </c>
       <c r="P97" s="25">
         <f t="shared" si="17"/>
-        <v>5571</v>
+        <v>4557</v>
       </c>
       <c r="Q97" s="27">
         <f t="shared" si="18"/>
-        <v>631.37999999999988</v>
+        <v>631.29640000000006</v>
       </c>
       <c r="R97" s="26">
         <f t="shared" si="20"/>
-        <v>321.58711111111114</v>
+        <v>321.60531888888886</v>
       </c>
     </row>
     <row r="98" spans="1:18">
@@ -9814,8 +9814,8 @@
         <v>343</v>
       </c>
       <c r="J98" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A98,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.3040000000000003</v>
       </c>
       <c r="K98" s="27">
         <f>ตั้งค่า!$C$10*A98^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -9823,31 +9823,31 @@
       </c>
       <c r="L98" s="25">
         <f t="shared" si="15"/>
-        <v>5689.8436460376743</v>
+        <v>4659.3131976223731</v>
       </c>
       <c r="M98" s="25">
         <f t="shared" si="16"/>
-        <v>2190</v>
+        <v>2674</v>
       </c>
       <c r="N98" s="25">
         <f>MAX(1,ROUND(M98*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>876</v>
+        <v>1070</v>
       </c>
       <c r="O98" s="25">
         <f>MAX(1,ROUND(M98*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>1314</v>
+        <v>1604</v>
       </c>
       <c r="P98" s="25">
         <f t="shared" si="17"/>
-        <v>5689</v>
+        <v>4660</v>
       </c>
       <c r="Q98" s="27">
         <f t="shared" si="18"/>
-        <v>644.75333333333333</v>
+        <v>644.94399999999996</v>
       </c>
       <c r="R98" s="26">
         <f t="shared" si="20"/>
-        <v>332.11011111111117</v>
+        <v>332.12692555555554</v>
       </c>
     </row>
     <row r="99" spans="1:18">
@@ -9887,8 +9887,8 @@
         <v>351</v>
       </c>
       <c r="J99" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A99,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.3000000000000007</v>
       </c>
       <c r="K99" s="27">
         <f>ตั้งค่า!$C$10*A99^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -9896,31 +9896,31 @@
       </c>
       <c r="L99" s="25">
         <f t="shared" si="15"/>
-        <v>5811.4348480369772</v>
+        <v>4761.1755381507764</v>
       </c>
       <c r="M99" s="25">
         <f t="shared" si="16"/>
-        <v>2213</v>
+        <v>2701</v>
       </c>
       <c r="N99" s="25">
         <f>MAX(1,ROUND(M99*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>885</v>
+        <v>1080</v>
       </c>
       <c r="O99" s="25">
         <f>MAX(1,ROUND(M99*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>1328</v>
+        <v>1621</v>
       </c>
       <c r="P99" s="25">
         <f t="shared" si="17"/>
-        <v>5812</v>
+        <v>4762</v>
       </c>
       <c r="Q99" s="27">
         <f t="shared" si="18"/>
-        <v>658.69333333333327</v>
+        <v>658.74333333333345</v>
       </c>
       <c r="R99" s="26">
         <f t="shared" si="20"/>
-        <v>342.85600000000005</v>
+        <v>342.87599222222224</v>
       </c>
     </row>
     <row r="100" spans="1:18">
@@ -9960,8 +9960,8 @@
         <v>360</v>
       </c>
       <c r="J100" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A100,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.3000000000000007</v>
       </c>
       <c r="K100" s="27">
         <f>ตั้งค่า!$C$10*A100^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -9969,31 +9969,31 @@
       </c>
       <c r="L100" s="25">
         <f t="shared" si="15"/>
-        <v>5934.3127294225142</v>
+        <v>4861.8465735027821</v>
       </c>
       <c r="M100" s="25">
         <f t="shared" si="16"/>
-        <v>2236</v>
+        <v>2730</v>
       </c>
       <c r="N100" s="25">
         <f>MAX(1,ROUND(M100*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>894</v>
+        <v>1092</v>
       </c>
       <c r="O100" s="25">
         <f>MAX(1,ROUND(M100*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>1342</v>
+        <v>1638</v>
       </c>
       <c r="P100" s="25">
         <f t="shared" si="17"/>
-        <v>5936</v>
+        <v>4862</v>
       </c>
       <c r="Q100" s="27">
         <f t="shared" si="18"/>
-        <v>672.74666666666656</v>
+        <v>672.57666666666671</v>
       </c>
       <c r="R100" s="26">
         <f t="shared" si="20"/>
-        <v>353.83422222222225</v>
+        <v>353.85504777777777</v>
       </c>
     </row>
     <row r="101" spans="1:18">
@@ -10033,8 +10033,8 @@
         <v>369</v>
       </c>
       <c r="J101" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A101,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.2959999999999994</v>
       </c>
       <c r="K101" s="27">
         <f>ตั้งค่า!$C$10*A101^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -10042,31 +10042,31 @@
       </c>
       <c r="L101" s="25">
         <f t="shared" ref="L101:L132" si="22">K101*60/J101</f>
-        <v>6058.4772901942879</v>
+        <v>4965.9649919625308</v>
       </c>
       <c r="M101" s="25">
         <f t="shared" ref="M101:M132" si="23">MAX(1,ROUND(B101/L101,0))</f>
-        <v>2260</v>
+        <v>2757</v>
       </c>
       <c r="N101" s="25">
         <f>MAX(1,ROUND(M101*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>904</v>
+        <v>1103</v>
       </c>
       <c r="O101" s="25">
         <f>MAX(1,ROUND(M101*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>1356</v>
+        <v>1654</v>
       </c>
       <c r="P101" s="25">
         <f t="shared" si="17"/>
-        <v>6058</v>
+        <v>4966</v>
       </c>
       <c r="Q101" s="27">
         <f t="shared" ref="Q101:Q132" si="24">P101*J101/60</f>
-        <v>686.57333333333338</v>
+        <v>686.63226666666662</v>
       </c>
       <c r="R101" s="26">
         <f t="shared" si="20"/>
-        <v>365.04666666666668</v>
+        <v>365.06465888888886</v>
       </c>
     </row>
     <row r="102" spans="1:18">
@@ -10106,8 +10106,8 @@
         <v>378</v>
       </c>
       <c r="J102" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A102,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.2919999999999998</v>
       </c>
       <c r="K102" s="27">
         <f>ตั้งค่า!$C$10*A102^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -10115,31 +10115,31 @@
       </c>
       <c r="L102" s="25">
         <f t="shared" si="22"/>
-        <v>6183.9285303522965</v>
+        <v>5071.2390263381112</v>
       </c>
       <c r="M102" s="25">
         <f t="shared" si="23"/>
-        <v>2283</v>
+        <v>2784</v>
       </c>
       <c r="N102" s="25">
         <f>MAX(1,ROUND(M102*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>913</v>
+        <v>1114</v>
       </c>
       <c r="O102" s="25">
         <f>MAX(1,ROUND(M102*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>1370</v>
+        <v>1670</v>
       </c>
       <c r="P102" s="25">
         <f t="shared" si="17"/>
-        <v>6184</v>
+        <v>5072</v>
       </c>
       <c r="Q102" s="27">
         <f t="shared" si="24"/>
-        <v>700.85333333333324</v>
+        <v>700.95039999999995</v>
       </c>
       <c r="R102" s="26">
         <f t="shared" si="20"/>
-        <v>376.48955555555557</v>
+        <v>376.50852999999995</v>
       </c>
     </row>
     <row r="103" spans="1:18">
@@ -10179,8 +10179,8 @@
         <v>387</v>
       </c>
       <c r="J103" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A103,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.2880000000000003</v>
       </c>
       <c r="K103" s="27">
         <f>ตั้งค่า!$C$10*A103^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -10188,31 +10188,31 @@
       </c>
       <c r="L103" s="25">
         <f t="shared" si="22"/>
-        <v>6310.666449896542</v>
+        <v>5177.6703498185907</v>
       </c>
       <c r="M103" s="25">
         <f t="shared" si="23"/>
-        <v>2306</v>
+        <v>2811</v>
       </c>
       <c r="N103" s="25">
         <f>MAX(1,ROUND(M103*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>922</v>
+        <v>1124</v>
       </c>
       <c r="O103" s="25">
         <f>MAX(1,ROUND(M103*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>1384</v>
+        <v>1687</v>
       </c>
       <c r="P103" s="25">
         <f t="shared" si="17"/>
-        <v>6312</v>
+        <v>5178</v>
       </c>
       <c r="Q103" s="27">
         <f t="shared" si="24"/>
-        <v>715.36</v>
+        <v>715.25440000000003</v>
       </c>
       <c r="R103" s="26">
         <f t="shared" si="20"/>
-        <v>388.17044444444446</v>
+        <v>388.19103666666661</v>
       </c>
     </row>
     <row r="104" spans="1:18">
@@ -10252,8 +10252,8 @@
         <v>397</v>
       </c>
       <c r="J104" s="27">
-        <f>ตั้งค่า!$C$20*ตั้งค่า!$C$18+ตั้งค่า!$C$21</f>
-        <v>6.8</v>
+        <f>ตั้งค่า!$C$20*INDEX(สายเลี้ยงตัว!$K$5:$K$104,MIN(A104,100))/1000+ตั้งค่า!$C$21</f>
+        <v>8.2800000000000011</v>
       </c>
       <c r="K104" s="27">
         <f>ตั้งค่า!$C$10*A104^ตั้งค่า!$C$8+ตั้งค่า!$C$9</f>
@@ -10261,31 +10261,31 @@
       </c>
       <c r="L104" s="25">
         <f t="shared" si="22"/>
-        <v>6438.6910488270232</v>
+        <v>5287.8139048337862</v>
       </c>
       <c r="M104" s="25">
         <f t="shared" si="23"/>
-        <v>2330</v>
+        <v>2837</v>
       </c>
       <c r="N104" s="25">
         <f>MAX(1,ROUND(M104*ตั้งค่า!$C$26*(1-ตั้งค่า!$C$27),0))</f>
-        <v>932</v>
+        <v>1135</v>
       </c>
       <c r="O104" s="25">
         <f>MAX(1,ROUND(M104*ตั้งค่า!$C$26*(1+ตั้งค่า!$C$27),0))</f>
-        <v>1398</v>
+        <v>1702</v>
       </c>
       <c r="P104" s="25">
         <f t="shared" si="17"/>
-        <v>6438</v>
+        <v>5288</v>
       </c>
       <c r="Q104" s="27">
         <f t="shared" si="24"/>
-        <v>729.64</v>
+        <v>729.74400000000014</v>
       </c>
       <c r="R104" s="26">
         <f t="shared" si="20"/>
-        <v>400.09311111111111</v>
+        <v>400.11194333333327</v>
       </c>
     </row>
   </sheetData>
@@ -10516,15 +10516,15 @@
       </c>
       <c r="K6" s="25">
         <f>ROUND(INDEX(เลเวล!$M$5:$M$104,C6)*G6*IF(D6="บอส",ตั้งค่า!$C$30,1),0)</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L6" s="25">
         <f>ROUND(INDEX(เลเวล!$N$5:$N$104,C6)*IF(D6="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M6" s="25">
         <f>ROUND(INDEX(เลเวล!$O$5:$O$104,C6)*IF(D6="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N6" s="25">
         <f>ROUNDUP(H6/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C6,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C6,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C6,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C6,100))*(1-T6/100)-U6)),0)</f>
@@ -10688,15 +10688,15 @@
       </c>
       <c r="K8" s="25">
         <f>ROUND(INDEX(เลเวล!$M$5:$M$104,C8)*G8*IF(D8="บอส",ตั้งค่า!$C$30,1),0)</f>
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="L8" s="25">
         <f>ROUND(INDEX(เลเวล!$N$5:$N$104,C8)*IF(D8="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="M8" s="25">
         <f>ROUND(INDEX(เลเวล!$O$5:$O$104,C8)*IF(D8="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="N8" s="25">
         <f>ROUNDUP(H8/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C8,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C8,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C8,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C8,100))*(1-T8/100)-U8)),0)</f>
@@ -10774,15 +10774,15 @@
       </c>
       <c r="K9" s="25">
         <f>ROUND(INDEX(เลเวล!$M$5:$M$104,C9)*G9*IF(D9="บอส",ตั้งค่า!$C$30,1),0)</f>
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="L9" s="25">
         <f>ROUND(INDEX(เลเวล!$N$5:$N$104,C9)*IF(D9="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="M9" s="25">
         <f>ROUND(INDEX(เลเวล!$O$5:$O$104,C9)*IF(D9="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="N9" s="25">
         <f>ROUNDUP(H9/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C9,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C9,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C9,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C9,100))*(1-T9/100)-U9)),0)</f>
@@ -10860,15 +10860,15 @@
       </c>
       <c r="K10" s="25">
         <f>ROUND(INDEX(เลเวล!$M$5:$M$104,C10)*G10*IF(D10="บอส",ตั้งค่า!$C$30,1),0)</f>
-        <v>161</v>
+        <v>205</v>
       </c>
       <c r="L10" s="25">
         <f>ROUND(INDEX(เลเวล!$N$5:$N$104,C10)*IF(D10="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="M10" s="25">
         <f>ROUND(INDEX(เลเวล!$O$5:$O$104,C10)*IF(D10="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="N10" s="25">
         <f>ROUNDUP(H10/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C10,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C10,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C10,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C10,100))*(1-T10/100)-U10)),0)</f>
@@ -10946,15 +10946,15 @@
       </c>
       <c r="K11" s="25">
         <f>ROUND(INDEX(เลเวล!$M$5:$M$104,C11)*G11*IF(D11="บอส",ตั้งค่า!$C$30,1),0)</f>
-        <v>165</v>
+        <v>210</v>
       </c>
       <c r="L11" s="25">
         <f>ROUND(INDEX(เลเวล!$N$5:$N$104,C11)*IF(D11="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="M11" s="25">
         <f>ROUND(INDEX(เลเวล!$O$5:$O$104,C11)*IF(D11="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="N11" s="25">
         <f>ROUNDUP(H11/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C11,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C11,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C11,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C11,100))*(1-T11/100)-U11)),0)</f>
@@ -11032,15 +11032,15 @@
       </c>
       <c r="K12" s="25">
         <f>ROUND(INDEX(เลเวล!$M$5:$M$104,C12)*G12*IF(D12="บอส",ตั้งค่า!$C$30,1),0)</f>
-        <v>5375</v>
+        <v>6850</v>
       </c>
       <c r="L12" s="25">
         <f>ROUND(INDEX(เลเวล!$N$5:$N$104,C12)*IF(D12="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>1720</v>
+        <v>2200</v>
       </c>
       <c r="M12" s="25">
         <f>ROUND(INDEX(เลเวล!$O$5:$O$104,C12)*IF(D12="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>2580</v>
+        <v>3280</v>
       </c>
       <c r="N12" s="25">
         <f>ROUNDUP(H12/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C12,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C12,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C12,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C12,100))*(1-T12/100)-U12)),0)</f>
@@ -11118,15 +11118,15 @@
       </c>
       <c r="K13" s="25">
         <f>ROUND(INDEX(เลเวล!$M$5:$M$104,C13)*G13*IF(D13="บอส",ตั้งค่า!$C$30,1),0)</f>
-        <v>216</v>
+        <v>275</v>
       </c>
       <c r="L13" s="25">
         <f>ROUND(INDEX(เลเวล!$N$5:$N$104,C13)*IF(D13="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>96</v>
+        <v>122</v>
       </c>
       <c r="M13" s="25">
         <f>ROUND(INDEX(เลเวล!$O$5:$O$104,C13)*IF(D13="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>144</v>
+        <v>183</v>
       </c>
       <c r="N13" s="25">
         <f>ROUNDUP(H13/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C13,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C13,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C13,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C13,100))*(1-T13/100)-U13)),0)</f>
@@ -11204,15 +11204,15 @@
       </c>
       <c r="K14" s="25">
         <f>ROUND(INDEX(เลเวล!$M$5:$M$104,C14)*G14*IF(D14="บอส",ตั้งค่า!$C$30,1),0)</f>
-        <v>303</v>
+        <v>385</v>
       </c>
       <c r="L14" s="25">
         <f>ROUND(INDEX(เลเวล!$N$5:$N$104,C14)*IF(D14="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>116</v>
+        <v>147</v>
       </c>
       <c r="M14" s="25">
         <f>ROUND(INDEX(เลเวล!$O$5:$O$104,C14)*IF(D14="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>173</v>
+        <v>220</v>
       </c>
       <c r="N14" s="25">
         <f>ROUNDUP(H14/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C14,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C14,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C14,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C14,100))*(1-T14/100)-U14)),0)</f>
@@ -11290,15 +11290,15 @@
       </c>
       <c r="K15" s="25">
         <f>ROUND(INDEX(เลเวล!$M$5:$M$104,C15)*G15*IF(D15="บอส",ตั้งค่า!$C$30,1),0)</f>
-        <v>329</v>
+        <v>418</v>
       </c>
       <c r="L15" s="25">
         <f>ROUND(INDEX(เลเวล!$N$5:$N$104,C15)*IF(D15="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>125</v>
+        <v>159</v>
       </c>
       <c r="M15" s="25">
         <f>ROUND(INDEX(เลเวล!$O$5:$O$104,C15)*IF(D15="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>188</v>
+        <v>239</v>
       </c>
       <c r="N15" s="25">
         <f>ROUNDUP(H15/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C15,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C15,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C15,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C15,100))*(1-T15/100)-U15)),0)</f>
@@ -11376,15 +11376,15 @@
       </c>
       <c r="K16" s="25">
         <f>ROUND(INDEX(เลเวล!$M$5:$M$104,C16)*G16*IF(D16="บอส",ตั้งค่า!$C$30,1),0)</f>
-        <v>397</v>
+        <v>505</v>
       </c>
       <c r="L16" s="25">
         <f>ROUND(INDEX(เลเวล!$N$5:$N$104,C16)*IF(D16="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>144</v>
+        <v>184</v>
       </c>
       <c r="M16" s="25">
         <f>ROUND(INDEX(เลเวล!$O$5:$O$104,C16)*IF(D16="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="N16" s="25">
         <f>ROUNDUP(H16/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C16,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C16,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C16,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C16,100))*(1-T16/100)-U16)),0)</f>
@@ -11462,15 +11462,15 @@
       </c>
       <c r="K17" s="25">
         <f>ROUND(INDEX(เลเวล!$M$5:$M$104,C17)*G17*IF(D17="บอส",ตั้งค่า!$C$30,1),0)</f>
-        <v>511</v>
+        <v>649</v>
       </c>
       <c r="L17" s="25">
         <f>ROUND(INDEX(เลเวล!$N$5:$N$104,C17)*IF(D17="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>164</v>
+        <v>208</v>
       </c>
       <c r="M17" s="25">
         <f>ROUND(INDEX(เลเวล!$O$5:$O$104,C17)*IF(D17="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>245</v>
+        <v>311</v>
       </c>
       <c r="N17" s="25">
         <f>ROUNDUP(H17/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C17,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C17,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C17,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C17,100))*(1-T17/100)-U17)),0)</f>
@@ -11548,15 +11548,15 @@
       </c>
       <c r="K18" s="25">
         <f>ROUND(INDEX(เลเวล!$M$5:$M$104,C18)*G18*IF(D18="บอส",ตั้งค่า!$C$30,1),0)</f>
-        <v>11425</v>
+        <v>14475</v>
       </c>
       <c r="L18" s="25">
         <f>ROUND(INDEX(เลเวล!$N$5:$N$104,C18)*IF(D18="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>3660</v>
+        <v>4640</v>
       </c>
       <c r="M18" s="25">
         <f>ROUND(INDEX(เลเวล!$O$5:$O$104,C18)*IF(D18="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>5480</v>
+        <v>6940</v>
       </c>
       <c r="N18" s="25">
         <f>ROUNDUP(H18/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C18,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C18,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C18,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C18,100))*(1-T18/100)-U18)),0)</f>
@@ -11634,15 +11634,15 @@
       </c>
       <c r="K19" s="25">
         <f>ROUND(INDEX(เลเวล!$M$5:$M$104,C19)*G19*IF(D19="บอส",ตั้งค่า!$C$30,1),0)</f>
-        <v>554</v>
+        <v>702</v>
       </c>
       <c r="L19" s="25">
         <f>ROUND(INDEX(เลเวล!$N$5:$N$104,C19)*IF(D19="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>202</v>
+        <v>255</v>
       </c>
       <c r="M19" s="25">
         <f>ROUND(INDEX(เลเวล!$O$5:$O$104,C19)*IF(D19="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>302</v>
+        <v>383</v>
       </c>
       <c r="N19" s="25">
         <f>ROUNDUP(H19/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C19,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C19,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C19,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C19,100))*(1-T19/100)-U19)),0)</f>
@@ -11720,15 +11720,15 @@
       </c>
       <c r="K20" s="25">
         <f>ROUND(INDEX(เลเวล!$M$5:$M$104,C20)*G20*IF(D20="บอส",ตั้งค่า!$C$30,1),0)</f>
-        <v>497</v>
+        <v>628</v>
       </c>
       <c r="L20" s="25">
         <f>ROUND(INDEX(เลเวล!$N$5:$N$104,C20)*IF(D20="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>221</v>
+        <v>279</v>
       </c>
       <c r="M20" s="25">
         <f>ROUND(INDEX(เลเวล!$O$5:$O$104,C20)*IF(D20="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>331</v>
+        <v>419</v>
       </c>
       <c r="N20" s="25">
         <f>ROUNDUP(H20/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C20,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C20,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C20,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C20,100))*(1-T20/100)-U20)),0)</f>
@@ -11806,15 +11806,15 @@
       </c>
       <c r="K21" s="25">
         <f>ROUND(INDEX(เลเวล!$M$5:$M$104,C21)*G21*IF(D21="บอส",ตั้งค่า!$C$30,1),0)</f>
-        <v>629</v>
+        <v>794</v>
       </c>
       <c r="L21" s="25">
         <f>ROUND(INDEX(เลเวล!$N$5:$N$104,C21)*IF(D21="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>240</v>
+        <v>302</v>
       </c>
       <c r="M21" s="25">
         <f>ROUND(INDEX(เลเวล!$O$5:$O$104,C21)*IF(D21="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>359</v>
+        <v>454</v>
       </c>
       <c r="N21" s="25">
         <f>ROUNDUP(H21/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C21,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C21,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C21,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C21,100))*(1-T21/100)-U21)),0)</f>
@@ -11892,15 +11892,15 @@
       </c>
       <c r="K22" s="25">
         <f>ROUND(INDEX(เลเวล!$M$5:$M$104,C22)*G22*IF(D22="บอส",ตั้งค่า!$C$30,1),0)</f>
-        <v>737</v>
+        <v>930</v>
       </c>
       <c r="L22" s="25">
         <f>ROUND(INDEX(เลเวล!$N$5:$N$104,C22)*IF(D22="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>268</v>
+        <v>338</v>
       </c>
       <c r="M22" s="25">
         <f>ROUND(INDEX(เลเวล!$O$5:$O$104,C22)*IF(D22="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>402</v>
+        <v>507</v>
       </c>
       <c r="N22" s="25">
         <f>ROUNDUP(H22/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C22,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C22,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C22,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C22,100))*(1-T22/100)-U22)),0)</f>
@@ -11978,15 +11978,15 @@
       </c>
       <c r="K23" s="25">
         <f>ROUND(INDEX(เลเวล!$M$5:$M$104,C23)*G23*IF(D23="บอส",ตั้งค่า!$C$30,1),0)</f>
-        <v>999</v>
+        <v>1258</v>
       </c>
       <c r="L23" s="25">
         <f>ROUND(INDEX(เลเวล!$N$5:$N$104,C23)*IF(D23="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>296</v>
+        <v>373</v>
       </c>
       <c r="M23" s="25">
         <f>ROUND(INDEX(เลเวล!$O$5:$O$104,C23)*IF(D23="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>444</v>
+        <v>559</v>
       </c>
       <c r="N23" s="25">
         <f>ROUNDUP(H23/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C23,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C23,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C23,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C23,100))*(1-T23/100)-U23)),0)</f>
@@ -12064,15 +12064,15 @@
       </c>
       <c r="K24" s="25">
         <f>ROUND(INDEX(เลเวล!$M$5:$M$104,C24)*G24*IF(D24="บอส",ตั้งค่า!$C$30,1),0)</f>
-        <v>20275</v>
+        <v>25500</v>
       </c>
       <c r="L24" s="25">
         <f>ROUND(INDEX(เลเวล!$N$5:$N$104,C24)*IF(D24="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>6480</v>
+        <v>8160</v>
       </c>
       <c r="M24" s="25">
         <f>ROUND(INDEX(เลเวล!$O$5:$O$104,C24)*IF(D24="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>9740</v>
+        <v>12240</v>
       </c>
       <c r="N24" s="25">
         <f>ROUNDUP(H24/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C24,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C24,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C24,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C24,100))*(1-T24/100)-U24)),0)</f>
@@ -12150,15 +12150,15 @@
       </c>
       <c r="K25" s="25">
         <f>ROUND(INDEX(เลเวล!$M$5:$M$104,C25)*G25*IF(D25="บอส",ตั้งค่า!$C$30,1),0)</f>
-        <v>925</v>
+        <v>1161</v>
       </c>
       <c r="L25" s="25">
         <f>ROUND(INDEX(เลเวล!$N$5:$N$104,C25)*IF(D25="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>352</v>
+        <v>442</v>
       </c>
       <c r="M25" s="25">
         <f>ROUND(INDEX(เลเวล!$O$5:$O$104,C25)*IF(D25="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>529</v>
+        <v>664</v>
       </c>
       <c r="N25" s="25">
         <f>ROUNDUP(H25/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C25,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C25,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C25,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C25,100))*(1-T25/100)-U25)),0)</f>
@@ -12236,15 +12236,15 @@
       </c>
       <c r="K26" s="25">
         <f>ROUND(INDEX(เลเวล!$M$5:$M$104,C26)*G26*IF(D26="บอส",ตั้งค่า!$C$30,1),0)</f>
-        <v>951</v>
+        <v>1194</v>
       </c>
       <c r="L26" s="25">
         <f>ROUND(INDEX(เลเวล!$N$5:$N$104,C26)*IF(D26="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>380</v>
+        <v>478</v>
       </c>
       <c r="M26" s="25">
         <f>ROUND(INDEX(เลเวล!$O$5:$O$104,C26)*IF(D26="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>571</v>
+        <v>716</v>
       </c>
       <c r="N26" s="25">
         <f>ROUNDUP(H26/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C26,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C26,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C26,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C26,100))*(1-T26/100)-U26)),0)</f>
@@ -12322,15 +12322,15 @@
       </c>
       <c r="K27" s="25">
         <f>ROUND(INDEX(เลเวล!$M$5:$M$104,C27)*G27*IF(D27="บอส",ตั้งค่า!$C$30,1),0)</f>
-        <v>998</v>
+        <v>1251</v>
       </c>
       <c r="L27" s="25">
         <f>ROUND(INDEX(เลเวล!$N$5:$N$104,C27)*IF(D27="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>399</v>
+        <v>500</v>
       </c>
       <c r="M27" s="25">
         <f>ROUND(INDEX(เลเวล!$O$5:$O$104,C27)*IF(D27="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>599</v>
+        <v>751</v>
       </c>
       <c r="N27" s="25">
         <f>ROUNDUP(H27/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C27,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C27,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C27,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C27,100))*(1-T27/100)-U27)),0)</f>
@@ -12408,15 +12408,15 @@
       </c>
       <c r="K28" s="25">
         <f>ROUND(INDEX(เลเวล!$M$5:$M$104,C28)*G28*IF(D28="บอส",ตั้งค่า!$C$30,1),0)</f>
-        <v>1175</v>
+        <v>1471</v>
       </c>
       <c r="L28" s="25">
         <f>ROUND(INDEX(เลเวล!$N$5:$N$104,C28)*IF(D28="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>427</v>
+        <v>535</v>
       </c>
       <c r="M28" s="25">
         <f>ROUND(INDEX(เลเวล!$O$5:$O$104,C28)*IF(D28="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>641</v>
+        <v>802</v>
       </c>
       <c r="N28" s="25">
         <f>ROUNDUP(H28/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C28,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C28,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C28,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C28,100))*(1-T28/100)-U28)),0)</f>
@@ -12494,15 +12494,15 @@
       </c>
       <c r="K29" s="25">
         <f>ROUND(INDEX(เลเวล!$M$5:$M$104,C29)*G29*IF(D29="บอส",ตั้งค่า!$C$30,1),0)</f>
-        <v>1511</v>
+        <v>1886</v>
       </c>
       <c r="L29" s="25">
         <f>ROUND(INDEX(เลเวล!$N$5:$N$104,C29)*IF(D29="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>465</v>
+        <v>580</v>
       </c>
       <c r="M29" s="25">
         <f>ROUND(INDEX(เลเวล!$O$5:$O$104,C29)*IF(D29="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>697</v>
+        <v>871</v>
       </c>
       <c r="N29" s="25">
         <f>ROUNDUP(H29/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C29,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C29,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C29,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C29,100))*(1-T29/100)-U29)),0)</f>
@@ -12580,15 +12580,15 @@
       </c>
       <c r="K30" s="25">
         <f>ROUND(INDEX(เลเวล!$M$5:$M$104,C30)*G30*IF(D30="บอส",ตั้งค่า!$C$30,1),0)</f>
-        <v>31975</v>
+        <v>39825</v>
       </c>
       <c r="L30" s="25">
         <f>ROUND(INDEX(เลเวล!$N$5:$N$104,C30)*IF(D30="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>10240</v>
+        <v>12740</v>
       </c>
       <c r="M30" s="25">
         <f>ROUND(INDEX(เลเวล!$O$5:$O$104,C30)*IF(D30="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>15340</v>
+        <v>19120</v>
       </c>
       <c r="N30" s="25">
         <f>ROUNDUP(H30/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C30,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C30,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C30,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C30,100))*(1-T30/100)-U30)),0)</f>
@@ -12666,15 +12666,15 @@
       </c>
       <c r="K31" s="25">
         <f>ROUND(INDEX(เลเวล!$M$5:$M$104,C31)*G31*IF(D31="บอส",ตั้งค่า!$C$30,1),0)</f>
-        <v>1551</v>
+        <v>1930</v>
       </c>
       <c r="L31" s="25">
         <f>ROUND(INDEX(เลเวล!$N$5:$N$104,C31)*IF(D31="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>540</v>
+        <v>671</v>
       </c>
       <c r="M31" s="25">
         <f>ROUND(INDEX(เลเวล!$O$5:$O$104,C31)*IF(D31="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>809</v>
+        <v>1007</v>
       </c>
       <c r="N31" s="25">
         <f>ROUNDUP(H31/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C31,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C31,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C31,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C31,100))*(1-T31/100)-U31)),0)</f>
@@ -12752,15 +12752,15 @@
       </c>
       <c r="K32" s="25">
         <f>ROUND(INDEX(เลเวล!$M$5:$M$104,C32)*G32*IF(D32="บอส",ตั้งค่า!$C$30,1),0)</f>
-        <v>1561</v>
+        <v>1938</v>
       </c>
       <c r="L32" s="25">
         <f>ROUND(INDEX(เลเวล!$N$5:$N$104,C32)*IF(D32="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>568</v>
+        <v>705</v>
       </c>
       <c r="M32" s="25">
         <f>ROUND(INDEX(เลเวล!$O$5:$O$104,C32)*IF(D32="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>851</v>
+        <v>1057</v>
       </c>
       <c r="N32" s="25">
         <f>ROUNDUP(H32/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C32,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C32,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C32,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C32,100))*(1-T32/100)-U32)),0)</f>
@@ -12838,15 +12838,15 @@
       </c>
       <c r="K33" s="25">
         <f>ROUND(INDEX(เลเวล!$M$5:$M$104,C33)*G33*IF(D33="บอส",ตั้งค่า!$C$30,1),0)</f>
-        <v>1563</v>
+        <v>1940</v>
       </c>
       <c r="L33" s="25">
         <f>ROUND(INDEX(เลเวล!$N$5:$N$104,C33)*IF(D33="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>596</v>
+        <v>739</v>
       </c>
       <c r="M33" s="25">
         <f>ROUND(INDEX(เลเวล!$O$5:$O$104,C33)*IF(D33="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>893</v>
+        <v>1109</v>
       </c>
       <c r="N33" s="25">
         <f>ROUNDUP(H33/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C33,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C33,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C33,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C33,100))*(1-T33/100)-U33)),0)</f>
@@ -12924,15 +12924,15 @@
       </c>
       <c r="K34" s="25">
         <f>ROUND(INDEX(เลเวล!$M$5:$M$104,C34)*G34*IF(D34="บอส",ตั้งค่า!$C$30,1),0)</f>
-        <v>1949</v>
+        <v>2414</v>
       </c>
       <c r="L34" s="25">
         <f>ROUND(INDEX(เลเวล!$N$5:$N$104,C34)*IF(D34="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>624</v>
+        <v>772</v>
       </c>
       <c r="M34" s="25">
         <f>ROUND(INDEX(เลเวล!$O$5:$O$104,C34)*IF(D34="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>935</v>
+        <v>1159</v>
       </c>
       <c r="N34" s="25">
         <f>ROUNDUP(H34/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C34,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C34,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C34,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C34,100))*(1-T34/100)-U34)),0)</f>
@@ -13010,15 +13010,15 @@
       </c>
       <c r="K35" s="25">
         <f>ROUND(INDEX(เลเวล!$M$5:$M$104,C35)*G35*IF(D35="บอส",ตั้งค่า!$C$30,1),0)</f>
-        <v>1901</v>
+        <v>2351</v>
       </c>
       <c r="L35" s="25">
         <f>ROUND(INDEX(เลเวล!$N$5:$N$104,C35)*IF(D35="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>661</v>
+        <v>818</v>
       </c>
       <c r="M35" s="25">
         <f>ROUND(INDEX(เลเวล!$O$5:$O$104,C35)*IF(D35="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>992</v>
+        <v>1226</v>
       </c>
       <c r="N35" s="25">
         <f>ROUNDUP(H35/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C35,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C35,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C35,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C35,100))*(1-T35/100)-U35)),0)</f>
@@ -13096,15 +13096,15 @@
       </c>
       <c r="K36" s="25">
         <f>ROUND(INDEX(เลเวล!$M$5:$M$104,C36)*G36*IF(D36="บอส",ตั้งค่า!$C$30,1),0)</f>
-        <v>43650</v>
+        <v>53850</v>
       </c>
       <c r="L36" s="25">
         <f>ROUND(INDEX(เลเวล!$N$5:$N$104,C36)*IF(D36="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>13960</v>
+        <v>17240</v>
       </c>
       <c r="M36" s="25">
         <f>ROUND(INDEX(เลเวล!$O$5:$O$104,C36)*IF(D36="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>20960</v>
+        <v>25840</v>
       </c>
       <c r="N36" s="25">
         <f>ROUNDUP(H36/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C36,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C36,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C36,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C36,100))*(1-T36/100)-U36)),0)</f>
@@ -13182,15 +13182,15 @@
       </c>
       <c r="K37" s="25">
         <f>ROUND(INDEX(เลเวล!$M$5:$M$104,C37)*G37*IF(D37="บอส",ตั้งค่า!$C$30,1),0)</f>
-        <v>2049</v>
+        <v>2521</v>
       </c>
       <c r="L37" s="25">
         <f>ROUND(INDEX(เลเวล!$N$5:$N$104,C37)*IF(D37="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>745</v>
+        <v>917</v>
       </c>
       <c r="M37" s="25">
         <f>ROUND(INDEX(เลเวล!$O$5:$O$104,C37)*IF(D37="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>1118</v>
+        <v>1375</v>
       </c>
       <c r="N37" s="25">
         <f>ROUNDUP(H37/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C37,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C37,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C37,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C37,100))*(1-T37/100)-U37)),0)</f>
@@ -13268,15 +13268,15 @@
       </c>
       <c r="K38" s="25">
         <f>ROUND(INDEX(เลเวล!$M$5:$M$104,C38)*G38*IF(D38="บอส",ตั้งค่า!$C$30,1),0)</f>
-        <v>2054</v>
+        <v>2522</v>
       </c>
       <c r="L38" s="25">
         <f>ROUND(INDEX(เลเวล!$N$5:$N$104,C38)*IF(D38="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>782</v>
+        <v>961</v>
       </c>
       <c r="M38" s="25">
         <f>ROUND(INDEX(เลเวล!$O$5:$O$104,C38)*IF(D38="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>1174</v>
+        <v>1441</v>
       </c>
       <c r="N38" s="25">
         <f>ROUNDUP(H38/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C38,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C38,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C38,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C38,100))*(1-T38/100)-U38)),0)</f>
@@ -13354,15 +13354,15 @@
       </c>
       <c r="K39" s="25">
         <f>ROUND(INDEX(เลเวล!$M$5:$M$104,C39)*G39*IF(D39="บอส",ตั้งค่า!$C$30,1),0)</f>
-        <v>2050</v>
+        <v>2513</v>
       </c>
       <c r="L39" s="25">
         <f>ROUND(INDEX(เลเวล!$N$5:$N$104,C39)*IF(D39="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>820</v>
+        <v>1005</v>
       </c>
       <c r="M39" s="25">
         <f>ROUND(INDEX(เลเวล!$O$5:$O$104,C39)*IF(D39="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>1230</v>
+        <v>1508</v>
       </c>
       <c r="N39" s="25">
         <f>ROUNDUP(H39/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C39,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C39,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C39,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C39,100))*(1-T39/100)-U39)),0)</f>
@@ -13440,15 +13440,15 @@
       </c>
       <c r="K40" s="25">
         <f>ROUND(INDEX(เลเวล!$M$5:$M$104,C40)*G40*IF(D40="บอส",ตั้งค่า!$C$30,1),0)</f>
-        <v>2250</v>
+        <v>2752</v>
       </c>
       <c r="L40" s="25">
         <f>ROUND(INDEX(เลเวล!$N$5:$N$104,C40)*IF(D40="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>857</v>
+        <v>1048</v>
       </c>
       <c r="M40" s="25">
         <f>ROUND(INDEX(เลเวล!$O$5:$O$104,C40)*IF(D40="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>1286</v>
+        <v>1573</v>
       </c>
       <c r="N40" s="25">
         <f>ROUNDUP(H40/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C40,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C40,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C40,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C40,100))*(1-T40/100)-U40)),0)</f>
@@ -13526,15 +13526,15 @@
       </c>
       <c r="K41" s="25">
         <f>ROUND(INDEX(เลเวล!$M$5:$M$104,C41)*G41*IF(D41="บอส",ตั้งค่า!$C$30,1),0)</f>
-        <v>2683</v>
+        <v>3276</v>
       </c>
       <c r="L41" s="25">
         <f>ROUND(INDEX(เลเวล!$N$5:$N$104,C41)*IF(D41="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>894</v>
+        <v>1092</v>
       </c>
       <c r="M41" s="25">
         <f>ROUND(INDEX(เลเวล!$O$5:$O$104,C41)*IF(D41="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>1342</v>
+        <v>1638</v>
       </c>
       <c r="N41" s="25">
         <f>ROUNDUP(H41/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C41,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C41,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C41,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C41,100))*(1-T41/100)-U41)),0)</f>
@@ -13610,15 +13610,15 @@
       </c>
       <c r="K42" s="25">
         <f>ROUND(INDEX(เลเวล!$M$5:$M$104,C42)*G42*IF(D42="บอส",ตั้งค่า!$C$30,1),0)</f>
-        <v>58250</v>
+        <v>70925</v>
       </c>
       <c r="L42" s="25">
         <f>ROUND(INDEX(เลเวล!$N$5:$N$104,C42)*IF(D42="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>18640</v>
+        <v>22700</v>
       </c>
       <c r="M42" s="25">
         <f>ROUND(INDEX(เลเวล!$O$5:$O$104,C42)*IF(D42="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>27960</v>
+        <v>34040</v>
       </c>
       <c r="N42" s="25">
         <f>ROUNDUP(H42/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C42,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C42,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C42,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C42,100))*(1-T42/100)-U42)),0)</f>
@@ -13696,15 +13696,15 @@
       </c>
       <c r="K43" s="25">
         <f>ROUND(INDEX(เลเวล!$M$5:$M$104,C43)*G43*IF(D43="บอส",ตั้งค่า!$C$30,1),0)</f>
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="L43" s="25">
         <f>ROUND(INDEX(เลเวล!$N$5:$N$104,C43)*IF(D43="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="M43" s="25">
         <f>ROUND(INDEX(เลเวล!$O$5:$O$104,C43)*IF(D43="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="N43">
         <f>ROUNDUP(H43/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C43,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C43,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C43,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C43,100))*(1-T43/100)-U43)),0)</f>
@@ -13779,15 +13779,15 @@
       </c>
       <c r="K44" s="25">
         <f>ROUND(INDEX(เลเวล!$M$5:$M$104,C44)*G44*IF(D44="บอส",ตั้งค่า!$C$30,1),0)</f>
-        <v>215</v>
+        <v>274</v>
       </c>
       <c r="L44" s="25">
         <f>ROUND(INDEX(เลเวล!$N$5:$N$104,C44)*IF(D44="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="M44" s="25">
         <f>ROUND(INDEX(เลเวล!$O$5:$O$104,C44)*IF(D44="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>129</v>
+        <v>164</v>
       </c>
       <c r="N44">
         <f>ROUNDUP(H44/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C44,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C44,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C44,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C44,100))*(1-T44/100)-U44)),0)</f>
@@ -13862,15 +13862,15 @@
       </c>
       <c r="K45" s="25">
         <f>ROUND(INDEX(เลเวล!$M$5:$M$104,C45)*G45*IF(D45="บอส",ตั้งค่า!$C$30,1),0)</f>
-        <v>265</v>
+        <v>337</v>
       </c>
       <c r="L45" s="25">
         <f>ROUND(INDEX(เลเวล!$N$5:$N$104,C45)*IF(D45="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="M45" s="25">
         <f>ROUND(INDEX(เลเวล!$O$5:$O$104,C45)*IF(D45="บอส",ตั้งค่า!$C$33,1),0)</f>
-        <v>159</v>
+        <v>202</v>
       </c>
       <c r="N45">
         <f>ROUNDUP(H45/(INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C45,100))/100*INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C45,100))*1.4+(1-INDEX(สายเลี้ยงตัว!$H$5:$H$104,MIN(C45,100))/100)*MAX(1,INDEX(สายเลี้ยงตัว!$E$5:$E$104,MIN(C45,100))*(1-T45/100)-U45)),0)</f>
